--- a/public/data/orders.xlsx
+++ b/public/data/orders.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="806">
   <si>
     <t>Submitted time</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Morning</t>
   </si>
   <si>
-    <t>- (clement jangan tulisa nama)</t>
+    <t/>
   </si>
   <si>
     <t>22</t>
@@ -209,9 +209,6 @@
   </si>
   <si>
     <t>Davin P</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>8</t>
@@ -3105,10 +3102,10 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
         <v>65</v>
-      </c>
-      <c r="E11" t="s">
-        <v>66</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -3126,24 +3123,24 @@
         <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
         <v>68</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" t="s">
         <v>70</v>
-      </c>
-      <c r="E12" t="s">
-        <v>71</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
@@ -3161,24 +3158,24 @@
         <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
         <v>73</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" t="s">
         <v>75</v>
-      </c>
-      <c r="E13" t="s">
-        <v>76</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -3196,24 +3193,24 @@
         <v>20</v>
       </c>
       <c r="K13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
         <v>78</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
         <v>80</v>
-      </c>
-      <c r="E14" t="s">
-        <v>81</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
@@ -3231,21 +3228,21 @@
         <v>20</v>
       </c>
       <c r="K14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
         <v>61</v>
@@ -3266,24 +3263,24 @@
         <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
         <v>86</v>
-      </c>
-      <c r="B16" t="s">
-        <v>87</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
@@ -3301,24 +3298,24 @@
         <v>25</v>
       </c>
       <c r="K16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
         <v>90</v>
-      </c>
-      <c r="B17" t="s">
-        <v>91</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
       </c>
       <c r="D17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" t="s">
         <v>92</v>
-      </c>
-      <c r="E17" t="s">
-        <v>93</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
@@ -3336,24 +3333,24 @@
         <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" t="s">
         <v>95</v>
-      </c>
-      <c r="B18" t="s">
-        <v>96</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
       </c>
       <c r="D18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" t="s">
         <v>97</v>
-      </c>
-      <c r="E18" t="s">
-        <v>98</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -3371,24 +3368,24 @@
         <v>25</v>
       </c>
       <c r="K18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" t="s">
         <v>100</v>
-      </c>
-      <c r="B19" t="s">
-        <v>101</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F19" t="s">
         <v>34</v>
@@ -3406,24 +3403,24 @@
         <v>25</v>
       </c>
       <c r="K19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" t="s">
         <v>104</v>
-      </c>
-      <c r="B20" t="s">
-        <v>105</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
       </c>
       <c r="D20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" t="s">
         <v>106</v>
-      </c>
-      <c r="E20" t="s">
-        <v>107</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
@@ -3441,24 +3438,24 @@
         <v>20</v>
       </c>
       <c r="K20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" t="s">
         <v>109</v>
       </c>
-      <c r="B21" t="s">
-        <v>110</v>
-      </c>
       <c r="C21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" t="s">
         <v>111</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>112</v>
-      </c>
-      <c r="E21" t="s">
-        <v>113</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
@@ -3476,21 +3473,21 @@
         <v>20</v>
       </c>
       <c r="K21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" t="s">
         <v>115</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>116</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>117</v>
-      </c>
-      <c r="D22" t="s">
-        <v>118</v>
       </c>
       <c r="E22" t="s">
         <v>55</v>
@@ -3511,24 +3508,24 @@
         <v>25</v>
       </c>
       <c r="K22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" t="s">
         <v>120</v>
       </c>
-      <c r="B23" t="s">
-        <v>121</v>
-      </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -3540,30 +3537,30 @@
         <v>36</v>
       </c>
       <c r="I23" t="s">
+        <v>121</v>
+      </c>
+      <c r="J23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" t="s">
         <v>122</v>
-      </c>
-      <c r="J23" t="s">
-        <v>25</v>
-      </c>
-      <c r="K23" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" t="s">
         <v>124</v>
       </c>
-      <c r="C24" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>125</v>
-      </c>
-      <c r="E24" t="s">
-        <v>126</v>
       </c>
       <c r="F24" t="s">
         <v>16</v>
@@ -3581,24 +3578,24 @@
         <v>25</v>
       </c>
       <c r="K24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" t="s">
         <v>128</v>
       </c>
-      <c r="C25" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>129</v>
-      </c>
-      <c r="E25" t="s">
-        <v>130</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -3616,24 +3613,24 @@
         <v>25</v>
       </c>
       <c r="K25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
         <v>132</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" t="s">
         <v>133</v>
       </c>
-      <c r="C26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>134</v>
-      </c>
-      <c r="E26" t="s">
-        <v>135</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
@@ -3651,24 +3648,24 @@
         <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" t="s">
         <v>137</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
         <v>138</v>
       </c>
-      <c r="C27" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>139</v>
-      </c>
-      <c r="E27" t="s">
-        <v>140</v>
       </c>
       <c r="F27" t="s">
         <v>34</v>
@@ -3677,7 +3674,7 @@
         <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I27" t="s">
         <v>19</v>
@@ -3686,21 +3683,21 @@
         <v>25</v>
       </c>
       <c r="K27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" t="s">
         <v>142</v>
       </c>
-      <c r="B28" t="s">
-        <v>143</v>
-      </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E28" t="s">
         <v>33</v>
@@ -3715,30 +3712,30 @@
         <v>36</v>
       </c>
       <c r="I28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J28" t="s">
         <v>20</v>
       </c>
       <c r="K28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
         <v>145</v>
       </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>146</v>
-      </c>
       <c r="E29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F29" t="s">
         <v>16</v>
@@ -3756,24 +3753,24 @@
         <v>25</v>
       </c>
       <c r="K29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>146</v>
+      </c>
+      <c r="B30" t="s">
         <v>147</v>
-      </c>
-      <c r="B30" t="s">
-        <v>148</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" t="s">
         <v>149</v>
-      </c>
-      <c r="E30" t="s">
-        <v>150</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -3791,21 +3788,21 @@
         <v>25</v>
       </c>
       <c r="K30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B31" t="s">
+        <v>151</v>
+      </c>
+      <c r="C31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" t="s">
         <v>152</v>
-      </c>
-      <c r="C31" t="s">
-        <v>111</v>
-      </c>
-      <c r="D31" t="s">
-        <v>153</v>
       </c>
       <c r="E31" t="s">
         <v>33</v>
@@ -3826,24 +3823,24 @@
         <v>20</v>
       </c>
       <c r="K31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" t="s">
         <v>155</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" t="s">
         <v>156</v>
       </c>
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>157</v>
-      </c>
-      <c r="E32" t="s">
-        <v>158</v>
       </c>
       <c r="F32" t="s">
         <v>16</v>
@@ -3861,24 +3858,24 @@
         <v>20</v>
       </c>
       <c r="K32" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" t="s">
         <v>160</v>
       </c>
-      <c r="C33" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>161</v>
-      </c>
-      <c r="E33" t="s">
-        <v>162</v>
       </c>
       <c r="F33" t="s">
         <v>16</v>
@@ -3896,24 +3893,24 @@
         <v>25</v>
       </c>
       <c r="K33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" t="s">
         <v>164</v>
       </c>
-      <c r="C34" t="s">
-        <v>111</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>165</v>
-      </c>
-      <c r="E34" t="s">
-        <v>166</v>
       </c>
       <c r="F34" t="s">
         <v>16</v>
@@ -3931,24 +3928,24 @@
         <v>25</v>
       </c>
       <c r="K34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C35" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" t="s">
         <v>168</v>
       </c>
-      <c r="C35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>169</v>
-      </c>
-      <c r="E35" t="s">
-        <v>170</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
@@ -3966,24 +3963,24 @@
         <v>25</v>
       </c>
       <c r="K35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" t="s">
         <v>172</v>
-      </c>
-      <c r="B36" t="s">
-        <v>173</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
@@ -3992,7 +3989,7 @@
         <v>17</v>
       </c>
       <c r="H36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I36" t="s">
         <v>19</v>
@@ -4001,24 +3998,24 @@
         <v>20</v>
       </c>
       <c r="K36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>175</v>
+      </c>
+      <c r="B37" t="s">
         <v>176</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" t="s">
         <v>177</v>
       </c>
-      <c r="C37" t="s">
-        <v>111</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>178</v>
-      </c>
-      <c r="E37" t="s">
-        <v>179</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
@@ -4036,21 +4033,21 @@
         <v>25</v>
       </c>
       <c r="K37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B38" t="s">
+        <v>179</v>
+      </c>
+      <c r="C38" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" t="s">
         <v>180</v>
-      </c>
-      <c r="C38" t="s">
-        <v>111</v>
-      </c>
-      <c r="D38" t="s">
-        <v>181</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4071,24 +4068,24 @@
         <v>20</v>
       </c>
       <c r="K38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39" t="s">
         <v>183</v>
-      </c>
-      <c r="B39" t="s">
-        <v>184</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
       </c>
       <c r="D39" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" t="s">
         <v>185</v>
-      </c>
-      <c r="E39" t="s">
-        <v>186</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -4106,21 +4103,21 @@
         <v>25</v>
       </c>
       <c r="K39" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>187</v>
+      </c>
+      <c r="B40" t="s">
         <v>188</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" t="s">
         <v>189</v>
-      </c>
-      <c r="C40" t="s">
-        <v>111</v>
-      </c>
-      <c r="D40" t="s">
-        <v>190</v>
       </c>
       <c r="E40" t="s">
         <v>55</v>
@@ -4132,7 +4129,7 @@
         <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I40" t="s">
         <v>19</v>
@@ -4141,24 +4138,24 @@
         <v>20</v>
       </c>
       <c r="K40" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41" t="s">
         <v>191</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" t="s">
         <v>192</v>
       </c>
-      <c r="C41" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>193</v>
-      </c>
-      <c r="E41" t="s">
-        <v>194</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
@@ -4176,24 +4173,24 @@
         <v>25</v>
       </c>
       <c r="K41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" t="s">
         <v>196</v>
-      </c>
-      <c r="B42" t="s">
-        <v>197</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
       </c>
       <c r="D42" t="s">
+        <v>197</v>
+      </c>
+      <c r="E42" t="s">
         <v>198</v>
-      </c>
-      <c r="E42" t="s">
-        <v>199</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
@@ -4211,24 +4208,24 @@
         <v>25</v>
       </c>
       <c r="K42" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B43" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" t="s">
         <v>201</v>
       </c>
-      <c r="C43" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>202</v>
-      </c>
-      <c r="E43" t="s">
-        <v>203</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
@@ -4246,24 +4243,24 @@
         <v>25</v>
       </c>
       <c r="K43" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>204</v>
+      </c>
+      <c r="B44" t="s">
         <v>205</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" t="s">
         <v>206</v>
       </c>
-      <c r="C44" t="s">
-        <v>111</v>
-      </c>
-      <c r="D44" t="s">
-        <v>207</v>
-      </c>
       <c r="E44" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
@@ -4275,27 +4272,27 @@
         <v>42</v>
       </c>
       <c r="I44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J44" t="s">
         <v>20</v>
       </c>
       <c r="K44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" t="s">
         <v>209</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" t="s">
         <v>210</v>
-      </c>
-      <c r="C45" t="s">
-        <v>111</v>
-      </c>
-      <c r="D45" t="s">
-        <v>211</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4316,24 +4313,24 @@
         <v>20</v>
       </c>
       <c r="K45" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>212</v>
+      </c>
+      <c r="B46" t="s">
         <v>213</v>
-      </c>
-      <c r="B46" t="s">
-        <v>214</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E46" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
@@ -4351,21 +4348,21 @@
         <v>20</v>
       </c>
       <c r="K46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>216</v>
+      </c>
+      <c r="B47" t="s">
         <v>217</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" t="s">
         <v>218</v>
-      </c>
-      <c r="C47" t="s">
-        <v>111</v>
-      </c>
-      <c r="D47" t="s">
-        <v>219</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -4377,7 +4374,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
@@ -4386,24 +4383,24 @@
         <v>25</v>
       </c>
       <c r="K47" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>220</v>
+      </c>
+      <c r="B48" t="s">
         <v>221</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" t="s">
         <v>222</v>
       </c>
-      <c r="C48" t="s">
-        <v>111</v>
-      </c>
-      <c r="D48" t="s">
-        <v>223</v>
-      </c>
       <c r="E48" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -4421,21 +4418,21 @@
         <v>20</v>
       </c>
       <c r="K48" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>224</v>
+      </c>
+      <c r="B49" t="s">
         <v>225</v>
-      </c>
-      <c r="B49" t="s">
-        <v>226</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E49" t="s">
         <v>61</v>
@@ -4447,7 +4444,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
@@ -4456,24 +4453,24 @@
         <v>20</v>
       </c>
       <c r="K49" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>227</v>
+      </c>
+      <c r="B50" t="s">
         <v>228</v>
-      </c>
-      <c r="B50" t="s">
-        <v>229</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -4491,24 +4488,24 @@
         <v>20</v>
       </c>
       <c r="K50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>231</v>
+      </c>
+      <c r="B51" t="s">
         <v>232</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>110</v>
+      </c>
+      <c r="D51" t="s">
         <v>233</v>
       </c>
-      <c r="C51" t="s">
-        <v>111</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>234</v>
-      </c>
-      <c r="E51" t="s">
-        <v>235</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
@@ -4526,24 +4523,24 @@
         <v>25</v>
       </c>
       <c r="K51" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>236</v>
+      </c>
+      <c r="B52" t="s">
         <v>237</v>
-      </c>
-      <c r="B52" t="s">
-        <v>238</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E52" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s">
         <v>34</v>
@@ -4561,21 +4558,21 @@
         <v>25</v>
       </c>
       <c r="K52" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>239</v>
+      </c>
+      <c r="B53" t="s">
         <v>240</v>
-      </c>
-      <c r="B53" t="s">
-        <v>241</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E53" t="s">
         <v>47</v>
@@ -4596,21 +4593,21 @@
         <v>25</v>
       </c>
       <c r="K53" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>243</v>
+      </c>
+      <c r="B54" t="s">
         <v>244</v>
-      </c>
-      <c r="B54" t="s">
-        <v>245</v>
       </c>
       <c r="C54" t="s">
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E54" t="s">
         <v>55</v>
@@ -4631,21 +4628,21 @@
         <v>25</v>
       </c>
       <c r="K54" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>247</v>
+      </c>
+      <c r="B55" t="s">
         <v>248</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" t="s">
         <v>249</v>
-      </c>
-      <c r="C55" t="s">
-        <v>111</v>
-      </c>
-      <c r="D55" t="s">
-        <v>250</v>
       </c>
       <c r="E55" t="s">
         <v>47</v>
@@ -4666,24 +4663,24 @@
         <v>20</v>
       </c>
       <c r="K55" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>251</v>
+      </c>
+      <c r="B56" t="s">
         <v>252</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
+        <v>110</v>
+      </c>
+      <c r="D56" t="s">
         <v>253</v>
       </c>
-      <c r="C56" t="s">
-        <v>111</v>
-      </c>
-      <c r="D56" t="s">
-        <v>254</v>
-      </c>
       <c r="E56" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
@@ -4701,24 +4698,24 @@
         <v>20</v>
       </c>
       <c r="K56" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>255</v>
+      </c>
+      <c r="B57" t="s">
         <v>256</v>
-      </c>
-      <c r="B57" t="s">
-        <v>257</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
       </c>
       <c r="D57" t="s">
+        <v>257</v>
+      </c>
+      <c r="E57" t="s">
         <v>258</v>
-      </c>
-      <c r="E57" t="s">
-        <v>259</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
@@ -4736,21 +4733,21 @@
         <v>25</v>
       </c>
       <c r="K57" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>260</v>
+      </c>
+      <c r="B58" t="s">
         <v>261</v>
-      </c>
-      <c r="B58" t="s">
-        <v>262</v>
       </c>
       <c r="C58" t="s">
         <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E58" t="s">
         <v>55</v>
@@ -4765,27 +4762,27 @@
         <v>42</v>
       </c>
       <c r="I58" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J58" t="s">
         <v>25</v>
       </c>
       <c r="K58" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>264</v>
+      </c>
+      <c r="B59" t="s">
         <v>265</v>
-      </c>
-      <c r="B59" t="s">
-        <v>266</v>
       </c>
       <c r="C59" t="s">
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E59" t="s">
         <v>47</v>
@@ -4806,24 +4803,24 @@
         <v>25</v>
       </c>
       <c r="K59" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>268</v>
+      </c>
+      <c r="B60" t="s">
         <v>269</v>
-      </c>
-      <c r="B60" t="s">
-        <v>270</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E60" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F60" t="s">
         <v>34</v>
@@ -4841,21 +4838,21 @@
         <v>25</v>
       </c>
       <c r="K60" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>272</v>
+      </c>
+      <c r="B61" t="s">
         <v>273</v>
-      </c>
-      <c r="B61" t="s">
-        <v>274</v>
       </c>
       <c r="C61" t="s">
         <v>13</v>
       </c>
       <c r="D61" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -4876,24 +4873,24 @@
         <v>25</v>
       </c>
       <c r="K61" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>275</v>
+      </c>
+      <c r="B62" t="s">
         <v>276</v>
       </c>
-      <c r="B62" t="s">
-        <v>277</v>
-      </c>
       <c r="C62" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D62" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
@@ -4902,7 +4899,7 @@
         <v>17</v>
       </c>
       <c r="H62" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
@@ -4911,24 +4908,24 @@
         <v>20</v>
       </c>
       <c r="K62" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>278</v>
+      </c>
+      <c r="B63" t="s">
         <v>279</v>
-      </c>
-      <c r="B63" t="s">
-        <v>280</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F63" t="s">
         <v>16</v>
@@ -4946,24 +4943,24 @@
         <v>25</v>
       </c>
       <c r="K63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>282</v>
+      </c>
+      <c r="B64" t="s">
         <v>283</v>
-      </c>
-      <c r="B64" t="s">
-        <v>284</v>
       </c>
       <c r="C64" t="s">
         <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
@@ -4981,24 +4978,24 @@
         <v>20</v>
       </c>
       <c r="K64" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>286</v>
+      </c>
+      <c r="B65" t="s">
         <v>287</v>
-      </c>
-      <c r="B65" t="s">
-        <v>288</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E65" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
@@ -5016,24 +5013,24 @@
         <v>20</v>
       </c>
       <c r="K65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>290</v>
+      </c>
+      <c r="B66" t="s">
         <v>291</v>
-      </c>
-      <c r="B66" t="s">
-        <v>292</v>
       </c>
       <c r="C66" t="s">
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F66" t="s">
         <v>34</v>
@@ -5051,24 +5048,24 @@
         <v>20</v>
       </c>
       <c r="K66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>293</v>
+      </c>
+      <c r="B67" t="s">
         <v>294</v>
-      </c>
-      <c r="B67" t="s">
-        <v>295</v>
       </c>
       <c r="C67" t="s">
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E67" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
@@ -5086,24 +5083,24 @@
         <v>20</v>
       </c>
       <c r="K67" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>297</v>
+      </c>
+      <c r="B68" t="s">
         <v>298</v>
-      </c>
-      <c r="B68" t="s">
-        <v>299</v>
       </c>
       <c r="C68" t="s">
         <v>13</v>
       </c>
       <c r="D68" t="s">
+        <v>299</v>
+      </c>
+      <c r="E68" t="s">
         <v>300</v>
-      </c>
-      <c r="E68" t="s">
-        <v>301</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
@@ -5121,24 +5118,24 @@
         <v>25</v>
       </c>
       <c r="K68" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>302</v>
+      </c>
+      <c r="B69" t="s">
         <v>303</v>
-      </c>
-      <c r="B69" t="s">
-        <v>304</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
         <v>16</v>
@@ -5156,24 +5153,24 @@
         <v>25</v>
       </c>
       <c r="K69" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>306</v>
+      </c>
+      <c r="B70" t="s">
         <v>307</v>
-      </c>
-      <c r="B70" t="s">
-        <v>308</v>
       </c>
       <c r="C70" t="s">
         <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F70" t="s">
         <v>16</v>
@@ -5191,24 +5188,24 @@
         <v>20</v>
       </c>
       <c r="K70" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>310</v>
+      </c>
+      <c r="B71" t="s">
         <v>311</v>
-      </c>
-      <c r="B71" t="s">
-        <v>312</v>
       </c>
       <c r="C71" t="s">
         <v>13</v>
       </c>
       <c r="D71" t="s">
+        <v>312</v>
+      </c>
+      <c r="E71" t="s">
         <v>313</v>
-      </c>
-      <c r="E71" t="s">
-        <v>314</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
@@ -5226,24 +5223,24 @@
         <v>20</v>
       </c>
       <c r="K71" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>315</v>
+      </c>
+      <c r="B72" t="s">
         <v>316</v>
-      </c>
-      <c r="B72" t="s">
-        <v>317</v>
       </c>
       <c r="C72" t="s">
         <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E72" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F72" t="s">
         <v>34</v>
@@ -5261,24 +5258,24 @@
         <v>25</v>
       </c>
       <c r="K72" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B73" t="s">
+        <v>191</v>
+      </c>
+      <c r="C73" t="s">
+        <v>110</v>
+      </c>
+      <c r="D73" t="s">
         <v>192</v>
       </c>
-      <c r="C73" t="s">
-        <v>111</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>193</v>
-      </c>
-      <c r="E73" t="s">
-        <v>194</v>
       </c>
       <c r="F73" t="s">
         <v>16</v>
@@ -5296,24 +5293,24 @@
         <v>20</v>
       </c>
       <c r="K73" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>321</v>
+      </c>
+      <c r="B74" t="s">
         <v>322</v>
-      </c>
-      <c r="B74" t="s">
-        <v>323</v>
       </c>
       <c r="C74" t="s">
         <v>13</v>
       </c>
       <c r="D74" t="s">
+        <v>323</v>
+      </c>
+      <c r="E74" t="s">
         <v>324</v>
-      </c>
-      <c r="E74" t="s">
-        <v>325</v>
       </c>
       <c r="F74" t="s">
         <v>34</v>
@@ -5325,30 +5322,30 @@
         <v>56</v>
       </c>
       <c r="I74" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J74" t="s">
         <v>25</v>
       </c>
       <c r="K74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B75" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C75" t="s">
         <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E75" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F75" t="s">
         <v>34</v>
@@ -5366,21 +5363,21 @@
         <v>25</v>
       </c>
       <c r="K75" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>327</v>
+      </c>
+      <c r="B76" t="s">
         <v>328</v>
-      </c>
-      <c r="B76" t="s">
-        <v>329</v>
       </c>
       <c r="C76" t="s">
         <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E76" t="s">
         <v>29</v>
@@ -5401,21 +5398,21 @@
         <v>20</v>
       </c>
       <c r="K76" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C77" t="s">
         <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E77" t="s">
         <v>29</v>
@@ -5436,24 +5433,24 @@
         <v>25</v>
       </c>
       <c r="K77" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>332</v>
+      </c>
+      <c r="B78" t="s">
         <v>333</v>
-      </c>
-      <c r="B78" t="s">
-        <v>334</v>
       </c>
       <c r="C78" t="s">
         <v>13</v>
       </c>
       <c r="D78" t="s">
+        <v>334</v>
+      </c>
+      <c r="E78" t="s">
         <v>335</v>
-      </c>
-      <c r="E78" t="s">
-        <v>336</v>
       </c>
       <c r="F78" t="s">
         <v>16</v>
@@ -5471,21 +5468,21 @@
         <v>25</v>
       </c>
       <c r="K78" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>337</v>
+      </c>
+      <c r="B79" t="s">
         <v>338</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
+        <v>110</v>
+      </c>
+      <c r="D79" t="s">
         <v>339</v>
-      </c>
-      <c r="C79" t="s">
-        <v>111</v>
-      </c>
-      <c r="D79" t="s">
-        <v>340</v>
       </c>
       <c r="E79" t="s">
         <v>29</v>
@@ -5506,24 +5503,24 @@
         <v>25</v>
       </c>
       <c r="K79" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>341</v>
+      </c>
+      <c r="B80" t="s">
         <v>342</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
+        <v>110</v>
+      </c>
+      <c r="D80" t="s">
         <v>343</v>
       </c>
-      <c r="C80" t="s">
-        <v>111</v>
-      </c>
-      <c r="D80" t="s">
-        <v>344</v>
-      </c>
       <c r="E80" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F80" t="s">
         <v>16</v>
@@ -5541,21 +5538,21 @@
         <v>25</v>
       </c>
       <c r="K80" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>345</v>
+      </c>
+      <c r="B81" t="s">
         <v>346</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
+        <v>110</v>
+      </c>
+      <c r="D81" t="s">
         <v>347</v>
-      </c>
-      <c r="C81" t="s">
-        <v>111</v>
-      </c>
-      <c r="D81" t="s">
-        <v>348</v>
       </c>
       <c r="E81" t="s">
         <v>61</v>
@@ -5576,24 +5573,24 @@
         <v>20</v>
       </c>
       <c r="K81" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>349</v>
+      </c>
+      <c r="B82" t="s">
         <v>350</v>
-      </c>
-      <c r="B82" t="s">
-        <v>351</v>
       </c>
       <c r="C82" t="s">
         <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F82" t="s">
         <v>34</v>
@@ -5611,24 +5608,24 @@
         <v>25</v>
       </c>
       <c r="K82" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>352</v>
+      </c>
+      <c r="B83" t="s">
         <v>353</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
+        <v>110</v>
+      </c>
+      <c r="D83" t="s">
         <v>354</v>
       </c>
-      <c r="C83" t="s">
-        <v>111</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>355</v>
-      </c>
-      <c r="E83" t="s">
-        <v>356</v>
       </c>
       <c r="F83" t="s">
         <v>16</v>
@@ -5637,7 +5634,7 @@
         <v>35</v>
       </c>
       <c r="H83" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I83" t="s">
         <v>19</v>
@@ -5646,21 +5643,21 @@
         <v>25</v>
       </c>
       <c r="K83" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>357</v>
+      </c>
+      <c r="B84" t="s">
         <v>358</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
+        <v>110</v>
+      </c>
+      <c r="D84" t="s">
         <v>359</v>
-      </c>
-      <c r="C84" t="s">
-        <v>111</v>
-      </c>
-      <c r="D84" t="s">
-        <v>360</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -5681,24 +5678,24 @@
         <v>25</v>
       </c>
       <c r="K84" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>361</v>
+      </c>
+      <c r="B85" t="s">
         <v>362</v>
-      </c>
-      <c r="B85" t="s">
-        <v>363</v>
       </c>
       <c r="C85" t="s">
         <v>13</v>
       </c>
       <c r="D85" t="s">
+        <v>363</v>
+      </c>
+      <c r="E85" t="s">
         <v>364</v>
-      </c>
-      <c r="E85" t="s">
-        <v>365</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -5716,24 +5713,24 @@
         <v>25</v>
       </c>
       <c r="K85" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>366</v>
+      </c>
+      <c r="B86" t="s">
         <v>367</v>
-      </c>
-      <c r="B86" t="s">
-        <v>368</v>
       </c>
       <c r="C86" t="s">
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E86" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F86" t="s">
         <v>16</v>
@@ -5751,21 +5748,21 @@
         <v>25</v>
       </c>
       <c r="K86" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>370</v>
+      </c>
+      <c r="B87" t="s">
         <v>371</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
+        <v>110</v>
+      </c>
+      <c r="D87" t="s">
         <v>372</v>
-      </c>
-      <c r="C87" t="s">
-        <v>111</v>
-      </c>
-      <c r="D87" t="s">
-        <v>373</v>
       </c>
       <c r="E87" t="s">
         <v>33</v>
@@ -5786,24 +5783,24 @@
         <v>25</v>
       </c>
       <c r="K87" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B88" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C88" t="s">
         <v>13</v>
       </c>
       <c r="D88" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E88" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F88" t="s">
         <v>34</v>
@@ -5821,24 +5818,24 @@
         <v>25</v>
       </c>
       <c r="K88" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
+        <v>377</v>
+      </c>
+      <c r="B89" t="s">
         <v>378</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>110</v>
+      </c>
+      <c r="D89" t="s">
         <v>379</v>
       </c>
-      <c r="C89" t="s">
-        <v>111</v>
-      </c>
-      <c r="D89" t="s">
-        <v>380</v>
-      </c>
       <c r="E89" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F89" t="s">
         <v>16</v>
@@ -5856,21 +5853,21 @@
         <v>25</v>
       </c>
       <c r="K89" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
+        <v>381</v>
+      </c>
+      <c r="B90" t="s">
         <v>382</v>
-      </c>
-      <c r="B90" t="s">
-        <v>383</v>
       </c>
       <c r="C90" t="s">
         <v>13</v>
       </c>
       <c r="D90" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E90" t="s">
         <v>61</v>
@@ -5882,7 +5879,7 @@
         <v>17</v>
       </c>
       <c r="H90" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I90" t="s">
         <v>19</v>
@@ -5891,24 +5888,24 @@
         <v>25</v>
       </c>
       <c r="K90" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
+        <v>385</v>
+      </c>
+      <c r="B91" t="s">
         <v>386</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
+        <v>110</v>
+      </c>
+      <c r="D91" t="s">
         <v>387</v>
       </c>
-      <c r="C91" t="s">
-        <v>111</v>
-      </c>
-      <c r="D91" t="s">
-        <v>388</v>
-      </c>
       <c r="E91" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F91" t="s">
         <v>16</v>
@@ -5926,24 +5923,24 @@
         <v>25</v>
       </c>
       <c r="K91" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>389</v>
+      </c>
+      <c r="B92" t="s">
         <v>390</v>
-      </c>
-      <c r="B92" t="s">
-        <v>391</v>
       </c>
       <c r="C92" t="s">
         <v>13</v>
       </c>
       <c r="D92" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E92" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F92" t="s">
         <v>16</v>
@@ -5961,21 +5958,21 @@
         <v>20</v>
       </c>
       <c r="K92" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B93" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C93" t="s">
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E93" t="s">
         <v>55</v>
@@ -5987,7 +5984,7 @@
         <v>35</v>
       </c>
       <c r="H93" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
@@ -5996,24 +5993,24 @@
         <v>25</v>
       </c>
       <c r="K93" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
+        <v>395</v>
+      </c>
+      <c r="B94" t="s">
         <v>396</v>
-      </c>
-      <c r="B94" t="s">
-        <v>397</v>
       </c>
       <c r="C94" t="s">
         <v>13</v>
       </c>
       <c r="D94" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E94" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F94" t="s">
         <v>16</v>
@@ -6031,24 +6028,24 @@
         <v>20</v>
       </c>
       <c r="K94" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>399</v>
+      </c>
+      <c r="B95" t="s">
         <v>400</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
+        <v>110</v>
+      </c>
+      <c r="D95" t="s">
         <v>401</v>
       </c>
-      <c r="C95" t="s">
-        <v>111</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>402</v>
-      </c>
-      <c r="E95" t="s">
-        <v>403</v>
       </c>
       <c r="F95" t="s">
         <v>16</v>
@@ -6066,24 +6063,24 @@
         <v>20</v>
       </c>
       <c r="K95" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
+        <v>404</v>
+      </c>
+      <c r="B96" t="s">
         <v>405</v>
-      </c>
-      <c r="B96" t="s">
-        <v>406</v>
       </c>
       <c r="C96" t="s">
         <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E96" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F96" t="s">
         <v>16</v>
@@ -6101,24 +6098,24 @@
         <v>25</v>
       </c>
       <c r="K96" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
+        <v>408</v>
+      </c>
+      <c r="B97" t="s">
         <v>409</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
+        <v>110</v>
+      </c>
+      <c r="D97" t="s">
         <v>410</v>
       </c>
-      <c r="C97" t="s">
-        <v>111</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>411</v>
-      </c>
-      <c r="E97" t="s">
-        <v>412</v>
       </c>
       <c r="F97" t="s">
         <v>16</v>
@@ -6130,30 +6127,30 @@
         <v>36</v>
       </c>
       <c r="I97" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J97" t="s">
         <v>25</v>
       </c>
       <c r="K97" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>413</v>
+      </c>
+      <c r="B98" t="s">
         <v>414</v>
-      </c>
-      <c r="B98" t="s">
-        <v>415</v>
       </c>
       <c r="C98" t="s">
         <v>13</v>
       </c>
       <c r="D98" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98" t="s">
         <v>65</v>
-      </c>
-      <c r="E98" t="s">
-        <v>66</v>
       </c>
       <c r="F98" t="s">
         <v>34</v>
@@ -6171,24 +6168,24 @@
         <v>25</v>
       </c>
       <c r="K98" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>416</v>
+      </c>
+      <c r="B99" t="s">
         <v>417</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
+        <v>110</v>
+      </c>
+      <c r="D99" t="s">
         <v>418</v>
       </c>
-      <c r="C99" t="s">
-        <v>111</v>
-      </c>
-      <c r="D99" t="s">
-        <v>419</v>
-      </c>
       <c r="E99" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F99" t="s">
         <v>16</v>
@@ -6206,24 +6203,24 @@
         <v>25</v>
       </c>
       <c r="K99" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B100" t="s">
+        <v>137</v>
+      </c>
+      <c r="C100" t="s">
+        <v>110</v>
+      </c>
+      <c r="D100" t="s">
         <v>138</v>
       </c>
-      <c r="C100" t="s">
-        <v>111</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>139</v>
-      </c>
-      <c r="E100" t="s">
-        <v>140</v>
       </c>
       <c r="F100" t="s">
         <v>34</v>
@@ -6232,7 +6229,7 @@
         <v>17</v>
       </c>
       <c r="H100" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
@@ -6241,24 +6238,24 @@
         <v>20</v>
       </c>
       <c r="K100" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>421</v>
+      </c>
+      <c r="B101" t="s">
         <v>422</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
+        <v>110</v>
+      </c>
+      <c r="D101" t="s">
         <v>423</v>
       </c>
-      <c r="C101" t="s">
-        <v>111</v>
-      </c>
-      <c r="D101" t="s">
-        <v>424</v>
-      </c>
       <c r="E101" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F101" t="s">
         <v>16</v>
@@ -6276,24 +6273,24 @@
         <v>20</v>
       </c>
       <c r="K101" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
+        <v>425</v>
+      </c>
+      <c r="B102" t="s">
         <v>426</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
+        <v>110</v>
+      </c>
+      <c r="D102" t="s">
         <v>427</v>
       </c>
-      <c r="C102" t="s">
-        <v>111</v>
-      </c>
-      <c r="D102" t="s">
-        <v>428</v>
-      </c>
       <c r="E102" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F102" t="s">
         <v>16</v>
@@ -6311,24 +6308,24 @@
         <v>20</v>
       </c>
       <c r="K102" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
+        <v>429</v>
+      </c>
+      <c r="B103" t="s">
         <v>430</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
+        <v>110</v>
+      </c>
+      <c r="D103" t="s">
         <v>431</v>
       </c>
-      <c r="C103" t="s">
-        <v>111</v>
-      </c>
-      <c r="D103" t="s">
-        <v>432</v>
-      </c>
       <c r="E103" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F103" t="s">
         <v>16</v>
@@ -6346,21 +6343,21 @@
         <v>25</v>
       </c>
       <c r="K103" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
+        <v>433</v>
+      </c>
+      <c r="B104" t="s">
+        <v>430</v>
+      </c>
+      <c r="C104" t="s">
+        <v>110</v>
+      </c>
+      <c r="D104" t="s">
         <v>434</v>
-      </c>
-      <c r="B104" t="s">
-        <v>431</v>
-      </c>
-      <c r="C104" t="s">
-        <v>111</v>
-      </c>
-      <c r="D104" t="s">
-        <v>435</v>
       </c>
       <c r="E104" t="s">
         <v>41</v>
@@ -6372,33 +6369,33 @@
         <v>17</v>
       </c>
       <c r="H104" t="s">
+        <v>435</v>
+      </c>
+      <c r="I104" t="s">
+        <v>19</v>
+      </c>
+      <c r="J104" t="s">
+        <v>25</v>
+      </c>
+      <c r="K104" t="s">
         <v>436</v>
-      </c>
-      <c r="I104" t="s">
-        <v>19</v>
-      </c>
-      <c r="J104" t="s">
-        <v>25</v>
-      </c>
-      <c r="K104" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
+        <v>437</v>
+      </c>
+      <c r="B105" t="s">
         <v>438</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
+        <v>110</v>
+      </c>
+      <c r="D105" t="s">
         <v>439</v>
       </c>
-      <c r="C105" t="s">
-        <v>111</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>440</v>
-      </c>
-      <c r="E105" t="s">
-        <v>441</v>
       </c>
       <c r="F105" t="s">
         <v>34</v>
@@ -6410,30 +6407,30 @@
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J105" t="s">
         <v>25</v>
       </c>
       <c r="K105" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
+        <v>441</v>
+      </c>
+      <c r="B106" t="s">
         <v>442</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
+        <v>110</v>
+      </c>
+      <c r="D106" t="s">
         <v>443</v>
       </c>
-      <c r="C106" t="s">
-        <v>111</v>
-      </c>
-      <c r="D106" t="s">
-        <v>444</v>
-      </c>
       <c r="E106" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F106" t="s">
         <v>16</v>
@@ -6451,24 +6448,24 @@
         <v>20</v>
       </c>
       <c r="K106" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
+        <v>445</v>
+      </c>
+      <c r="B107" t="s">
         <v>446</v>
-      </c>
-      <c r="B107" t="s">
-        <v>447</v>
       </c>
       <c r="C107" t="s">
         <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E107" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F107" t="s">
         <v>16</v>
@@ -6486,24 +6483,24 @@
         <v>20</v>
       </c>
       <c r="K107" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
+        <v>448</v>
+      </c>
+      <c r="B108" t="s">
         <v>449</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
+        <v>110</v>
+      </c>
+      <c r="D108" t="s">
         <v>450</v>
       </c>
-      <c r="C108" t="s">
-        <v>111</v>
-      </c>
-      <c r="D108" t="s">
-        <v>451</v>
-      </c>
       <c r="E108" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F108" t="s">
         <v>16</v>
@@ -6521,24 +6518,24 @@
         <v>20</v>
       </c>
       <c r="K108" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
+        <v>452</v>
+      </c>
+      <c r="B109" t="s">
         <v>453</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
+        <v>110</v>
+      </c>
+      <c r="D109" t="s">
         <v>454</v>
       </c>
-      <c r="C109" t="s">
-        <v>111</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>455</v>
-      </c>
-      <c r="E109" t="s">
-        <v>456</v>
       </c>
       <c r="F109" t="s">
         <v>16</v>
@@ -6556,24 +6553,24 @@
         <v>20</v>
       </c>
       <c r="K109" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>457</v>
+      </c>
+      <c r="B110" t="s">
         <v>458</v>
-      </c>
-      <c r="B110" t="s">
-        <v>459</v>
       </c>
       <c r="C110" t="s">
         <v>13</v>
       </c>
       <c r="D110" t="s">
+        <v>459</v>
+      </c>
+      <c r="E110" t="s">
         <v>460</v>
-      </c>
-      <c r="E110" t="s">
-        <v>461</v>
       </c>
       <c r="F110" t="s">
         <v>16</v>
@@ -6591,24 +6588,24 @@
         <v>25</v>
       </c>
       <c r="K110" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
+        <v>462</v>
+      </c>
+      <c r="B111" t="s">
         <v>463</v>
-      </c>
-      <c r="B111" t="s">
-        <v>464</v>
       </c>
       <c r="C111" t="s">
         <v>13</v>
       </c>
       <c r="D111" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E111" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F111" t="s">
         <v>16</v>
@@ -6626,24 +6623,24 @@
         <v>20</v>
       </c>
       <c r="K111" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
+        <v>466</v>
+      </c>
+      <c r="B112" t="s">
         <v>467</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
+        <v>110</v>
+      </c>
+      <c r="D112" t="s">
         <v>468</v>
       </c>
-      <c r="C112" t="s">
-        <v>111</v>
-      </c>
-      <c r="D112" t="s">
-        <v>469</v>
-      </c>
       <c r="E112" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F112" t="s">
         <v>16</v>
@@ -6661,24 +6658,24 @@
         <v>20</v>
       </c>
       <c r="K112" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
+        <v>470</v>
+      </c>
+      <c r="B113" t="s">
         <v>471</v>
-      </c>
-      <c r="B113" t="s">
-        <v>472</v>
       </c>
       <c r="C113" t="s">
         <v>13</v>
       </c>
       <c r="D113" t="s">
+        <v>472</v>
+      </c>
+      <c r="E113" t="s">
         <v>473</v>
-      </c>
-      <c r="E113" t="s">
-        <v>474</v>
       </c>
       <c r="F113" t="s">
         <v>16</v>
@@ -6696,24 +6693,24 @@
         <v>20</v>
       </c>
       <c r="K113" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>475</v>
+      </c>
+      <c r="B114" t="s">
         <v>476</v>
-      </c>
-      <c r="B114" t="s">
-        <v>477</v>
       </c>
       <c r="C114" t="s">
         <v>13</v>
       </c>
       <c r="D114" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E114" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F114" t="s">
         <v>34</v>
@@ -6722,7 +6719,7 @@
         <v>35</v>
       </c>
       <c r="H114" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I114" t="s">
         <v>19</v>
@@ -6731,24 +6728,24 @@
         <v>25</v>
       </c>
       <c r="K114" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>478</v>
+      </c>
+      <c r="B115" t="s">
         <v>479</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
+        <v>110</v>
+      </c>
+      <c r="D115" t="s">
         <v>480</v>
       </c>
-      <c r="C115" t="s">
-        <v>111</v>
-      </c>
-      <c r="D115" t="s">
-        <v>481</v>
-      </c>
       <c r="E115" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F115" t="s">
         <v>16</v>
@@ -6760,30 +6757,30 @@
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J115" t="s">
         <v>25</v>
       </c>
       <c r="K115" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
+        <v>482</v>
+      </c>
+      <c r="B116" t="s">
         <v>483</v>
-      </c>
-      <c r="B116" t="s">
-        <v>484</v>
       </c>
       <c r="C116" t="s">
         <v>13</v>
       </c>
       <c r="D116" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E116" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F116" t="s">
         <v>16</v>
@@ -6801,21 +6798,21 @@
         <v>20</v>
       </c>
       <c r="K116" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B117" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C117" t="s">
         <v>13</v>
       </c>
       <c r="D117" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E117" t="s">
         <v>41</v>
@@ -6827,7 +6824,7 @@
         <v>35</v>
       </c>
       <c r="H117" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I117" t="s">
         <v>19</v>
@@ -6836,24 +6833,24 @@
         <v>25</v>
       </c>
       <c r="K117" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
+        <v>489</v>
+      </c>
+      <c r="B118" t="s">
+        <v>479</v>
+      </c>
+      <c r="C118" t="s">
+        <v>110</v>
+      </c>
+      <c r="D118" t="s">
         <v>490</v>
       </c>
-      <c r="B118" t="s">
-        <v>480</v>
-      </c>
-      <c r="C118" t="s">
-        <v>111</v>
-      </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
         <v>491</v>
-      </c>
-      <c r="E118" t="s">
-        <v>492</v>
       </c>
       <c r="F118" t="s">
         <v>34</v>
@@ -6871,24 +6868,24 @@
         <v>20</v>
       </c>
       <c r="K118" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>493</v>
+      </c>
+      <c r="B119" t="s">
         <v>494</v>
-      </c>
-      <c r="B119" t="s">
-        <v>495</v>
       </c>
       <c r="C119" t="s">
         <v>13</v>
       </c>
       <c r="D119" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F119" t="s">
         <v>16</v>
@@ -6906,24 +6903,24 @@
         <v>25</v>
       </c>
       <c r="K119" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
+        <v>496</v>
+      </c>
+      <c r="B120" t="s">
         <v>497</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
+        <v>110</v>
+      </c>
+      <c r="D120" t="s">
         <v>498</v>
       </c>
-      <c r="C120" t="s">
-        <v>111</v>
-      </c>
-      <c r="D120" t="s">
-        <v>499</v>
-      </c>
       <c r="E120" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F120" t="s">
         <v>16</v>
@@ -6941,24 +6938,24 @@
         <v>25</v>
       </c>
       <c r="K120" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
+        <v>499</v>
+      </c>
+      <c r="B121" t="s">
         <v>500</v>
-      </c>
-      <c r="B121" t="s">
-        <v>501</v>
       </c>
       <c r="C121" t="s">
         <v>13</v>
       </c>
       <c r="D121" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E121" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F121" t="s">
         <v>16</v>
@@ -6976,24 +6973,24 @@
         <v>25</v>
       </c>
       <c r="K121" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B122" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C122" t="s">
         <v>13</v>
       </c>
       <c r="D122" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E122" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F122" t="s">
         <v>16</v>
@@ -7011,24 +7008,24 @@
         <v>20</v>
       </c>
       <c r="K122" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>503</v>
+      </c>
+      <c r="B123" t="s">
         <v>504</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
+        <v>110</v>
+      </c>
+      <c r="D123" t="s">
         <v>505</v>
       </c>
-      <c r="C123" t="s">
-        <v>111</v>
-      </c>
-      <c r="D123" t="s">
-        <v>506</v>
-      </c>
       <c r="E123" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F123" t="s">
         <v>16</v>
@@ -7040,30 +7037,30 @@
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J123" t="s">
         <v>25</v>
       </c>
       <c r="K123" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>507</v>
+      </c>
+      <c r="B124" t="s">
         <v>508</v>
-      </c>
-      <c r="B124" t="s">
-        <v>509</v>
       </c>
       <c r="C124" t="s">
         <v>13</v>
       </c>
       <c r="D124" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E124" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F124" t="s">
         <v>34</v>
@@ -7081,24 +7078,24 @@
         <v>20</v>
       </c>
       <c r="K124" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
+        <v>511</v>
+      </c>
+      <c r="B125" t="s">
         <v>512</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
+        <v>110</v>
+      </c>
+      <c r="D125" t="s">
         <v>513</v>
       </c>
-      <c r="C125" t="s">
-        <v>111</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>514</v>
-      </c>
-      <c r="E125" t="s">
-        <v>515</v>
       </c>
       <c r="F125" t="s">
         <v>16</v>
@@ -7116,24 +7113,24 @@
         <v>25</v>
       </c>
       <c r="K125" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
+        <v>516</v>
+      </c>
+      <c r="B126" t="s">
         <v>517</v>
       </c>
-      <c r="B126" t="s">
-        <v>518</v>
-      </c>
       <c r="C126" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D126" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E126" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F126" t="s">
         <v>16</v>
@@ -7151,24 +7148,24 @@
         <v>20</v>
       </c>
       <c r="K126" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
+        <v>519</v>
+      </c>
+      <c r="B127" t="s">
         <v>520</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
+        <v>110</v>
+      </c>
+      <c r="D127" t="s">
         <v>521</v>
       </c>
-      <c r="C127" t="s">
-        <v>111</v>
-      </c>
-      <c r="D127" t="s">
-        <v>522</v>
-      </c>
       <c r="E127" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F127" t="s">
         <v>16</v>
@@ -7186,56 +7183,56 @@
         <v>25</v>
       </c>
       <c r="K127" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>523</v>
+      </c>
+      <c r="B128" t="s">
         <v>524</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
+        <v>110</v>
+      </c>
+      <c r="D128" t="s">
         <v>525</v>
       </c>
-      <c r="C128" t="s">
-        <v>111</v>
-      </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
+        <v>491</v>
+      </c>
+      <c r="F128" t="s">
+        <v>16</v>
+      </c>
+      <c r="G128" t="s">
+        <v>17</v>
+      </c>
+      <c r="H128" t="s">
+        <v>173</v>
+      </c>
+      <c r="I128" t="s">
+        <v>19</v>
+      </c>
+      <c r="J128" t="s">
+        <v>25</v>
+      </c>
+      <c r="K128" t="s">
         <v>526</v>
-      </c>
-      <c r="E128" t="s">
-        <v>492</v>
-      </c>
-      <c r="F128" t="s">
-        <v>16</v>
-      </c>
-      <c r="G128" t="s">
-        <v>17</v>
-      </c>
-      <c r="H128" t="s">
-        <v>174</v>
-      </c>
-      <c r="I128" t="s">
-        <v>19</v>
-      </c>
-      <c r="J128" t="s">
-        <v>25</v>
-      </c>
-      <c r="K128" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
+        <v>527</v>
+      </c>
+      <c r="B129" t="s">
         <v>528</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
+        <v>110</v>
+      </c>
+      <c r="D129" t="s">
         <v>529</v>
-      </c>
-      <c r="C129" t="s">
-        <v>111</v>
-      </c>
-      <c r="D129" t="s">
-        <v>530</v>
       </c>
       <c r="E129" t="s">
         <v>41</v>
@@ -7256,21 +7253,21 @@
         <v>20</v>
       </c>
       <c r="K129" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>531</v>
+      </c>
+      <c r="B130" t="s">
+        <v>528</v>
+      </c>
+      <c r="C130" t="s">
+        <v>110</v>
+      </c>
+      <c r="D130" t="s">
         <v>532</v>
-      </c>
-      <c r="B130" t="s">
-        <v>529</v>
-      </c>
-      <c r="C130" t="s">
-        <v>111</v>
-      </c>
-      <c r="D130" t="s">
-        <v>533</v>
       </c>
       <c r="E130" t="s">
         <v>41</v>
@@ -7291,56 +7288,56 @@
         <v>25</v>
       </c>
       <c r="K130" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
+        <v>533</v>
+      </c>
+      <c r="B131" t="s">
         <v>534</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
+        <v>110</v>
+      </c>
+      <c r="D131" t="s">
         <v>535</v>
       </c>
-      <c r="C131" t="s">
-        <v>111</v>
-      </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
+        <v>157</v>
+      </c>
+      <c r="F131" t="s">
+        <v>16</v>
+      </c>
+      <c r="G131" t="s">
+        <v>17</v>
+      </c>
+      <c r="H131" t="s">
+        <v>173</v>
+      </c>
+      <c r="I131" t="s">
+        <v>19</v>
+      </c>
+      <c r="J131" t="s">
+        <v>25</v>
+      </c>
+      <c r="K131" t="s">
         <v>536</v>
-      </c>
-      <c r="E131" t="s">
-        <v>158</v>
-      </c>
-      <c r="F131" t="s">
-        <v>16</v>
-      </c>
-      <c r="G131" t="s">
-        <v>17</v>
-      </c>
-      <c r="H131" t="s">
-        <v>174</v>
-      </c>
-      <c r="I131" t="s">
-        <v>19</v>
-      </c>
-      <c r="J131" t="s">
-        <v>25</v>
-      </c>
-      <c r="K131" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
+        <v>537</v>
+      </c>
+      <c r="B132" t="s">
         <v>538</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
+        <v>110</v>
+      </c>
+      <c r="D132" t="s">
         <v>539</v>
-      </c>
-      <c r="C132" t="s">
-        <v>111</v>
-      </c>
-      <c r="D132" t="s">
-        <v>540</v>
       </c>
       <c r="E132" t="s">
         <v>47</v>
@@ -7361,24 +7358,24 @@
         <v>25</v>
       </c>
       <c r="K132" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
+        <v>541</v>
+      </c>
+      <c r="B133" t="s">
         <v>542</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
+        <v>110</v>
+      </c>
+      <c r="D133" t="s">
         <v>543</v>
       </c>
-      <c r="C133" t="s">
-        <v>111</v>
-      </c>
-      <c r="D133" t="s">
-        <v>544</v>
-      </c>
       <c r="E133" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F133" t="s">
         <v>16</v>
@@ -7396,24 +7393,24 @@
         <v>25</v>
       </c>
       <c r="K133" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
+        <v>545</v>
+      </c>
+      <c r="B134" t="s">
         <v>546</v>
-      </c>
-      <c r="B134" t="s">
-        <v>547</v>
       </c>
       <c r="C134" t="s">
         <v>13</v>
       </c>
       <c r="D134" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E134" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F134" t="s">
         <v>16</v>
@@ -7431,24 +7428,24 @@
         <v>25</v>
       </c>
       <c r="K134" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
+        <v>549</v>
+      </c>
+      <c r="B135" t="s">
         <v>550</v>
-      </c>
-      <c r="B135" t="s">
-        <v>551</v>
       </c>
       <c r="C135" t="s">
         <v>13</v>
       </c>
       <c r="D135" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E135" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F135" t="s">
         <v>16</v>
@@ -7466,24 +7463,24 @@
         <v>20</v>
       </c>
       <c r="K135" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
+        <v>553</v>
+      </c>
+      <c r="B136" t="s">
         <v>554</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
+        <v>110</v>
+      </c>
+      <c r="D136" t="s">
         <v>555</v>
       </c>
-      <c r="C136" t="s">
-        <v>111</v>
-      </c>
-      <c r="D136" t="s">
-        <v>556</v>
-      </c>
       <c r="E136" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F136" t="s">
         <v>16</v>
@@ -7501,24 +7498,24 @@
         <v>25</v>
       </c>
       <c r="K136" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
+        <v>557</v>
+      </c>
+      <c r="B137" t="s">
         <v>558</v>
-      </c>
-      <c r="B137" t="s">
-        <v>559</v>
       </c>
       <c r="C137" t="s">
         <v>13</v>
       </c>
       <c r="D137" t="s">
+        <v>559</v>
+      </c>
+      <c r="E137" t="s">
         <v>560</v>
-      </c>
-      <c r="E137" t="s">
-        <v>561</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
@@ -7536,24 +7533,24 @@
         <v>20</v>
       </c>
       <c r="K137" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
+        <v>562</v>
+      </c>
+      <c r="B138" t="s">
         <v>563</v>
       </c>
-      <c r="B138" t="s">
-        <v>564</v>
-      </c>
       <c r="C138" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D138" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F138" t="s">
         <v>34</v>
@@ -7565,30 +7562,30 @@
         <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J138" t="s">
         <v>25</v>
       </c>
       <c r="K138" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
+        <v>565</v>
+      </c>
+      <c r="B139" t="s">
         <v>566</v>
       </c>
-      <c r="B139" t="s">
-        <v>567</v>
-      </c>
       <c r="C139" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D139" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E139" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F139" t="s">
         <v>16</v>
@@ -7606,24 +7603,24 @@
         <v>25</v>
       </c>
       <c r="K139" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
+        <v>568</v>
+      </c>
+      <c r="B140" t="s">
         <v>569</v>
-      </c>
-      <c r="B140" t="s">
-        <v>570</v>
       </c>
       <c r="C140" t="s">
         <v>13</v>
       </c>
       <c r="D140" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E140" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F140" t="s">
         <v>16</v>
@@ -7641,24 +7638,24 @@
         <v>25</v>
       </c>
       <c r="K140" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
+        <v>572</v>
+      </c>
+      <c r="B141" t="s">
         <v>573</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
+        <v>110</v>
+      </c>
+      <c r="D141" t="s">
         <v>574</v>
       </c>
-      <c r="C141" t="s">
-        <v>111</v>
-      </c>
-      <c r="D141" t="s">
-        <v>575</v>
-      </c>
       <c r="E141" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F141" t="s">
         <v>16</v>
@@ -7676,24 +7673,24 @@
         <v>25</v>
       </c>
       <c r="K141" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B142" t="s">
+        <v>573</v>
+      </c>
+      <c r="C142" t="s">
+        <v>110</v>
+      </c>
+      <c r="D142" t="s">
         <v>574</v>
       </c>
-      <c r="C142" t="s">
-        <v>111</v>
-      </c>
-      <c r="D142" t="s">
-        <v>575</v>
-      </c>
       <c r="E142" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F142" t="s">
         <v>16</v>
@@ -7711,24 +7708,24 @@
         <v>20</v>
       </c>
       <c r="K142" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
+        <v>578</v>
+      </c>
+      <c r="B143" t="s">
         <v>579</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
+        <v>110</v>
+      </c>
+      <c r="D143" t="s">
         <v>580</v>
       </c>
-      <c r="C143" t="s">
-        <v>111</v>
-      </c>
-      <c r="D143" t="s">
-        <v>581</v>
-      </c>
       <c r="E143" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F143" t="s">
         <v>16</v>
@@ -7746,24 +7743,24 @@
         <v>20</v>
       </c>
       <c r="K143" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
+        <v>582</v>
+      </c>
+      <c r="B144" t="s">
         <v>583</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
+        <v>110</v>
+      </c>
+      <c r="D144" t="s">
         <v>584</v>
       </c>
-      <c r="C144" t="s">
-        <v>111</v>
-      </c>
-      <c r="D144" t="s">
-        <v>585</v>
-      </c>
       <c r="E144" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F144" t="s">
         <v>16</v>
@@ -7781,24 +7778,24 @@
         <v>20</v>
       </c>
       <c r="K144" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
+        <v>586</v>
+      </c>
+      <c r="B145" t="s">
         <v>587</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" t="s">
+        <v>110</v>
+      </c>
+      <c r="D145" t="s">
         <v>588</v>
       </c>
-      <c r="C145" t="s">
-        <v>111</v>
-      </c>
-      <c r="D145" t="s">
-        <v>589</v>
-      </c>
       <c r="E145" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -7816,24 +7813,24 @@
         <v>20</v>
       </c>
       <c r="K145" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
+        <v>590</v>
+      </c>
+      <c r="B146" t="s">
         <v>591</v>
-      </c>
-      <c r="B146" t="s">
-        <v>592</v>
       </c>
       <c r="C146" t="s">
         <v>13</v>
       </c>
       <c r="D146" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E146" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F146" t="s">
         <v>34</v>
@@ -7851,21 +7848,21 @@
         <v>25</v>
       </c>
       <c r="K146" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
+        <v>594</v>
+      </c>
+      <c r="B147" t="s">
         <v>595</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" t="s">
+        <v>110</v>
+      </c>
+      <c r="D147" t="s">
         <v>596</v>
-      </c>
-      <c r="C147" t="s">
-        <v>111</v>
-      </c>
-      <c r="D147" t="s">
-        <v>597</v>
       </c>
       <c r="E147" t="s">
         <v>29</v>
@@ -7886,24 +7883,24 @@
         <v>25</v>
       </c>
       <c r="K147" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
+        <v>598</v>
+      </c>
+      <c r="B148" t="s">
         <v>599</v>
-      </c>
-      <c r="B148" t="s">
-        <v>600</v>
       </c>
       <c r="C148" t="s">
         <v>13</v>
       </c>
       <c r="D148" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E148" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F148" t="s">
         <v>34</v>
@@ -7912,7 +7909,7 @@
         <v>35</v>
       </c>
       <c r="H148" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I148" t="s">
         <v>19</v>
@@ -7921,24 +7918,24 @@
         <v>20</v>
       </c>
       <c r="K148" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
+        <v>602</v>
+      </c>
+      <c r="B149" t="s">
         <v>603</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
+        <v>110</v>
+      </c>
+      <c r="D149" t="s">
         <v>604</v>
       </c>
-      <c r="C149" t="s">
-        <v>111</v>
-      </c>
-      <c r="D149" t="s">
-        <v>605</v>
-      </c>
       <c r="E149" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F149" t="s">
         <v>16</v>
@@ -7956,24 +7953,24 @@
         <v>25</v>
       </c>
       <c r="K149" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
+        <v>606</v>
+      </c>
+      <c r="B150" t="s">
         <v>607</v>
-      </c>
-      <c r="B150" t="s">
-        <v>608</v>
       </c>
       <c r="C150" t="s">
         <v>13</v>
       </c>
       <c r="D150" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E150" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F150" t="s">
         <v>16</v>
@@ -7991,24 +7988,24 @@
         <v>20</v>
       </c>
       <c r="K150" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
+        <v>610</v>
+      </c>
+      <c r="B151" t="s">
         <v>611</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C151" t="s">
+        <v>110</v>
+      </c>
+      <c r="D151" t="s">
         <v>612</v>
       </c>
-      <c r="C151" t="s">
-        <v>111</v>
-      </c>
-      <c r="D151" t="s">
-        <v>613</v>
-      </c>
       <c r="E151" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F151" t="s">
         <v>16</v>
@@ -8026,24 +8023,24 @@
         <v>20</v>
       </c>
       <c r="K151" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
+        <v>614</v>
+      </c>
+      <c r="B152" t="s">
         <v>615</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
+        <v>110</v>
+      </c>
+      <c r="D152" t="s">
         <v>616</v>
       </c>
-      <c r="C152" t="s">
-        <v>111</v>
-      </c>
-      <c r="D152" t="s">
-        <v>617</v>
-      </c>
       <c r="E152" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F152" t="s">
         <v>16</v>
@@ -8061,21 +8058,21 @@
         <v>20</v>
       </c>
       <c r="K152" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
+        <v>618</v>
+      </c>
+      <c r="B153" t="s">
         <v>619</v>
-      </c>
-      <c r="B153" t="s">
-        <v>620</v>
       </c>
       <c r="C153" t="s">
         <v>13</v>
       </c>
       <c r="D153" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E153" t="s">
         <v>47</v>
@@ -8096,24 +8093,24 @@
         <v>20</v>
       </c>
       <c r="K153" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
+        <v>622</v>
+      </c>
+      <c r="B154" t="s">
         <v>623</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" t="s">
+        <v>110</v>
+      </c>
+      <c r="D154" t="s">
+        <v>14</v>
+      </c>
+      <c r="E154" t="s">
         <v>624</v>
-      </c>
-      <c r="C154" t="s">
-        <v>111</v>
-      </c>
-      <c r="D154" t="s">
-        <v>65</v>
-      </c>
-      <c r="E154" t="s">
-        <v>625</v>
       </c>
       <c r="F154" t="s">
         <v>16</v>
@@ -8131,24 +8128,24 @@
         <v>25</v>
       </c>
       <c r="K154" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
+        <v>626</v>
+      </c>
+      <c r="B155" t="s">
         <v>627</v>
-      </c>
-      <c r="B155" t="s">
-        <v>628</v>
       </c>
       <c r="C155" t="s">
         <v>13</v>
       </c>
       <c r="D155" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E155" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -8166,24 +8163,24 @@
         <v>20</v>
       </c>
       <c r="K155" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
+        <v>630</v>
+      </c>
+      <c r="B156" t="s">
         <v>631</v>
-      </c>
-      <c r="B156" t="s">
-        <v>632</v>
       </c>
       <c r="C156" t="s">
         <v>13</v>
       </c>
       <c r="D156" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E156" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F156" t="s">
         <v>34</v>
@@ -8201,24 +8198,24 @@
         <v>20</v>
       </c>
       <c r="K156" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
+        <v>634</v>
+      </c>
+      <c r="B157" t="s">
         <v>635</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
+        <v>110</v>
+      </c>
+      <c r="D157" t="s">
         <v>636</v>
       </c>
-      <c r="C157" t="s">
-        <v>111</v>
-      </c>
-      <c r="D157" t="s">
-        <v>637</v>
-      </c>
       <c r="E157" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F157" t="s">
         <v>16</v>
@@ -8236,59 +8233,59 @@
         <v>25</v>
       </c>
       <c r="K157" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
+        <v>638</v>
+      </c>
+      <c r="B158" t="s">
         <v>639</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
+        <v>110</v>
+      </c>
+      <c r="D158" t="s">
         <v>640</v>
       </c>
-      <c r="C158" t="s">
-        <v>111</v>
-      </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
+        <v>411</v>
+      </c>
+      <c r="F158" t="s">
+        <v>16</v>
+      </c>
+      <c r="G158" t="s">
+        <v>17</v>
+      </c>
+      <c r="H158" t="s">
+        <v>140</v>
+      </c>
+      <c r="I158" t="s">
+        <v>19</v>
+      </c>
+      <c r="J158" t="s">
+        <v>25</v>
+      </c>
+      <c r="K158" t="s">
         <v>641</v>
-      </c>
-      <c r="E158" t="s">
-        <v>412</v>
-      </c>
-      <c r="F158" t="s">
-        <v>16</v>
-      </c>
-      <c r="G158" t="s">
-        <v>17</v>
-      </c>
-      <c r="H158" t="s">
-        <v>141</v>
-      </c>
-      <c r="I158" t="s">
-        <v>19</v>
-      </c>
-      <c r="J158" t="s">
-        <v>25</v>
-      </c>
-      <c r="K158" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
+        <v>642</v>
+      </c>
+      <c r="B159" t="s">
         <v>643</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
+        <v>110</v>
+      </c>
+      <c r="D159" t="s">
         <v>644</v>
       </c>
-      <c r="C159" t="s">
-        <v>111</v>
-      </c>
-      <c r="D159" t="s">
-        <v>645</v>
-      </c>
       <c r="E159" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F159" t="s">
         <v>16</v>
@@ -8297,7 +8294,7 @@
         <v>35</v>
       </c>
       <c r="H159" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I159" t="s">
         <v>19</v>
@@ -8306,24 +8303,24 @@
         <v>25</v>
       </c>
       <c r="K159" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
+        <v>646</v>
+      </c>
+      <c r="B160" t="s">
         <v>647</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C160" t="s">
+        <v>110</v>
+      </c>
+      <c r="D160" t="s">
         <v>648</v>
       </c>
-      <c r="C160" t="s">
-        <v>111</v>
-      </c>
-      <c r="D160" t="s">
-        <v>649</v>
-      </c>
       <c r="E160" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F160" t="s">
         <v>34</v>
@@ -8332,33 +8329,33 @@
         <v>17</v>
       </c>
       <c r="H160" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I160" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J160" t="s">
         <v>25</v>
       </c>
       <c r="K160" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
+        <v>650</v>
+      </c>
+      <c r="B161" t="s">
         <v>651</v>
-      </c>
-      <c r="B161" t="s">
-        <v>652</v>
       </c>
       <c r="C161" t="s">
         <v>13</v>
       </c>
       <c r="D161" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E161" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F161" t="s">
         <v>16</v>
@@ -8376,24 +8373,24 @@
         <v>20</v>
       </c>
       <c r="K161" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
+        <v>654</v>
+      </c>
+      <c r="B162" t="s">
         <v>655</v>
-      </c>
-      <c r="B162" t="s">
-        <v>656</v>
       </c>
       <c r="C162" t="s">
         <v>13</v>
       </c>
       <c r="D162" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E162" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F162" t="s">
         <v>34</v>
@@ -8411,24 +8408,24 @@
         <v>20</v>
       </c>
       <c r="K162" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
+        <v>658</v>
+      </c>
+      <c r="B163" t="s">
         <v>659</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C163" t="s">
+        <v>110</v>
+      </c>
+      <c r="D163" t="s">
         <v>660</v>
       </c>
-      <c r="C163" t="s">
-        <v>111</v>
-      </c>
-      <c r="D163" t="s">
-        <v>661</v>
-      </c>
       <c r="E163" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F163" t="s">
         <v>16</v>
@@ -8446,24 +8443,24 @@
         <v>25</v>
       </c>
       <c r="K163" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
+        <v>662</v>
+      </c>
+      <c r="B164" t="s">
         <v>663</v>
-      </c>
-      <c r="B164" t="s">
-        <v>664</v>
       </c>
       <c r="C164" t="s">
         <v>13</v>
       </c>
       <c r="D164" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E164" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F164" t="s">
         <v>16</v>
@@ -8481,24 +8478,24 @@
         <v>25</v>
       </c>
       <c r="K164" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
+        <v>666</v>
+      </c>
+      <c r="B165" t="s">
         <v>667</v>
       </c>
-      <c r="B165" t="s">
-        <v>668</v>
-      </c>
       <c r="C165" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D165" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E165" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F165" t="s">
         <v>34</v>
@@ -8516,24 +8513,24 @@
         <v>25</v>
       </c>
       <c r="K165" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
+        <v>669</v>
+      </c>
+      <c r="B166" t="s">
         <v>670</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
+        <v>110</v>
+      </c>
+      <c r="D166" t="s">
         <v>671</v>
       </c>
-      <c r="C166" t="s">
-        <v>111</v>
-      </c>
-      <c r="D166" t="s">
-        <v>672</v>
-      </c>
       <c r="E166" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F166" t="s">
         <v>16</v>
@@ -8551,24 +8548,24 @@
         <v>20</v>
       </c>
       <c r="K166" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
+        <v>672</v>
+      </c>
+      <c r="B167" t="s">
         <v>673</v>
       </c>
-      <c r="B167" t="s">
+      <c r="C167" t="s">
+        <v>110</v>
+      </c>
+      <c r="D167" t="s">
         <v>674</v>
       </c>
-      <c r="C167" t="s">
-        <v>111</v>
-      </c>
-      <c r="D167" t="s">
-        <v>675</v>
-      </c>
       <c r="E167" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F167" t="s">
         <v>16</v>
@@ -8577,7 +8574,7 @@
         <v>35</v>
       </c>
       <c r="H167" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I167" t="s">
         <v>19</v>
@@ -8586,24 +8583,24 @@
         <v>20</v>
       </c>
       <c r="K167" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
+        <v>676</v>
+      </c>
+      <c r="B168" t="s">
         <v>677</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C168" t="s">
+        <v>110</v>
+      </c>
+      <c r="D168" t="s">
         <v>678</v>
       </c>
-      <c r="C168" t="s">
-        <v>111</v>
-      </c>
-      <c r="D168" t="s">
-        <v>679</v>
-      </c>
       <c r="E168" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F168" t="s">
         <v>16</v>
@@ -8621,24 +8618,24 @@
         <v>25</v>
       </c>
       <c r="K168" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
+        <v>680</v>
+      </c>
+      <c r="B169" t="s">
         <v>681</v>
-      </c>
-      <c r="B169" t="s">
-        <v>682</v>
       </c>
       <c r="C169" t="s">
         <v>13</v>
       </c>
       <c r="D169" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E169" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F169" t="s">
         <v>16</v>
@@ -8656,24 +8653,24 @@
         <v>25</v>
       </c>
       <c r="K169" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
+        <v>684</v>
+      </c>
+      <c r="B170" t="s">
         <v>685</v>
-      </c>
-      <c r="B170" t="s">
-        <v>686</v>
       </c>
       <c r="C170" t="s">
         <v>13</v>
       </c>
       <c r="D170" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E170" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F170" t="s">
         <v>16</v>
@@ -8691,21 +8688,21 @@
         <v>25</v>
       </c>
       <c r="K170" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
+        <v>688</v>
+      </c>
+      <c r="B171" t="s">
         <v>689</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C171" t="s">
+        <v>110</v>
+      </c>
+      <c r="D171" t="s">
         <v>690</v>
-      </c>
-      <c r="C171" t="s">
-        <v>111</v>
-      </c>
-      <c r="D171" t="s">
-        <v>691</v>
       </c>
       <c r="E171" t="s">
         <v>15</v>
@@ -8726,24 +8723,24 @@
         <v>20</v>
       </c>
       <c r="K171" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
+        <v>692</v>
+      </c>
+      <c r="B172" t="s">
         <v>693</v>
-      </c>
-      <c r="B172" t="s">
-        <v>694</v>
       </c>
       <c r="C172" t="s">
         <v>13</v>
       </c>
       <c r="D172" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E172" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F172" t="s">
         <v>16</v>
@@ -8761,24 +8758,24 @@
         <v>25</v>
       </c>
       <c r="K172" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
+        <v>696</v>
+      </c>
+      <c r="B173" t="s">
         <v>697</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C173" t="s">
+        <v>110</v>
+      </c>
+      <c r="D173" t="s">
         <v>698</v>
       </c>
-      <c r="C173" t="s">
-        <v>111</v>
-      </c>
-      <c r="D173" t="s">
-        <v>699</v>
-      </c>
       <c r="E173" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F173" t="s">
         <v>16</v>
@@ -8796,24 +8793,24 @@
         <v>25</v>
       </c>
       <c r="K173" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
+        <v>700</v>
+      </c>
+      <c r="B174" t="s">
         <v>701</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
+        <v>110</v>
+      </c>
+      <c r="D174" t="s">
         <v>702</v>
       </c>
-      <c r="C174" t="s">
-        <v>111</v>
-      </c>
-      <c r="D174" t="s">
-        <v>703</v>
-      </c>
       <c r="E174" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F174" t="s">
         <v>16</v>
@@ -8831,24 +8828,24 @@
         <v>20</v>
       </c>
       <c r="K174" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
+        <v>704</v>
+      </c>
+      <c r="B175" t="s">
         <v>705</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
+        <v>110</v>
+      </c>
+      <c r="D175" t="s">
         <v>706</v>
       </c>
-      <c r="C175" t="s">
-        <v>111</v>
-      </c>
-      <c r="D175" t="s">
-        <v>707</v>
-      </c>
       <c r="E175" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -8866,24 +8863,24 @@
         <v>20</v>
       </c>
       <c r="K175" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
+        <v>708</v>
+      </c>
+      <c r="B176" t="s">
         <v>709</v>
       </c>
-      <c r="B176" t="s">
-        <v>710</v>
-      </c>
       <c r="C176" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D176" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E176" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F176" t="s">
         <v>16</v>
@@ -8895,27 +8892,27 @@
         <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J176" t="s">
         <v>20</v>
       </c>
       <c r="K176" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
+        <v>711</v>
+      </c>
+      <c r="B177" t="s">
         <v>712</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C177" t="s">
+        <v>110</v>
+      </c>
+      <c r="D177" t="s">
         <v>713</v>
-      </c>
-      <c r="C177" t="s">
-        <v>111</v>
-      </c>
-      <c r="D177" t="s">
-        <v>714</v>
       </c>
       <c r="E177" t="s">
         <v>29</v>
@@ -8936,24 +8933,24 @@
         <v>25</v>
       </c>
       <c r="K177" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
+        <v>715</v>
+      </c>
+      <c r="B178" t="s">
+        <v>587</v>
+      </c>
+      <c r="C178" t="s">
+        <v>110</v>
+      </c>
+      <c r="D178" t="s">
         <v>716</v>
       </c>
-      <c r="B178" t="s">
-        <v>588</v>
-      </c>
-      <c r="C178" t="s">
-        <v>111</v>
-      </c>
-      <c r="D178" t="s">
-        <v>717</v>
-      </c>
       <c r="E178" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F178" t="s">
         <v>34</v>
@@ -8971,24 +8968,24 @@
         <v>25</v>
       </c>
       <c r="K178" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
+        <v>718</v>
+      </c>
+      <c r="B179" t="s">
         <v>719</v>
-      </c>
-      <c r="B179" t="s">
-        <v>720</v>
       </c>
       <c r="C179" t="s">
         <v>13</v>
       </c>
       <c r="D179" t="s">
+        <v>14</v>
+      </c>
+      <c r="E179" t="s">
         <v>65</v>
-      </c>
-      <c r="E179" t="s">
-        <v>66</v>
       </c>
       <c r="F179" t="s">
         <v>34</v>
@@ -9006,24 +9003,24 @@
         <v>25</v>
       </c>
       <c r="K179" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
+        <v>721</v>
+      </c>
+      <c r="B180" t="s">
         <v>722</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
+        <v>110</v>
+      </c>
+      <c r="D180" t="s">
         <v>723</v>
       </c>
-      <c r="C180" t="s">
-        <v>111</v>
-      </c>
-      <c r="D180" t="s">
-        <v>724</v>
-      </c>
       <c r="E180" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -9035,30 +9032,30 @@
         <v>18</v>
       </c>
       <c r="I180" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J180" t="s">
         <v>20</v>
       </c>
       <c r="K180" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B181" t="s">
+        <v>725</v>
+      </c>
+      <c r="C181" t="s">
+        <v>110</v>
+      </c>
+      <c r="D181" t="s">
         <v>726</v>
       </c>
-      <c r="C181" t="s">
-        <v>111</v>
-      </c>
-      <c r="D181" t="s">
-        <v>727</v>
-      </c>
       <c r="E181" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F181" t="s">
         <v>34</v>
@@ -9076,24 +9073,24 @@
         <v>25</v>
       </c>
       <c r="K181" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
+        <v>728</v>
+      </c>
+      <c r="B182" t="s">
         <v>729</v>
-      </c>
-      <c r="B182" t="s">
-        <v>730</v>
       </c>
       <c r="C182" t="s">
         <v>13</v>
       </c>
       <c r="D182" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E182" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F182" t="s">
         <v>34</v>
@@ -9111,24 +9108,24 @@
         <v>25</v>
       </c>
       <c r="K182" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B183" t="s">
+        <v>732</v>
+      </c>
+      <c r="C183" t="s">
+        <v>110</v>
+      </c>
+      <c r="D183" t="s">
         <v>733</v>
       </c>
-      <c r="C183" t="s">
-        <v>111</v>
-      </c>
-      <c r="D183" t="s">
-        <v>734</v>
-      </c>
       <c r="E183" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F183" t="s">
         <v>16</v>
@@ -9146,21 +9143,21 @@
         <v>20</v>
       </c>
       <c r="K183" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
+        <v>735</v>
+      </c>
+      <c r="B184" t="s">
         <v>736</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
+        <v>110</v>
+      </c>
+      <c r="D184" t="s">
         <v>737</v>
-      </c>
-      <c r="C184" t="s">
-        <v>111</v>
-      </c>
-      <c r="D184" t="s">
-        <v>738</v>
       </c>
       <c r="E184" t="s">
         <v>29</v>
@@ -9172,7 +9169,7 @@
         <v>17</v>
       </c>
       <c r="H184" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I184" t="s">
         <v>19</v>
@@ -9181,24 +9178,24 @@
         <v>20</v>
       </c>
       <c r="K184" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
+        <v>739</v>
+      </c>
+      <c r="B185" t="s">
         <v>740</v>
-      </c>
-      <c r="B185" t="s">
-        <v>741</v>
       </c>
       <c r="C185" t="s">
         <v>13</v>
       </c>
       <c r="D185" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E185" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F185" t="s">
         <v>16</v>
@@ -9210,27 +9207,27 @@
         <v>36</v>
       </c>
       <c r="I185" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J185" t="s">
         <v>25</v>
       </c>
       <c r="K185" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
+        <v>743</v>
+      </c>
+      <c r="B186" t="s">
         <v>744</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
+        <v>110</v>
+      </c>
+      <c r="D186" t="s">
         <v>745</v>
-      </c>
-      <c r="C186" t="s">
-        <v>111</v>
-      </c>
-      <c r="D186" t="s">
-        <v>746</v>
       </c>
       <c r="E186" t="s">
         <v>61</v>
@@ -9251,24 +9248,24 @@
         <v>25</v>
       </c>
       <c r="K186" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
+        <v>747</v>
+      </c>
+      <c r="B187" t="s">
         <v>748</v>
       </c>
-      <c r="B187" t="s">
+      <c r="C187" t="s">
+        <v>110</v>
+      </c>
+      <c r="D187" t="s">
         <v>749</v>
       </c>
-      <c r="C187" t="s">
-        <v>111</v>
-      </c>
-      <c r="D187" t="s">
-        <v>750</v>
-      </c>
       <c r="E187" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F187" t="s">
         <v>16</v>
@@ -9286,24 +9283,24 @@
         <v>25</v>
       </c>
       <c r="K187" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
+        <v>751</v>
+      </c>
+      <c r="B188" t="s">
         <v>752</v>
-      </c>
-      <c r="B188" t="s">
-        <v>753</v>
       </c>
       <c r="C188" t="s">
         <v>13</v>
       </c>
       <c r="D188" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E188" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -9321,24 +9318,24 @@
         <v>20</v>
       </c>
       <c r="K188" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
+        <v>755</v>
+      </c>
+      <c r="B189" t="s">
         <v>756</v>
-      </c>
-      <c r="B189" t="s">
-        <v>757</v>
       </c>
       <c r="C189" t="s">
         <v>13</v>
       </c>
       <c r="D189" t="s">
+        <v>757</v>
+      </c>
+      <c r="E189" t="s">
         <v>758</v>
-      </c>
-      <c r="E189" t="s">
-        <v>759</v>
       </c>
       <c r="F189" t="s">
         <v>16</v>
@@ -9356,24 +9353,24 @@
         <v>20</v>
       </c>
       <c r="K189" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
+        <v>760</v>
+      </c>
+      <c r="B190" t="s">
+        <v>566</v>
+      </c>
+      <c r="C190" t="s">
+        <v>110</v>
+      </c>
+      <c r="D190" t="s">
         <v>761</v>
       </c>
-      <c r="B190" t="s">
-        <v>567</v>
-      </c>
-      <c r="C190" t="s">
-        <v>111</v>
-      </c>
-      <c r="D190" t="s">
-        <v>762</v>
-      </c>
       <c r="E190" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F190" t="s">
         <v>34</v>
@@ -9391,24 +9388,24 @@
         <v>20</v>
       </c>
       <c r="K190" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
+        <v>763</v>
+      </c>
+      <c r="B191" t="s">
         <v>764</v>
-      </c>
-      <c r="B191" t="s">
-        <v>765</v>
       </c>
       <c r="C191" t="s">
         <v>13</v>
       </c>
       <c r="D191" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E191" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F191" t="s">
         <v>16</v>
@@ -9426,24 +9423,24 @@
         <v>25</v>
       </c>
       <c r="K191" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
+        <v>767</v>
+      </c>
+      <c r="B192" t="s">
         <v>768</v>
-      </c>
-      <c r="B192" t="s">
-        <v>769</v>
       </c>
       <c r="C192" t="s">
         <v>13</v>
       </c>
       <c r="D192" t="s">
+        <v>769</v>
+      </c>
+      <c r="E192" t="s">
         <v>770</v>
-      </c>
-      <c r="E192" t="s">
-        <v>771</v>
       </c>
       <c r="F192" t="s">
         <v>16</v>
@@ -9461,21 +9458,21 @@
         <v>25</v>
       </c>
       <c r="K192" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
+        <v>772</v>
+      </c>
+      <c r="B193" t="s">
         <v>773</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C193" t="s">
+        <v>110</v>
+      </c>
+      <c r="D193" t="s">
         <v>774</v>
-      </c>
-      <c r="C193" t="s">
-        <v>111</v>
-      </c>
-      <c r="D193" t="s">
-        <v>775</v>
       </c>
       <c r="E193" t="s">
         <v>33</v>
@@ -9496,24 +9493,24 @@
         <v>25</v>
       </c>
       <c r="K193" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
+        <v>776</v>
+      </c>
+      <c r="B194" t="s">
         <v>777</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
+        <v>110</v>
+      </c>
+      <c r="D194" t="s">
         <v>778</v>
       </c>
-      <c r="C194" t="s">
-        <v>111</v>
-      </c>
-      <c r="D194" t="s">
-        <v>779</v>
-      </c>
       <c r="E194" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F194" t="s">
         <v>16</v>
@@ -9531,24 +9528,24 @@
         <v>20</v>
       </c>
       <c r="K194" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
+        <v>780</v>
+      </c>
+      <c r="B195" t="s">
         <v>781</v>
-      </c>
-      <c r="B195" t="s">
-        <v>782</v>
       </c>
       <c r="C195" t="s">
         <v>13</v>
       </c>
       <c r="D195" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E195" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F195" t="s">
         <v>16</v>
@@ -9566,15 +9563,15 @@
         <v>20</v>
       </c>
       <c r="K195" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
+        <v>784</v>
+      </c>
+      <c r="B196" t="s">
         <v>785</v>
-      </c>
-      <c r="B196" t="s">
-        <v>786</v>
       </c>
       <c r="C196" t="s">
         <v>13</v>
@@ -9583,7 +9580,7 @@
         <v>18</v>
       </c>
       <c r="E196" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -9601,21 +9598,21 @@
         <v>25</v>
       </c>
       <c r="K196" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B197" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C197" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D197" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E197" t="s">
         <v>47</v>
@@ -9630,30 +9627,30 @@
         <v>18</v>
       </c>
       <c r="I197" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J197" t="s">
         <v>25</v>
       </c>
       <c r="K197" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
+        <v>789</v>
+      </c>
+      <c r="B198" t="s">
         <v>790</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C198" t="s">
+        <v>116</v>
+      </c>
+      <c r="D198" t="s">
         <v>791</v>
       </c>
-      <c r="C198" t="s">
-        <v>117</v>
-      </c>
-      <c r="D198" t="s">
+      <c r="E198" t="s">
         <v>792</v>
-      </c>
-      <c r="E198" t="s">
-        <v>793</v>
       </c>
       <c r="F198" t="s">
         <v>34</v>
@@ -9662,7 +9659,7 @@
         <v>17</v>
       </c>
       <c r="H198" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I198" t="s">
         <v>19</v>
@@ -9671,24 +9668,24 @@
         <v>25</v>
       </c>
       <c r="K198" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
+        <v>794</v>
+      </c>
+      <c r="B199" t="s">
         <v>795</v>
       </c>
-      <c r="B199" t="s">
+      <c r="C199" t="s">
+        <v>116</v>
+      </c>
+      <c r="D199" t="s">
         <v>796</v>
       </c>
-      <c r="C199" t="s">
-        <v>117</v>
-      </c>
-      <c r="D199" t="s">
-        <v>797</v>
-      </c>
       <c r="E199" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F199" t="s">
         <v>16</v>
@@ -9700,30 +9697,30 @@
         <v>42</v>
       </c>
       <c r="I199" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J199" t="s">
         <v>25</v>
       </c>
       <c r="K199" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
+        <v>798</v>
+      </c>
+      <c r="B200" t="s">
         <v>799</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" t="s">
+        <v>110</v>
+      </c>
+      <c r="D200" t="s">
         <v>800</v>
       </c>
-      <c r="C200" t="s">
-        <v>111</v>
-      </c>
-      <c r="D200" t="s">
-        <v>801</v>
-      </c>
       <c r="E200" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F200" t="s">
         <v>16</v>
@@ -9741,24 +9738,24 @@
         <v>20</v>
       </c>
       <c r="K200" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
+        <v>802</v>
+      </c>
+      <c r="B201" t="s">
         <v>803</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C201" t="s">
+        <v>110</v>
+      </c>
+      <c r="D201" t="s">
         <v>804</v>
       </c>
-      <c r="C201" t="s">
-        <v>111</v>
-      </c>
-      <c r="D201" t="s">
-        <v>805</v>
-      </c>
       <c r="E201" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F201" t="s">
         <v>16</v>
@@ -9776,7 +9773,7 @@
         <v>25</v>
       </c>
       <c r="K201" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/orders.xlsx
+++ b/public/data/orders.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="808">
   <si>
     <t>Submitted time</t>
   </si>
@@ -211,6 +211,9 @@
     <t>Davin P</t>
   </si>
   <si>
+    <t>mer</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
@@ -454,6 +457,9 @@
     <t>ardiena</t>
   </si>
   <si>
+    <t>83</t>
+  </si>
+  <si>
     <t>06/26/2026 06:47 AM</t>
   </si>
   <si>
@@ -2206,7 +2212,7 @@
     <t>Feivel Qutby</t>
   </si>
   <si>
-    <t>Feivel</t>
+    <t>FEIVEL</t>
   </si>
   <si>
     <t>Screenshot 2026-06-29 at 11.53.36 PM.png</t>
@@ -3102,10 +3108,10 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -3123,24 +3129,24 @@
         <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
@@ -3158,24 +3164,24 @@
         <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -3193,24 +3199,24 @@
         <v>20</v>
       </c>
       <c r="K13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
@@ -3228,21 +3234,21 @@
         <v>20</v>
       </c>
       <c r="K14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
         <v>61</v>
@@ -3263,24 +3269,24 @@
         <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
@@ -3298,24 +3304,24 @@
         <v>25</v>
       </c>
       <c r="K16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
@@ -3333,24 +3339,24 @@
         <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -3368,15 +3374,15 @@
         <v>25</v>
       </c>
       <c r="K18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
@@ -3385,7 +3391,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F19" t="s">
         <v>34</v>
@@ -3403,24 +3409,24 @@
         <v>25</v>
       </c>
       <c r="K19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
@@ -3438,24 +3444,24 @@
         <v>20</v>
       </c>
       <c r="K20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
@@ -3473,21 +3479,21 @@
         <v>20</v>
       </c>
       <c r="K21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
         <v>55</v>
@@ -3508,24 +3514,24 @@
         <v>25</v>
       </c>
       <c r="K22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -3537,30 +3543,30 @@
         <v>36</v>
       </c>
       <c r="I23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J23" t="s">
         <v>25</v>
       </c>
       <c r="K23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F24" t="s">
         <v>16</v>
@@ -3578,24 +3584,24 @@
         <v>25</v>
       </c>
       <c r="K24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -3613,24 +3619,24 @@
         <v>25</v>
       </c>
       <c r="K25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
@@ -3648,24 +3654,24 @@
         <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F27" t="s">
         <v>34</v>
@@ -3674,7 +3680,7 @@
         <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I27" t="s">
         <v>19</v>
@@ -3683,21 +3689,21 @@
         <v>25</v>
       </c>
       <c r="K27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E28" t="s">
         <v>33</v>
@@ -3712,30 +3718,30 @@
         <v>36</v>
       </c>
       <c r="I28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J28" t="s">
         <v>20</v>
       </c>
       <c r="K28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="F29" t="s">
         <v>16</v>
@@ -3753,24 +3759,24 @@
         <v>25</v>
       </c>
       <c r="K29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -3788,21 +3794,21 @@
         <v>25</v>
       </c>
       <c r="K30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B31" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E31" t="s">
         <v>33</v>
@@ -3823,24 +3829,24 @@
         <v>20</v>
       </c>
       <c r="K31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B32" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E32" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F32" t="s">
         <v>16</v>
@@ -3858,24 +3864,24 @@
         <v>20</v>
       </c>
       <c r="K32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F33" t="s">
         <v>16</v>
@@ -3893,24 +3899,24 @@
         <v>25</v>
       </c>
       <c r="K33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B34" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E34" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F34" t="s">
         <v>16</v>
@@ -3928,24 +3934,24 @@
         <v>25</v>
       </c>
       <c r="K34" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E35" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
@@ -3963,15 +3969,15 @@
         <v>25</v>
       </c>
       <c r="K35" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
@@ -3980,7 +3986,7 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
@@ -3989,7 +3995,7 @@
         <v>17</v>
       </c>
       <c r="H36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I36" t="s">
         <v>19</v>
@@ -3998,24 +4004,24 @@
         <v>20</v>
       </c>
       <c r="K36" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E37" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
@@ -4033,21 +4039,21 @@
         <v>25</v>
       </c>
       <c r="K37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4068,24 +4074,24 @@
         <v>20</v>
       </c>
       <c r="K38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E39" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -4103,21 +4109,21 @@
         <v>25</v>
       </c>
       <c r="K39" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D40" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E40" t="s">
         <v>55</v>
@@ -4129,7 +4135,7 @@
         <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I40" t="s">
         <v>19</v>
@@ -4143,19 +4149,19 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D41" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E41" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
@@ -4173,24 +4179,24 @@
         <v>25</v>
       </c>
       <c r="K41" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E42" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
@@ -4208,24 +4214,24 @@
         <v>25</v>
       </c>
       <c r="K42" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D43" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E43" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
@@ -4243,24 +4249,24 @@
         <v>25</v>
       </c>
       <c r="K43" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B44" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C44" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D44" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E44" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
@@ -4272,27 +4278,27 @@
         <v>42</v>
       </c>
       <c r="I44" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J44" t="s">
         <v>20</v>
       </c>
       <c r="K44" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B45" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C45" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D45" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4313,24 +4319,24 @@
         <v>20</v>
       </c>
       <c r="K45" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B46" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E46" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
@@ -4348,21 +4354,21 @@
         <v>20</v>
       </c>
       <c r="K46" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B47" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D47" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -4374,7 +4380,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>173</v>
+        <v>36</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
@@ -4383,24 +4389,24 @@
         <v>25</v>
       </c>
       <c r="K47" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B48" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C48" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D48" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E48" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -4418,15 +4424,15 @@
         <v>20</v>
       </c>
       <c r="K48" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
@@ -4444,7 +4450,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
@@ -4453,24 +4459,24 @@
         <v>20</v>
       </c>
       <c r="K49" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B50" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -4488,24 +4494,24 @@
         <v>20</v>
       </c>
       <c r="K50" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B51" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C51" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D51" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E51" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
@@ -4523,15 +4529,15 @@
         <v>25</v>
       </c>
       <c r="K51" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B52" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
@@ -4558,21 +4564,21 @@
         <v>25</v>
       </c>
       <c r="K52" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B53" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E53" t="s">
         <v>47</v>
@@ -4593,21 +4599,21 @@
         <v>25</v>
       </c>
       <c r="K53" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B54" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C54" t="s">
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E54" t="s">
         <v>55</v>
@@ -4628,21 +4634,21 @@
         <v>25</v>
       </c>
       <c r="K54" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B55" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C55" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D55" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E55" t="s">
         <v>47</v>
@@ -4663,24 +4669,24 @@
         <v>20</v>
       </c>
       <c r="K55" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B56" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C56" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D56" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E56" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
@@ -4698,24 +4704,24 @@
         <v>20</v>
       </c>
       <c r="K56" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B57" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E57" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
@@ -4733,21 +4739,21 @@
         <v>25</v>
       </c>
       <c r="K57" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B58" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C58" t="s">
         <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E58" t="s">
         <v>55</v>
@@ -4762,27 +4768,27 @@
         <v>42</v>
       </c>
       <c r="I58" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J58" t="s">
         <v>25</v>
       </c>
       <c r="K58" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B59" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C59" t="s">
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E59" t="s">
         <v>47</v>
@@ -4803,24 +4809,24 @@
         <v>25</v>
       </c>
       <c r="K59" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B60" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E60" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F60" t="s">
         <v>34</v>
@@ -4838,15 +4844,15 @@
         <v>25</v>
       </c>
       <c r="K60" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B61" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C61" t="s">
         <v>13</v>
@@ -4873,24 +4879,24 @@
         <v>25</v>
       </c>
       <c r="K61" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B62" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C62" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
@@ -4899,7 +4905,7 @@
         <v>17</v>
       </c>
       <c r="H62" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
@@ -4908,15 +4914,15 @@
         <v>20</v>
       </c>
       <c r="K62" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B63" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
@@ -4925,7 +4931,7 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F63" t="s">
         <v>16</v>
@@ -4943,15 +4949,15 @@
         <v>25</v>
       </c>
       <c r="K63" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B64" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C64" t="s">
         <v>13</v>
@@ -4960,7 +4966,7 @@
         <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
@@ -4978,24 +4984,24 @@
         <v>20</v>
       </c>
       <c r="K64" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B65" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E65" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
@@ -5013,24 +5019,24 @@
         <v>20</v>
       </c>
       <c r="K65" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B66" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C66" t="s">
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E66" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F66" t="s">
         <v>34</v>
@@ -5048,24 +5054,24 @@
         <v>20</v>
       </c>
       <c r="K66" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B67" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C67" t="s">
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E67" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
@@ -5083,24 +5089,24 @@
         <v>20</v>
       </c>
       <c r="K67" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B68" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C68" t="s">
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E68" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
@@ -5118,24 +5124,24 @@
         <v>25</v>
       </c>
       <c r="K68" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B69" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E69" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F69" t="s">
         <v>16</v>
@@ -5153,24 +5159,24 @@
         <v>25</v>
       </c>
       <c r="K69" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B70" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C70" t="s">
         <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E70" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F70" t="s">
         <v>16</v>
@@ -5188,24 +5194,24 @@
         <v>20</v>
       </c>
       <c r="K70" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B71" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C71" t="s">
         <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E71" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
@@ -5223,15 +5229,15 @@
         <v>20</v>
       </c>
       <c r="K71" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B72" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C72" t="s">
         <v>13</v>
@@ -5240,7 +5246,7 @@
         <v>14</v>
       </c>
       <c r="E72" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F72" t="s">
         <v>34</v>
@@ -5258,24 +5264,24 @@
         <v>25</v>
       </c>
       <c r="K72" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B73" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C73" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D73" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E73" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F73" t="s">
         <v>16</v>
@@ -5293,24 +5299,24 @@
         <v>20</v>
       </c>
       <c r="K73" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B74" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C74" t="s">
         <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E74" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F74" t="s">
         <v>34</v>
@@ -5322,30 +5328,30 @@
         <v>56</v>
       </c>
       <c r="I74" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J74" t="s">
         <v>25</v>
       </c>
       <c r="K74" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B75" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C75" t="s">
         <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E75" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F75" t="s">
         <v>34</v>
@@ -5363,21 +5369,21 @@
         <v>25</v>
       </c>
       <c r="K75" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B76" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C76" t="s">
         <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E76" t="s">
         <v>29</v>
@@ -5398,21 +5404,21 @@
         <v>20</v>
       </c>
       <c r="K76" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B77" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C77" t="s">
         <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E77" t="s">
         <v>29</v>
@@ -5433,24 +5439,24 @@
         <v>25</v>
       </c>
       <c r="K77" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B78" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C78" t="s">
         <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E78" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F78" t="s">
         <v>16</v>
@@ -5468,21 +5474,21 @@
         <v>25</v>
       </c>
       <c r="K78" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B79" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C79" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E79" t="s">
         <v>29</v>
@@ -5503,24 +5509,24 @@
         <v>25</v>
       </c>
       <c r="K79" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C80" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E80" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F80" t="s">
         <v>16</v>
@@ -5538,21 +5544,21 @@
         <v>25</v>
       </c>
       <c r="K80" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B81" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C81" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D81" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E81" t="s">
         <v>61</v>
@@ -5573,15 +5579,15 @@
         <v>20</v>
       </c>
       <c r="K81" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B82" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C82" t="s">
         <v>13</v>
@@ -5590,7 +5596,7 @@
         <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F82" t="s">
         <v>34</v>
@@ -5608,24 +5614,24 @@
         <v>25</v>
       </c>
       <c r="K82" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B83" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C83" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D83" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E83" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F83" t="s">
         <v>16</v>
@@ -5634,7 +5640,7 @@
         <v>35</v>
       </c>
       <c r="H83" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I83" t="s">
         <v>19</v>
@@ -5643,21 +5649,21 @@
         <v>25</v>
       </c>
       <c r="K83" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B84" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C84" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D84" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -5678,24 +5684,24 @@
         <v>25</v>
       </c>
       <c r="K84" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B85" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C85" t="s">
         <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E85" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -5713,24 +5719,24 @@
         <v>25</v>
       </c>
       <c r="K85" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B86" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C86" t="s">
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E86" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F86" t="s">
         <v>16</v>
@@ -5748,21 +5754,21 @@
         <v>25</v>
       </c>
       <c r="K86" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B87" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C87" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D87" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E87" t="s">
         <v>33</v>
@@ -5783,24 +5789,24 @@
         <v>25</v>
       </c>
       <c r="K87" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B88" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C88" t="s">
         <v>13</v>
       </c>
       <c r="D88" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E88" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F88" t="s">
         <v>34</v>
@@ -5818,24 +5824,24 @@
         <v>25</v>
       </c>
       <c r="K88" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B89" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C89" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D89" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E89" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F89" t="s">
         <v>16</v>
@@ -5853,21 +5859,21 @@
         <v>25</v>
       </c>
       <c r="K89" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B90" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C90" t="s">
         <v>13</v>
       </c>
       <c r="D90" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E90" t="s">
         <v>61</v>
@@ -5879,7 +5885,7 @@
         <v>17</v>
       </c>
       <c r="H90" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I90" t="s">
         <v>19</v>
@@ -5888,24 +5894,24 @@
         <v>25</v>
       </c>
       <c r="K90" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B91" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C91" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D91" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E91" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F91" t="s">
         <v>16</v>
@@ -5923,24 +5929,24 @@
         <v>25</v>
       </c>
       <c r="K91" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B92" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C92" t="s">
         <v>13</v>
       </c>
       <c r="D92" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E92" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F92" t="s">
         <v>16</v>
@@ -5958,21 +5964,21 @@
         <v>20</v>
       </c>
       <c r="K92" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B93" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C93" t="s">
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E93" t="s">
         <v>55</v>
@@ -5984,7 +5990,7 @@
         <v>35</v>
       </c>
       <c r="H93" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
@@ -5993,24 +5999,24 @@
         <v>25</v>
       </c>
       <c r="K93" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B94" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C94" t="s">
         <v>13</v>
       </c>
       <c r="D94" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E94" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F94" t="s">
         <v>16</v>
@@ -6028,24 +6034,24 @@
         <v>20</v>
       </c>
       <c r="K94" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B95" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C95" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D95" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E95" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F95" t="s">
         <v>16</v>
@@ -6063,24 +6069,24 @@
         <v>20</v>
       </c>
       <c r="K95" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B96" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C96" t="s">
         <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E96" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F96" t="s">
         <v>16</v>
@@ -6098,24 +6104,24 @@
         <v>25</v>
       </c>
       <c r="K96" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B97" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C97" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D97" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E97" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F97" t="s">
         <v>16</v>
@@ -6127,21 +6133,21 @@
         <v>36</v>
       </c>
       <c r="I97" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J97" t="s">
         <v>25</v>
       </c>
       <c r="K97" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B98" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C98" t="s">
         <v>13</v>
@@ -6150,7 +6156,7 @@
         <v>14</v>
       </c>
       <c r="E98" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F98" t="s">
         <v>34</v>
@@ -6168,24 +6174,24 @@
         <v>25</v>
       </c>
       <c r="K98" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B99" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C99" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D99" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E99" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F99" t="s">
         <v>16</v>
@@ -6203,24 +6209,24 @@
         <v>25</v>
       </c>
       <c r="K99" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B100" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C100" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D100" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E100" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F100" t="s">
         <v>34</v>
@@ -6229,7 +6235,7 @@
         <v>17</v>
       </c>
       <c r="H100" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
@@ -6238,24 +6244,24 @@
         <v>20</v>
       </c>
       <c r="K100" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B101" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C101" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D101" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E101" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F101" t="s">
         <v>16</v>
@@ -6273,24 +6279,24 @@
         <v>20</v>
       </c>
       <c r="K101" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B102" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C102" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D102" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E102" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F102" t="s">
         <v>16</v>
@@ -6308,24 +6314,24 @@
         <v>20</v>
       </c>
       <c r="K102" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B103" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C103" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D103" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E103" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F103" t="s">
         <v>16</v>
@@ -6343,21 +6349,21 @@
         <v>25</v>
       </c>
       <c r="K103" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B104" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C104" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D104" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E104" t="s">
         <v>41</v>
@@ -6369,7 +6375,7 @@
         <v>17</v>
       </c>
       <c r="H104" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="I104" t="s">
         <v>19</v>
@@ -6378,24 +6384,24 @@
         <v>25</v>
       </c>
       <c r="K104" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B105" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C105" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D105" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E105" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F105" t="s">
         <v>34</v>
@@ -6407,30 +6413,30 @@
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J105" t="s">
         <v>25</v>
       </c>
       <c r="K105" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B106" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C106" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D106" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E106" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F106" t="s">
         <v>16</v>
@@ -6448,24 +6454,24 @@
         <v>20</v>
       </c>
       <c r="K106" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B107" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C107" t="s">
         <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E107" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F107" t="s">
         <v>16</v>
@@ -6483,24 +6489,24 @@
         <v>20</v>
       </c>
       <c r="K107" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B108" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C108" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D108" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E108" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F108" t="s">
         <v>16</v>
@@ -6518,24 +6524,24 @@
         <v>20</v>
       </c>
       <c r="K108" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B109" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C109" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D109" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E109" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F109" t="s">
         <v>16</v>
@@ -6553,24 +6559,24 @@
         <v>20</v>
       </c>
       <c r="K109" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B110" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C110" t="s">
         <v>13</v>
       </c>
       <c r="D110" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E110" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F110" t="s">
         <v>16</v>
@@ -6588,24 +6594,24 @@
         <v>25</v>
       </c>
       <c r="K110" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B111" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C111" t="s">
         <v>13</v>
       </c>
       <c r="D111" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E111" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F111" t="s">
         <v>16</v>
@@ -6623,24 +6629,24 @@
         <v>20</v>
       </c>
       <c r="K111" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B112" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C112" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D112" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E112" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F112" t="s">
         <v>16</v>
@@ -6658,24 +6664,24 @@
         <v>20</v>
       </c>
       <c r="K112" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B113" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C113" t="s">
         <v>13</v>
       </c>
       <c r="D113" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E113" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F113" t="s">
         <v>16</v>
@@ -6693,24 +6699,24 @@
         <v>20</v>
       </c>
       <c r="K113" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B114" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C114" t="s">
         <v>13</v>
       </c>
       <c r="D114" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E114" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F114" t="s">
         <v>34</v>
@@ -6719,7 +6725,7 @@
         <v>35</v>
       </c>
       <c r="H114" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I114" t="s">
         <v>19</v>
@@ -6728,24 +6734,24 @@
         <v>25</v>
       </c>
       <c r="K114" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B115" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C115" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D115" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E115" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F115" t="s">
         <v>16</v>
@@ -6757,30 +6763,30 @@
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J115" t="s">
         <v>25</v>
       </c>
       <c r="K115" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B116" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C116" t="s">
         <v>13</v>
       </c>
       <c r="D116" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E116" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F116" t="s">
         <v>16</v>
@@ -6798,21 +6804,21 @@
         <v>20</v>
       </c>
       <c r="K116" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B117" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C117" t="s">
         <v>13</v>
       </c>
       <c r="D117" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E117" t="s">
         <v>41</v>
@@ -6824,7 +6830,7 @@
         <v>35</v>
       </c>
       <c r="H117" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I117" t="s">
         <v>19</v>
@@ -6833,24 +6839,24 @@
         <v>25</v>
       </c>
       <c r="K117" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B118" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C118" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D118" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E118" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F118" t="s">
         <v>34</v>
@@ -6868,15 +6874,15 @@
         <v>20</v>
       </c>
       <c r="K118" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B119" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C119" t="s">
         <v>13</v>
@@ -6885,7 +6891,7 @@
         <v>14</v>
       </c>
       <c r="E119" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F119" t="s">
         <v>16</v>
@@ -6903,24 +6909,24 @@
         <v>25</v>
       </c>
       <c r="K119" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B120" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C120" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D120" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E120" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F120" t="s">
         <v>16</v>
@@ -6938,24 +6944,24 @@
         <v>25</v>
       </c>
       <c r="K120" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B121" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C121" t="s">
         <v>13</v>
       </c>
       <c r="D121" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E121" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F121" t="s">
         <v>16</v>
@@ -6973,24 +6979,24 @@
         <v>25</v>
       </c>
       <c r="K121" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>504</v>
+      </c>
+      <c r="B122" t="s">
         <v>502</v>
-      </c>
-      <c r="B122" t="s">
-        <v>500</v>
       </c>
       <c r="C122" t="s">
         <v>13</v>
       </c>
       <c r="D122" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E122" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F122" t="s">
         <v>16</v>
@@ -7008,24 +7014,24 @@
         <v>20</v>
       </c>
       <c r="K122" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B123" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C123" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D123" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E123" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F123" t="s">
         <v>16</v>
@@ -7037,30 +7043,30 @@
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J123" t="s">
         <v>25</v>
       </c>
       <c r="K123" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B124" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C124" t="s">
         <v>13</v>
       </c>
       <c r="D124" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E124" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F124" t="s">
         <v>34</v>
@@ -7078,24 +7084,24 @@
         <v>20</v>
       </c>
       <c r="K124" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B125" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C125" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D125" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E125" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F125" t="s">
         <v>16</v>
@@ -7113,24 +7119,24 @@
         <v>25</v>
       </c>
       <c r="K125" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B126" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C126" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D126" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E126" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F126" t="s">
         <v>16</v>
@@ -7148,24 +7154,24 @@
         <v>20</v>
       </c>
       <c r="K126" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B127" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C127" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D127" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E127" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F127" t="s">
         <v>16</v>
@@ -7183,24 +7189,24 @@
         <v>25</v>
       </c>
       <c r="K127" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B128" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C128" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D128" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E128" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F128" t="s">
         <v>16</v>
@@ -7209,7 +7215,7 @@
         <v>17</v>
       </c>
       <c r="H128" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I128" t="s">
         <v>19</v>
@@ -7218,21 +7224,21 @@
         <v>25</v>
       </c>
       <c r="K128" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B129" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C129" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D129" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E129" t="s">
         <v>41</v>
@@ -7253,21 +7259,21 @@
         <v>20</v>
       </c>
       <c r="K129" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B130" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C130" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D130" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E130" t="s">
         <v>41</v>
@@ -7288,24 +7294,24 @@
         <v>25</v>
       </c>
       <c r="K130" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B131" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C131" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D131" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E131" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F131" t="s">
         <v>16</v>
@@ -7314,7 +7320,7 @@
         <v>17</v>
       </c>
       <c r="H131" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I131" t="s">
         <v>19</v>
@@ -7323,21 +7329,21 @@
         <v>25</v>
       </c>
       <c r="K131" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B132" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C132" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D132" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E132" t="s">
         <v>47</v>
@@ -7358,24 +7364,24 @@
         <v>25</v>
       </c>
       <c r="K132" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B133" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C133" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D133" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E133" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F133" t="s">
         <v>16</v>
@@ -7393,24 +7399,24 @@
         <v>25</v>
       </c>
       <c r="K133" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B134" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C134" t="s">
         <v>13</v>
       </c>
       <c r="D134" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E134" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F134" t="s">
         <v>16</v>
@@ -7428,24 +7434,24 @@
         <v>25</v>
       </c>
       <c r="K134" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B135" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C135" t="s">
         <v>13</v>
       </c>
       <c r="D135" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E135" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F135" t="s">
         <v>16</v>
@@ -7463,24 +7469,24 @@
         <v>20</v>
       </c>
       <c r="K135" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B136" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C136" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D136" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E136" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F136" t="s">
         <v>16</v>
@@ -7498,30 +7504,30 @@
         <v>25</v>
       </c>
       <c r="K136" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B137" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C137" t="s">
         <v>13</v>
       </c>
       <c r="D137" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E137" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
       </c>
       <c r="G137" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H137" t="s">
         <v>56</v>
@@ -7533,24 +7539,24 @@
         <v>20</v>
       </c>
       <c r="K137" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B138" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C138" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D138" t="s">
         <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F138" t="s">
         <v>34</v>
@@ -7562,30 +7568,30 @@
         <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J138" t="s">
         <v>25</v>
       </c>
       <c r="K138" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B139" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C139" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D139" t="s">
         <v>14</v>
       </c>
       <c r="E139" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F139" t="s">
         <v>16</v>
@@ -7603,21 +7609,21 @@
         <v>25</v>
       </c>
       <c r="K139" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B140" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C140" t="s">
         <v>13</v>
       </c>
       <c r="D140" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E140" t="s">
         <v>14</v>
@@ -7638,24 +7644,24 @@
         <v>25</v>
       </c>
       <c r="K140" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B141" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C141" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D141" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E141" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F141" t="s">
         <v>16</v>
@@ -7673,24 +7679,24 @@
         <v>25</v>
       </c>
       <c r="K141" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
+        <v>578</v>
+      </c>
+      <c r="B142" t="s">
+        <v>575</v>
+      </c>
+      <c r="C142" t="s">
+        <v>111</v>
+      </c>
+      <c r="D142" t="s">
         <v>576</v>
       </c>
-      <c r="B142" t="s">
-        <v>573</v>
-      </c>
-      <c r="C142" t="s">
-        <v>110</v>
-      </c>
-      <c r="D142" t="s">
-        <v>574</v>
-      </c>
       <c r="E142" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F142" t="s">
         <v>16</v>
@@ -7708,24 +7714,24 @@
         <v>20</v>
       </c>
       <c r="K142" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B143" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C143" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D143" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E143" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F143" t="s">
         <v>16</v>
@@ -7743,24 +7749,24 @@
         <v>20</v>
       </c>
       <c r="K143" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B144" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C144" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D144" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E144" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F144" t="s">
         <v>16</v>
@@ -7778,24 +7784,24 @@
         <v>20</v>
       </c>
       <c r="K144" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B145" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C145" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D145" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E145" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -7813,24 +7819,24 @@
         <v>20</v>
       </c>
       <c r="K145" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B146" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C146" t="s">
         <v>13</v>
       </c>
       <c r="D146" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E146" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F146" t="s">
         <v>34</v>
@@ -7848,21 +7854,21 @@
         <v>25</v>
       </c>
       <c r="K146" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B147" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C147" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D147" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E147" t="s">
         <v>29</v>
@@ -7883,24 +7889,24 @@
         <v>25</v>
       </c>
       <c r="K147" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B148" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C148" t="s">
         <v>13</v>
       </c>
       <c r="D148" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E148" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F148" t="s">
         <v>34</v>
@@ -7909,7 +7915,7 @@
         <v>35</v>
       </c>
       <c r="H148" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I148" t="s">
         <v>19</v>
@@ -7918,24 +7924,24 @@
         <v>20</v>
       </c>
       <c r="K148" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B149" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C149" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D149" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E149" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F149" t="s">
         <v>16</v>
@@ -7953,24 +7959,24 @@
         <v>25</v>
       </c>
       <c r="K149" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B150" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C150" t="s">
         <v>13</v>
       </c>
       <c r="D150" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E150" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F150" t="s">
         <v>16</v>
@@ -7988,24 +7994,24 @@
         <v>20</v>
       </c>
       <c r="K150" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B151" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C151" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D151" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E151" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F151" t="s">
         <v>16</v>
@@ -8023,24 +8029,24 @@
         <v>20</v>
       </c>
       <c r="K151" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B152" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C152" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D152" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E152" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F152" t="s">
         <v>16</v>
@@ -8058,21 +8064,21 @@
         <v>20</v>
       </c>
       <c r="K152" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B153" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C153" t="s">
         <v>13</v>
       </c>
       <c r="D153" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E153" t="s">
         <v>47</v>
@@ -8093,24 +8099,24 @@
         <v>20</v>
       </c>
       <c r="K153" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B154" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C154" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D154" t="s">
         <v>14</v>
       </c>
       <c r="E154" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F154" t="s">
         <v>16</v>
@@ -8128,24 +8134,24 @@
         <v>25</v>
       </c>
       <c r="K154" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B155" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C155" t="s">
         <v>13</v>
       </c>
       <c r="D155" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E155" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
@@ -8163,24 +8169,24 @@
         <v>20</v>
       </c>
       <c r="K155" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B156" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C156" t="s">
         <v>13</v>
       </c>
       <c r="D156" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E156" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F156" t="s">
         <v>34</v>
@@ -8198,24 +8204,24 @@
         <v>20</v>
       </c>
       <c r="K156" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B157" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C157" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D157" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E157" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F157" t="s">
         <v>16</v>
@@ -8233,24 +8239,24 @@
         <v>25</v>
       </c>
       <c r="K157" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B158" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C158" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D158" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E158" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F158" t="s">
         <v>16</v>
@@ -8259,7 +8265,7 @@
         <v>17</v>
       </c>
       <c r="H158" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I158" t="s">
         <v>19</v>
@@ -8268,24 +8274,24 @@
         <v>25</v>
       </c>
       <c r="K158" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B159" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C159" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D159" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E159" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F159" t="s">
         <v>16</v>
@@ -8294,7 +8300,7 @@
         <v>35</v>
       </c>
       <c r="H159" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I159" t="s">
         <v>19</v>
@@ -8303,24 +8309,24 @@
         <v>25</v>
       </c>
       <c r="K159" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B160" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C160" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D160" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E160" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F160" t="s">
         <v>34</v>
@@ -8329,33 +8335,33 @@
         <v>17</v>
       </c>
       <c r="H160" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I160" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J160" t="s">
         <v>25</v>
       </c>
       <c r="K160" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B161" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C161" t="s">
         <v>13</v>
       </c>
       <c r="D161" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E161" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F161" t="s">
         <v>16</v>
@@ -8373,24 +8379,24 @@
         <v>20</v>
       </c>
       <c r="K161" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B162" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C162" t="s">
         <v>13</v>
       </c>
       <c r="D162" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E162" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F162" t="s">
         <v>34</v>
@@ -8408,24 +8414,24 @@
         <v>20</v>
       </c>
       <c r="K162" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B163" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C163" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D163" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E163" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F163" t="s">
         <v>16</v>
@@ -8443,21 +8449,21 @@
         <v>25</v>
       </c>
       <c r="K163" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B164" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C164" t="s">
         <v>13</v>
       </c>
       <c r="D164" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E164" t="s">
         <v>14</v>
@@ -8478,18 +8484,18 @@
         <v>25</v>
       </c>
       <c r="K164" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B165" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C165" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D165" t="s">
         <v>14</v>
@@ -8513,24 +8519,24 @@
         <v>25</v>
       </c>
       <c r="K165" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B166" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C166" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D166" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E166" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F166" t="s">
         <v>16</v>
@@ -8548,24 +8554,24 @@
         <v>20</v>
       </c>
       <c r="K166" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B167" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C167" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D167" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E167" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F167" t="s">
         <v>16</v>
@@ -8574,7 +8580,7 @@
         <v>35</v>
       </c>
       <c r="H167" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I167" t="s">
         <v>19</v>
@@ -8583,24 +8589,24 @@
         <v>20</v>
       </c>
       <c r="K167" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B168" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C168" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D168" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E168" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F168" t="s">
         <v>16</v>
@@ -8618,24 +8624,24 @@
         <v>25</v>
       </c>
       <c r="K168" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B169" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C169" t="s">
         <v>13</v>
       </c>
       <c r="D169" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E169" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F169" t="s">
         <v>16</v>
@@ -8653,24 +8659,24 @@
         <v>25</v>
       </c>
       <c r="K169" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B170" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C170" t="s">
         <v>13</v>
       </c>
       <c r="D170" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E170" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F170" t="s">
         <v>16</v>
@@ -8688,21 +8694,21 @@
         <v>25</v>
       </c>
       <c r="K170" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B171" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C171" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D171" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E171" t="s">
         <v>15</v>
@@ -8723,24 +8729,24 @@
         <v>20</v>
       </c>
       <c r="K171" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B172" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C172" t="s">
         <v>13</v>
       </c>
       <c r="D172" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E172" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F172" t="s">
         <v>16</v>
@@ -8758,24 +8764,24 @@
         <v>25</v>
       </c>
       <c r="K172" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B173" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C173" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D173" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E173" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F173" t="s">
         <v>16</v>
@@ -8793,24 +8799,24 @@
         <v>25</v>
       </c>
       <c r="K173" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B174" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C174" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D174" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E174" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F174" t="s">
         <v>16</v>
@@ -8828,24 +8834,24 @@
         <v>20</v>
       </c>
       <c r="K174" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B175" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C175" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D175" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E175" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F175" t="s">
         <v>34</v>
@@ -8863,18 +8869,18 @@
         <v>20</v>
       </c>
       <c r="K175" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B176" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C176" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D176" t="s">
         <v>14</v>
@@ -8892,27 +8898,27 @@
         <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J176" t="s">
         <v>20</v>
       </c>
       <c r="K176" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B177" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C177" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D177" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E177" t="s">
         <v>29</v>
@@ -8933,24 +8939,24 @@
         <v>25</v>
       </c>
       <c r="K177" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B178" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C178" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D178" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E178" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F178" t="s">
         <v>34</v>
@@ -8968,15 +8974,15 @@
         <v>25</v>
       </c>
       <c r="K178" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B179" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C179" t="s">
         <v>13</v>
@@ -8985,7 +8991,7 @@
         <v>14</v>
       </c>
       <c r="E179" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F179" t="s">
         <v>34</v>
@@ -9003,24 +9009,24 @@
         <v>25</v>
       </c>
       <c r="K179" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B180" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C180" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D180" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E180" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -9032,30 +9038,30 @@
         <v>18</v>
       </c>
       <c r="I180" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J180" t="s">
         <v>20</v>
       </c>
       <c r="K180" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B181" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C181" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D181" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E181" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F181" t="s">
         <v>34</v>
@@ -9073,24 +9079,24 @@
         <v>25</v>
       </c>
       <c r="K181" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B182" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C182" t="s">
         <v>13</v>
       </c>
       <c r="D182" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E182" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F182" t="s">
         <v>34</v>
@@ -9108,24 +9114,24 @@
         <v>25</v>
       </c>
       <c r="K182" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B183" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C183" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D183" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E183" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F183" t="s">
         <v>16</v>
@@ -9143,21 +9149,21 @@
         <v>20</v>
       </c>
       <c r="K183" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B184" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C184" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D184" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E184" t="s">
         <v>29</v>
@@ -9169,7 +9175,7 @@
         <v>17</v>
       </c>
       <c r="H184" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I184" t="s">
         <v>19</v>
@@ -9178,24 +9184,24 @@
         <v>20</v>
       </c>
       <c r="K184" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B185" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C185" t="s">
         <v>13</v>
       </c>
       <c r="D185" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E185" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F185" t="s">
         <v>16</v>
@@ -9207,27 +9213,27 @@
         <v>36</v>
       </c>
       <c r="I185" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J185" t="s">
         <v>25</v>
       </c>
       <c r="K185" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B186" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C186" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D186" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E186" t="s">
         <v>61</v>
@@ -9248,24 +9254,24 @@
         <v>25</v>
       </c>
       <c r="K186" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B187" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C187" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D187" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E187" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F187" t="s">
         <v>16</v>
@@ -9283,24 +9289,24 @@
         <v>25</v>
       </c>
       <c r="K187" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B188" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C188" t="s">
         <v>13</v>
       </c>
       <c r="D188" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E188" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F188" t="s">
         <v>34</v>
@@ -9318,24 +9324,24 @@
         <v>20</v>
       </c>
       <c r="K188" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B189" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C189" t="s">
         <v>13</v>
       </c>
       <c r="D189" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E189" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="F189" t="s">
         <v>16</v>
@@ -9353,24 +9359,24 @@
         <v>20</v>
       </c>
       <c r="K189" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B190" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C190" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D190" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E190" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F190" t="s">
         <v>34</v>
@@ -9388,15 +9394,15 @@
         <v>20</v>
       </c>
       <c r="K190" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B191" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C191" t="s">
         <v>13</v>
@@ -9405,7 +9411,7 @@
         <v>14</v>
       </c>
       <c r="E191" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F191" t="s">
         <v>16</v>
@@ -9423,24 +9429,24 @@
         <v>25</v>
       </c>
       <c r="K191" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B192" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C192" t="s">
         <v>13</v>
       </c>
       <c r="D192" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="E192" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="F192" t="s">
         <v>16</v>
@@ -9458,21 +9464,21 @@
         <v>25</v>
       </c>
       <c r="K192" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B193" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C193" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D193" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="E193" t="s">
         <v>33</v>
@@ -9493,24 +9499,24 @@
         <v>25</v>
       </c>
       <c r="K193" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B194" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C194" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D194" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="E194" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F194" t="s">
         <v>16</v>
@@ -9528,24 +9534,24 @@
         <v>20</v>
       </c>
       <c r="K194" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B195" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C195" t="s">
         <v>13</v>
       </c>
       <c r="D195" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E195" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F195" t="s">
         <v>16</v>
@@ -9563,15 +9569,15 @@
         <v>20</v>
       </c>
       <c r="K195" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B196" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C196" t="s">
         <v>13</v>
@@ -9580,7 +9586,7 @@
         <v>18</v>
       </c>
       <c r="E196" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -9598,21 +9604,21 @@
         <v>25</v>
       </c>
       <c r="K196" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B197" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C197" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D197" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E197" t="s">
         <v>47</v>
@@ -9627,30 +9633,30 @@
         <v>18</v>
       </c>
       <c r="I197" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J197" t="s">
         <v>25</v>
       </c>
       <c r="K197" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B198" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C198" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D198" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="E198" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="F198" t="s">
         <v>34</v>
@@ -9659,7 +9665,7 @@
         <v>17</v>
       </c>
       <c r="H198" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="I198" t="s">
         <v>19</v>
@@ -9668,24 +9674,24 @@
         <v>25</v>
       </c>
       <c r="K198" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B199" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C199" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D199" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="E199" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F199" t="s">
         <v>16</v>
@@ -9697,30 +9703,30 @@
         <v>42</v>
       </c>
       <c r="I199" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J199" t="s">
         <v>25</v>
       </c>
       <c r="K199" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B200" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C200" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D200" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E200" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F200" t="s">
         <v>16</v>
@@ -9738,24 +9744,24 @@
         <v>20</v>
       </c>
       <c r="K200" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B201" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C201" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D201" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="E201" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F201" t="s">
         <v>16</v>
@@ -9773,7 +9779,7 @@
         <v>25</v>
       </c>
       <c r="K201" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/orders.xlsx
+++ b/public/data/orders.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="809">
   <si>
     <t>Submitted time</t>
   </si>
@@ -892,7 +892,1546 @@
     <t>IMG_0398.jpeg</t>
   </si>
   <si>
-    <t>06/26/2026 01:42 PM</t>
+    <t>06/26/2026 02:10 PM</t>
+  </si>
+  <si>
+    <t>Filbert Naldo Wijaya</t>
+  </si>
+  <si>
+    <t>FILBERT</t>
+  </si>
+  <si>
+    <t>IMG_0563.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 02:15 PM</t>
+  </si>
+  <si>
+    <t>Naufal Fahri</t>
+  </si>
+  <si>
+    <t>Naufal</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>IMG_2030.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 02:36 PM</t>
+  </si>
+  <si>
+    <t>Gabriel Budiman</t>
+  </si>
+  <si>
+    <t>Gabriel J</t>
+  </si>
+  <si>
+    <t>IMG_1974.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 02:40 PM</t>
+  </si>
+  <si>
+    <t>Gianina Christophilus</t>
+  </si>
+  <si>
+    <t>C9S1-40</t>
+  </si>
+  <si>
+    <t>IMG_5305.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 02:55 PM</t>
+  </si>
+  <si>
+    <t>Tiffany Michelle</t>
+  </si>
+  <si>
+    <t>TMS</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>IMG_2655.JPG</t>
+  </si>
+  <si>
+    <t>06/26/2026 03:11 PM</t>
+  </si>
+  <si>
+    <t>Graceila Natasya</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>IMG_3915.png</t>
+  </si>
+  <si>
+    <t>06/26/2026 03:29 PM</t>
+  </si>
+  <si>
+    <t>IMG_3772.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 03:37 PM</t>
+  </si>
+  <si>
+    <t>Stepanus Imanuel</t>
+  </si>
+  <si>
+    <t>el</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>06/26/2026 03:57 PM</t>
+  </si>
+  <si>
+    <t>IMG_1636.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 04:12 PM</t>
+  </si>
+  <si>
+    <t>Patricia Gautama</t>
+  </si>
+  <si>
+    <t>CYAK</t>
+  </si>
+  <si>
+    <t>2141cce6-a74b-4481-836b-a1532c64a654.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 04:13 PM</t>
+  </si>
+  <si>
+    <t>06/26/2026 04:20 PM</t>
+  </si>
+  <si>
+    <t>Rio Ferdinand</t>
+  </si>
+  <si>
+    <t>FERDINAND</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>IMG_2045.png</t>
+  </si>
+  <si>
+    <t>06/26/2026 04:22 PM</t>
+  </si>
+  <si>
+    <t>Joey Martin</t>
+  </si>
+  <si>
+    <t>Joey</t>
+  </si>
+  <si>
+    <t>IMG_2168.png</t>
+  </si>
+  <si>
+    <t>06/26/2026 04:26 PM</t>
+  </si>
+  <si>
+    <t>Jacqueline Iman</t>
+  </si>
+  <si>
+    <t>Jacqueline</t>
+  </si>
+  <si>
+    <t>WhatsApp Image 2026-06-26 at 23.06.00.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 04:41 PM</t>
+  </si>
+  <si>
+    <t>Dimas Ismaunnizam</t>
+  </si>
+  <si>
+    <t>MYZWAN</t>
+  </si>
+  <si>
+    <t>IMG_1811.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 04:42 PM</t>
+  </si>
+  <si>
+    <t>Devi Sujata</t>
+  </si>
+  <si>
+    <t>IMG_6353.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 05:08 PM</t>
+  </si>
+  <si>
+    <t>Michelle Roring</t>
+  </si>
+  <si>
+    <t>Misyel</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>7b4227fc-3562-4ad5-8812-b7edfabe1728.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 05:38 PM</t>
+  </si>
+  <si>
+    <t>Rosamond Lie</t>
+  </si>
+  <si>
+    <t>MOND</t>
+  </si>
+  <si>
+    <t>WhatsApp Image 2026-06-29 at 11.17.34.jpeg</t>
+  </si>
+  <si>
+    <t>06/26/2026 06:14 PM</t>
+  </si>
+  <si>
+    <t>Denzel Ibrahim</t>
+  </si>
+  <si>
+    <t>DENZEL</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>IMG_1405.png</t>
+  </si>
+  <si>
+    <t>06/26/2026 08:01 PM</t>
+  </si>
+  <si>
+    <t>Clarissa Aditjakra</t>
+  </si>
+  <si>
+    <t>CACA</t>
+  </si>
+  <si>
+    <t>IMG_0376.png</t>
+  </si>
+  <si>
+    <t>06/27/2026 12:58 AM</t>
+  </si>
+  <si>
+    <t>Marcello Wijaya</t>
+  </si>
+  <si>
+    <t>Epos</t>
+  </si>
+  <si>
+    <t>IMG_2987.jpeg</t>
+  </si>
+  <si>
+    <t>06/27/2026 02:34 AM</t>
+  </si>
+  <si>
+    <t>Allethrine</t>
+  </si>
+  <si>
+    <t>IMG_5307.jpeg</t>
+  </si>
+  <si>
+    <t>06/27/2026 06:13 AM</t>
+  </si>
+  <si>
+    <t>Rachel Sinaga</t>
+  </si>
+  <si>
+    <t>achel</t>
+  </si>
+  <si>
+    <t>IMG_3978.jpeg</t>
+  </si>
+  <si>
+    <t>06/27/2026 06:28 AM</t>
+  </si>
+  <si>
+    <t>Gwen Yeanlynn</t>
+  </si>
+  <si>
+    <t>gwen</t>
+  </si>
+  <si>
+    <t>IMG_0844.jpeg</t>
+  </si>
+  <si>
+    <t>06/27/2026 02:12 PM</t>
+  </si>
+  <si>
+    <t>Muhammad Ilyas</t>
+  </si>
+  <si>
+    <t>ilyas</t>
+  </si>
+  <si>
+    <t>IMG_0402.png</t>
+  </si>
+  <si>
+    <t>06/27/2026 03:19 PM</t>
+  </si>
+  <si>
+    <t>Raihan Daniswara</t>
+  </si>
+  <si>
+    <t>DANISWARA</t>
+  </si>
+  <si>
+    <t>IMG_3348.jpeg</t>
+  </si>
+  <si>
+    <t>06/27/2026 03:22 PM</t>
+  </si>
+  <si>
+    <t>IMG_3349.jpeg</t>
+  </si>
+  <si>
+    <t>06/27/2026 04:11 PM</t>
+  </si>
+  <si>
+    <t>Bernardus William</t>
+  </si>
+  <si>
+    <t>BEWES</t>
+  </si>
+  <si>
+    <t>IMG_2174.jpeg</t>
+  </si>
+  <si>
+    <t>06/27/2026 06:07 PM</t>
+  </si>
+  <si>
+    <t>Laurentius Nicholas</t>
+  </si>
+  <si>
+    <t>Nick</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>IMG_5710.png</t>
+  </si>
+  <si>
+    <t>06/27/2026 07:00 PM</t>
+  </si>
+  <si>
+    <t>Brandon Haliman</t>
+  </si>
+  <si>
+    <t>BRNDN</t>
+  </si>
+  <si>
+    <t>IMG_2086.png</t>
+  </si>
+  <si>
+    <t>06/27/2026 11:21 PM</t>
+  </si>
+  <si>
+    <t>Sintani Gina Lestari</t>
+  </si>
+  <si>
+    <t>Ginaa</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>f01ed7ec-a296-41e5-98fc-7367ae8721d0.jpeg</t>
+  </si>
+  <si>
+    <t>06/28/2026 01:35 AM</t>
+  </si>
+  <si>
+    <t>Maria Angliwarman</t>
+  </si>
+  <si>
+    <t>c3aeb7f5-4b9b-42be-8021-d211211e5652.jpeg</t>
+  </si>
+  <si>
+    <t>06/28/2026 06:03 AM</t>
+  </si>
+  <si>
+    <t>Filipus Darren</t>
+  </si>
+  <si>
+    <t>Fildar</t>
+  </si>
+  <si>
+    <t>IMG_6532.png</t>
+  </si>
+  <si>
+    <t>06/28/2026 06:35 AM</t>
+  </si>
+  <si>
+    <t>06/28/2026 09:42 AM</t>
+  </si>
+  <si>
+    <t>Vigo Sie</t>
+  </si>
+  <si>
+    <t>VAX</t>
+  </si>
+  <si>
+    <t>IMG_0450.jpeg</t>
+  </si>
+  <si>
+    <t>06/28/2026 10:05 AM</t>
+  </si>
+  <si>
+    <t>Akbar</t>
+  </si>
+  <si>
+    <t>AKBARE</t>
+  </si>
+  <si>
+    <t>WhatsApp Image 2026-06-28 at 17.04.43.jpeg</t>
+  </si>
+  <si>
+    <t>06/28/2026 10:37 AM</t>
+  </si>
+  <si>
+    <t>Reynard Setiawan</t>
+  </si>
+  <si>
+    <t>Rey</t>
+  </si>
+  <si>
+    <t>f9d9b56c-b61d-4e1e-9dd8-0ebe6875f12d.jpeg</t>
+  </si>
+  <si>
+    <t>06/28/2026 10:42 AM</t>
+  </si>
+  <si>
+    <t>Mangga</t>
+  </si>
+  <si>
+    <t>3XL (+ Rp 20.000)</t>
+  </si>
+  <si>
+    <t>1520c837-8280-47d3-b8c8-e0c4d30fdedd.jpeg</t>
+  </si>
+  <si>
+    <t>06/28/2026 11:02 AM</t>
+  </si>
+  <si>
+    <t>Kaisa Mardi</t>
+  </si>
+  <si>
+    <t>KAI</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>06/28/2026 11:34 AM</t>
+  </si>
+  <si>
+    <t>Muthiara Aliyu</t>
+  </si>
+  <si>
+    <t>muthi</t>
+  </si>
+  <si>
+    <t>IMG_4330.png</t>
+  </si>
+  <si>
+    <t>06/28/2026 11:43 AM</t>
+  </si>
+  <si>
+    <t>Sabila Ph</t>
+  </si>
+  <si>
+    <t>WhatsApp Image 2026-06-28 at 18.42.07.jpeg</t>
+  </si>
+  <si>
+    <t>06/28/2026 12:09 PM</t>
+  </si>
+  <si>
+    <t>Samuel Winoto</t>
+  </si>
+  <si>
+    <t>MUMU</t>
+  </si>
+  <si>
+    <t>IMG_3689.png</t>
+  </si>
+  <si>
+    <t>06/28/2026 02:33 PM</t>
+  </si>
+  <si>
+    <t>Jayvin Silo</t>
+  </si>
+  <si>
+    <t>Jayvin</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>bdbdbc9f-ab10-4508-840b-2d97443938e7.jpeg</t>
+  </si>
+  <si>
+    <t>06/28/2026 02:45 PM</t>
+  </si>
+  <si>
+    <t>Catherine Danielle</t>
+  </si>
+  <si>
+    <t>cdanielle</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Screenshot 2026-06-28 at 21.45.08.png</t>
+  </si>
+  <si>
+    <t>06/28/2026 02:48 PM</t>
+  </si>
+  <si>
+    <t>Xaviero Loganta</t>
+  </si>
+  <si>
+    <t>Ahing</t>
+  </si>
+  <si>
+    <t>PHOTO-2026-06-28-21-48-10.jpg</t>
+  </si>
+  <si>
+    <t>06/28/2026 03:54 PM</t>
+  </si>
+  <si>
+    <t>Janice Wijono</t>
+  </si>
+  <si>
+    <t>JENS</t>
+  </si>
+  <si>
+    <t>IMG_4284.jpeg</t>
+  </si>
+  <si>
+    <t>06/28/2026 04:02 PM</t>
+  </si>
+  <si>
+    <t>Gabriella Wijaya</t>
+  </si>
+  <si>
+    <t>GABEE</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>IMG_0538.png</t>
+  </si>
+  <si>
+    <t>06/28/2026 04:31 PM</t>
+  </si>
+  <si>
+    <t>Putri Checilia</t>
+  </si>
+  <si>
+    <t>chelle</t>
+  </si>
+  <si>
+    <t>06/28/2026 04:54 PM</t>
+  </si>
+  <si>
+    <t>Brian Darmadi</t>
+  </si>
+  <si>
+    <t>Darmadi</t>
+  </si>
+  <si>
+    <t>image.pngimage.png</t>
+  </si>
+  <si>
+    <t>06/28/2026 05:00 PM</t>
+  </si>
+  <si>
+    <t>Farrell Haris</t>
+  </si>
+  <si>
+    <t>Farrell</t>
+  </si>
+  <si>
+    <t>2fbe904a-04b7-4031-b04f-17b1a703d31f.jpeg</t>
+  </si>
+  <si>
+    <t>Angela Immaculata</t>
+  </si>
+  <si>
+    <t>immaculata</t>
+  </si>
+  <si>
+    <t>IMG_3943.jpeg</t>
+  </si>
+  <si>
+    <t>06/28/2026 05:06 PM</t>
+  </si>
+  <si>
+    <t>Juniarta</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>transaction_details.png</t>
+  </si>
+  <si>
+    <t>06/28/2026 05:12 PM</t>
+  </si>
+  <si>
+    <t>Rasya Devansyah</t>
+  </si>
+  <si>
+    <t>IMG_2882.png</t>
+  </si>
+  <si>
+    <t>06/28/2026 05:34 PM</t>
+  </si>
+  <si>
+    <t>Alessandro Lawadinata</t>
+  </si>
+  <si>
+    <t>LAWADINATA</t>
+  </si>
+  <si>
+    <t>06/28/2026 05:43 PM</t>
+  </si>
+  <si>
+    <t>Jesslyn Edvilie</t>
+  </si>
+  <si>
+    <t>Trixie</t>
+  </si>
+  <si>
+    <t>06/28/2026 05:52 PM</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:21 AM</t>
+  </si>
+  <si>
+    <t>Khalisha Khansa</t>
+  </si>
+  <si>
+    <t>khali</t>
+  </si>
+  <si>
+    <t>IMG_0669E25C8222-1.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:33 AM</t>
+  </si>
+  <si>
+    <t>Michelle Nathania</t>
+  </si>
+  <si>
+    <t>MICI</t>
+  </si>
+  <si>
+    <t>Michelle Nathania_Proof of Payment.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:52 AM</t>
+  </si>
+  <si>
+    <t>Valentino Triadi</t>
+  </si>
+  <si>
+    <t>VCT</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>IMG_1304.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 02:07 AM</t>
+  </si>
+  <si>
+    <t>Belmiro</t>
+  </si>
+  <si>
+    <t>IMG_2996.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 02:31 AM</t>
+  </si>
+  <si>
+    <t>Kenrich Sandria</t>
+  </si>
+  <si>
+    <t>Ken</t>
+  </si>
+  <si>
+    <t>IMG_2042.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 02:33 AM</t>
+  </si>
+  <si>
+    <t>Naufal Rauf</t>
+  </si>
+  <si>
+    <t>JATENG</t>
+  </si>
+  <si>
+    <t>IMG_8766.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 02:35 AM</t>
+  </si>
+  <si>
+    <t>Grace Frendy</t>
+  </si>
+  <si>
+    <t>GTES</t>
+  </si>
+  <si>
+    <t>IMG_0695.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 02:36 AM</t>
+  </si>
+  <si>
+    <t>FTED</t>
+  </si>
+  <si>
+    <t>06/29/2026 02:57 AM</t>
+  </si>
+  <si>
+    <t>Agnetta Indira Revata</t>
+  </si>
+  <si>
+    <t>AIR</t>
+  </si>
+  <si>
+    <t>WhatsApp Image 2026-06-29 at 09.56.18.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 03:46 AM</t>
+  </si>
+  <si>
+    <t>Albert Harison</t>
+  </si>
+  <si>
+    <t>Albert</t>
+  </si>
+  <si>
+    <t>WhatsApp Image 2026-06-29 at 10.43.13.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 04:17 AM</t>
+  </si>
+  <si>
+    <t>Harley Ganisson</t>
+  </si>
+  <si>
+    <t>Ley</t>
+  </si>
+  <si>
+    <t>IMG_1327.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 04:20 AM</t>
+  </si>
+  <si>
+    <t>Priska Aimee Likarsa</t>
+  </si>
+  <si>
+    <t>pika</t>
+  </si>
+  <si>
+    <t>896ce62d-07a7-4891-a8a9-dc416459174b.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 05:22 AM</t>
+  </si>
+  <si>
+    <t>Ananda Purwanto</t>
+  </si>
+  <si>
+    <t>Nanduy</t>
+  </si>
+  <si>
+    <t>IMG_2674.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 05:44 AM</t>
+  </si>
+  <si>
+    <t>Miranda Khairunnisa</t>
+  </si>
+  <si>
+    <t>MIRA</t>
+  </si>
+  <si>
+    <t>IMG_331CC1675D75-1.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 06:11 AM</t>
+  </si>
+  <si>
+    <t>Ananta Tharifah</t>
+  </si>
+  <si>
+    <t>Ananta G</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>IMG_6385.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 07:01 AM</t>
+  </si>
+  <si>
+    <t>Daffa Zayyan</t>
+  </si>
+  <si>
+    <t>Jersey Daffa Z.JPG</t>
+  </si>
+  <si>
+    <t>06/29/2026 07:07 AM</t>
+  </si>
+  <si>
+    <t>William Lourensius</t>
+  </si>
+  <si>
+    <t>IMG_0566.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 07:22 AM</t>
+  </si>
+  <si>
+    <t>Ignatius Ivan Wijaya</t>
+  </si>
+  <si>
+    <t>I I WIJAYA</t>
+  </si>
+  <si>
+    <t>IMG_5529.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 08:40 AM</t>
+  </si>
+  <si>
+    <t>Tegar Priambodo</t>
+  </si>
+  <si>
+    <t>Girr</t>
+  </si>
+  <si>
+    <t>IMG_4837.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 08:44 AM</t>
+  </si>
+  <si>
+    <t>IMG_4839.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 09:00 AM</t>
+  </si>
+  <si>
+    <t>Riyan Amerta</t>
+  </si>
+  <si>
+    <t>Amerta</t>
+  </si>
+  <si>
+    <t>IMG_1702.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 09:19 AM</t>
+  </si>
+  <si>
+    <t>Willy Tanuwijaya</t>
+  </si>
+  <si>
+    <t>Willy</t>
+  </si>
+  <si>
+    <t>IMG_0660.PNG</t>
+  </si>
+  <si>
+    <t>06/29/2026 09:34 AM</t>
+  </si>
+  <si>
+    <t>Sapta Pradana</t>
+  </si>
+  <si>
+    <t>Sapta</t>
+  </si>
+  <si>
+    <t>Jersey Sapta.jpg</t>
+  </si>
+  <si>
+    <t>06/29/2026 11:16 AM</t>
+  </si>
+  <si>
+    <t>Muhammad Deyis</t>
+  </si>
+  <si>
+    <t>oliver</t>
+  </si>
+  <si>
+    <t>image.jpgimage.jpg</t>
+  </si>
+  <si>
+    <t>06/29/2026 11:54 AM</t>
+  </si>
+  <si>
+    <t>Liecardo Antonio</t>
+  </si>
+  <si>
+    <t>Liecrd</t>
+  </si>
+  <si>
+    <t>IMG_1589.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 11:55 AM</t>
+  </si>
+  <si>
+    <t>Nayyara Safrilia</t>
+  </si>
+  <si>
+    <t>nayra</t>
+  </si>
+  <si>
+    <t>IMG_8094.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 11:59 AM</t>
+  </si>
+  <si>
+    <t>Kevin Handoyo</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>IMG_3494.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 12:07 PM</t>
+  </si>
+  <si>
+    <t>Teresa Tania Tamsil</t>
+  </si>
+  <si>
+    <t>Tania</t>
+  </si>
+  <si>
+    <t>IMG_8817.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 12:22 PM</t>
+  </si>
+  <si>
+    <t>Rayhan Nanda</t>
+  </si>
+  <si>
+    <t>Lim Yoona</t>
+  </si>
+  <si>
+    <t>dc42a9b5-c61e-49b0-8e48-e1016263da20.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 12:50 PM</t>
+  </si>
+  <si>
+    <t>Tasya Pandya</t>
+  </si>
+  <si>
+    <t>tasya</t>
+  </si>
+  <si>
+    <t>IMG_1427.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 12:53 PM</t>
+  </si>
+  <si>
+    <t>Arkansyah Setiawan</t>
+  </si>
+  <si>
+    <t>ARK</t>
+  </si>
+  <si>
+    <t>WhatsApp Image 2026-06-29 at 19.50.56.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:08 PM</t>
+  </si>
+  <si>
+    <t>Vannya Gunawan</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>WhatsApp Image 2026-06-29 at 19.24.46.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:10 PM</t>
+  </si>
+  <si>
+    <t>Muhammad Abidin</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>IMG_1294.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:15 PM</t>
+  </si>
+  <si>
+    <t>Benedicta Sutandyo</t>
+  </si>
+  <si>
+    <t>Joy</t>
+  </si>
+  <si>
+    <t>Jersey Joyce.PNG</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:18 PM</t>
+  </si>
+  <si>
+    <t>Benaya Given Janto</t>
+  </si>
+  <si>
+    <t>BEN</t>
+  </si>
+  <si>
+    <t>IMG_2137.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:21 PM</t>
+  </si>
+  <si>
+    <t>Stanley Pratama Teguh</t>
+  </si>
+  <si>
+    <t>Stanley</t>
+  </si>
+  <si>
+    <t>7edcee91-2c67-4acf-bef7-c8c2f00bad4d.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:27 PM</t>
+  </si>
+  <si>
+    <t>Deviana Natalia</t>
+  </si>
+  <si>
+    <t>Deviana</t>
+  </si>
+  <si>
+    <t>0063ff78-8c17-4363-9d2f-f70f5d444106.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:39 PM</t>
+  </si>
+  <si>
+    <t>Sayyidah Azzahra</t>
+  </si>
+  <si>
+    <t>Zahra</t>
+  </si>
+  <si>
+    <t>Jago_receipt_39-29-2026 08-39@260629JAGBIDJA00241325.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:48 PM</t>
+  </si>
+  <si>
+    <t>Rendi Septrian</t>
+  </si>
+  <si>
+    <t>Rendi</t>
+  </si>
+  <si>
+    <t>IMG_3785.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:51 PM</t>
+  </si>
+  <si>
+    <t>Ririn Riani</t>
+  </si>
+  <si>
+    <t>RIRIN</t>
+  </si>
+  <si>
+    <t>Jersey Ririn.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:55 PM</t>
+  </si>
+  <si>
+    <t>Fairuz Ismayana</t>
+  </si>
+  <si>
+    <t>Sloth</t>
+  </si>
+  <si>
+    <t>Jersey Faiz.JPG</t>
+  </si>
+  <si>
+    <t>06/29/2026 01:57 PM</t>
+  </si>
+  <si>
+    <t>Jeson Dharma</t>
+  </si>
+  <si>
+    <t>Jeson</t>
+  </si>
+  <si>
+    <t>IMG_62F0DCE6B558-1.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 02:24 PM</t>
+  </si>
+  <si>
+    <t>Vya</t>
+  </si>
+  <si>
+    <t>083eb7b3-614b-43d0-9185-593ef7a31d85.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 02:38 PM</t>
+  </si>
+  <si>
+    <t>Teo Apriyandi</t>
+  </si>
+  <si>
+    <t>Teo</t>
+  </si>
+  <si>
+    <t>06/29/2026 02:50 PM</t>
+  </si>
+  <si>
+    <t>Samantha Niandra</t>
+  </si>
+  <si>
+    <t>SAM</t>
+  </si>
+  <si>
+    <t>0f9fc15c-f156-4b18-9620-53ba207b9407.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 03:00 PM</t>
+  </si>
+  <si>
+    <t>Kezia Tandapai</t>
+  </si>
+  <si>
+    <t>Kezia</t>
+  </si>
+  <si>
+    <t>IMG_2226.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 03:05 PM</t>
+  </si>
+  <si>
+    <t>Beata Daneswari</t>
+  </si>
+  <si>
+    <t>Beata</t>
+  </si>
+  <si>
+    <t>Screenshot 2026-06-29 at 22.04.36.heic</t>
+  </si>
+  <si>
+    <t>06/29/2026 03:18 PM</t>
+  </si>
+  <si>
+    <t>Naila Lauza</t>
+  </si>
+  <si>
+    <t>NAI</t>
+  </si>
+  <si>
+    <t>IMG_5290.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 03:32 PM</t>
+  </si>
+  <si>
+    <t>Daud Dimas P</t>
+  </si>
+  <si>
+    <t>DAVIDE</t>
+  </si>
+  <si>
+    <t>IMG_6449.JPG</t>
+  </si>
+  <si>
+    <t>06/29/2026 03:33 PM</t>
+  </si>
+  <si>
+    <t>Jonathan Basuki</t>
+  </si>
+  <si>
+    <t>Jonathan</t>
+  </si>
+  <si>
+    <t>27e266f2-3c1e-46f9-bcea-cfbdcd70b9d7.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 04:06 PM</t>
+  </si>
+  <si>
+    <t>Haikal Izzanour</t>
+  </si>
+  <si>
+    <t>Lingard</t>
+  </si>
+  <si>
+    <t>IMG_2222.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 04:24 PM</t>
+  </si>
+  <si>
+    <t>Jessica Selistio</t>
+  </si>
+  <si>
+    <t>Jeli</t>
+  </si>
+  <si>
+    <t>IMG_1353.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 04:27 PM</t>
+  </si>
+  <si>
+    <t>Sebastian Darren</t>
+  </si>
+  <si>
+    <t>SEBA</t>
+  </si>
+  <si>
+    <t>PHOTO-2026-06-29-23-27-26.jpg</t>
+  </si>
+  <si>
+    <t>06/29/2026 04:32 PM</t>
+  </si>
+  <si>
+    <t>Syukra Ramadhan</t>
+  </si>
+  <si>
+    <t>JERSEY SYUKRA.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 04:34 PM</t>
+  </si>
+  <si>
+    <t>Rio Ferdian</t>
+  </si>
+  <si>
+    <t>LAMPUNG</t>
+  </si>
+  <si>
+    <t>Screenshot_20260629-233149.myBCA.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 04:35 PM</t>
+  </si>
+  <si>
+    <t>BANTEN</t>
+  </si>
+  <si>
+    <t>Screenshot_2026-06-29-23-34-47-892_id.co.bankbkemobile.digitalbank.jpg</t>
+  </si>
+  <si>
+    <t>06/29/2026 04:39 PM</t>
+  </si>
+  <si>
+    <t>Dimas Aryawan</t>
+  </si>
+  <si>
+    <t>IMG_1009.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 04:41 PM</t>
+  </si>
+  <si>
+    <t>Azis Hardy</t>
+  </si>
+  <si>
+    <t>Hardy</t>
+  </si>
+  <si>
+    <t>1F29400F-2ABE-4F91-8E1C-64703C2F5854.jpeg</t>
+  </si>
+  <si>
+    <t>Jatayu Wicaksono</t>
+  </si>
+  <si>
+    <t>JATIM</t>
+  </si>
+  <si>
+    <t>IMG_2477.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 04:54 PM</t>
+  </si>
+  <si>
+    <t>Feivel Qutby</t>
+  </si>
+  <si>
+    <t>FEIVEL</t>
+  </si>
+  <si>
+    <t>Screenshot 2026-06-29 at 11.53.36 PM.png</t>
+  </si>
+  <si>
+    <t>Kevin Halim</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>IMG_0741.jpg</t>
+  </si>
+  <si>
+    <t>06/29/2026 05:02 PM</t>
+  </si>
+  <si>
+    <t>Carleano Ravelza Wongso</t>
+  </si>
+  <si>
+    <t>Ravel</t>
+  </si>
+  <si>
+    <t>IMG_2235.png</t>
+  </si>
+  <si>
+    <t>06/29/2026 06:23 PM</t>
+  </si>
+  <si>
+    <t>Adri Putra</t>
+  </si>
+  <si>
+    <t>Adri</t>
+  </si>
+  <si>
+    <t>cbbaed3e-6458-4f1e-863e-95fd1a410541.jpeg</t>
+  </si>
+  <si>
+    <t>06/29/2026 06:46 PM</t>
+  </si>
+  <si>
+    <t>Nabiel Ardhityo</t>
+  </si>
+  <si>
+    <t>BIEL</t>
+  </si>
+  <si>
+    <t>IMG_6901.PNG</t>
+  </si>
+  <si>
+    <t>06/29/2026 07:04 PM</t>
+  </si>
+  <si>
+    <t>Abraar Hibatullah</t>
+  </si>
+  <si>
+    <t>ABEAR</t>
+  </si>
+  <si>
+    <t>IMG_2431.jpeg</t>
+  </si>
+  <si>
+    <t>06/30/2026 01:09 AM</t>
+  </si>
+  <si>
+    <t>Michael Mintje</t>
+  </si>
+  <si>
+    <t>Mike</t>
+  </si>
+  <si>
+    <t>Screenshot 2026-06-30 at 08.08.50.heic</t>
+  </si>
+  <si>
+    <t>06/30/2026 03:03 AM</t>
+  </si>
+  <si>
+    <t>Yuki Damanik</t>
+  </si>
+  <si>
+    <t>YUKI</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>IMG_2056.png</t>
+  </si>
+  <si>
+    <t>06/30/2026 06:40 AM</t>
+  </si>
+  <si>
+    <t>KALTENG</t>
+  </si>
+  <si>
+    <t>IMG_0568.png</t>
+  </si>
+  <si>
+    <t>06/30/2026 07:37 AM</t>
+  </si>
+  <si>
+    <t>Lidia Julean</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>WhatsApp Image 2026-06-30 at 14.34.35.jpeg</t>
+  </si>
+  <si>
+    <t>06/30/2026 07:40 AM</t>
+  </si>
+  <si>
+    <t>Reynard Lie</t>
+  </si>
+  <si>
+    <t>REY</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Transaksi_BCAmobile-20260630-143803.jpeg</t>
+  </si>
+  <si>
+    <t>06/30/2026 07:47 AM</t>
+  </si>
+  <si>
+    <t>Matthew Hutabarat</t>
+  </si>
+  <si>
+    <t>NgokNgok</t>
+  </si>
+  <si>
+    <t>WhatsApp Image 2026-06-30 at 14.46.41.jpeg</t>
+  </si>
+  <si>
+    <t>06/30/2026 09:49 AM</t>
+  </si>
+  <si>
+    <t>Rafi Favian</t>
+  </si>
+  <si>
+    <t>Papiann</t>
+  </si>
+  <si>
+    <t>Jersey Apple - Rafi.jpeg</t>
+  </si>
+  <si>
+    <t>06/30/2026 12:49 PM</t>
+  </si>
+  <si>
+    <t>Michael Ginting</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>JPEG image-42F0-A94D-A4-0.jpeg</t>
+  </si>
+  <si>
+    <t>07/01/2026 02:29 AM</t>
+  </si>
+  <si>
+    <t>L Erwin Saputra</t>
+  </si>
+  <si>
+    <t>IMG_0501.jpeg</t>
+  </si>
+  <si>
+    <t>07/01/2026 06:10 AM</t>
+  </si>
+  <si>
+    <t>IMG_3021.PNG</t>
+  </si>
+  <si>
+    <t>07/01/2026 11:35 AM</t>
+  </si>
+  <si>
+    <t>Rizqi Widianto</t>
+  </si>
+  <si>
+    <t>MARNO BENGKEL</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>IMG_2902.jpeg</t>
+  </si>
+  <si>
+    <t>07/01/2026 11:53 AM</t>
+  </si>
+  <si>
+    <t>Eko Cahyo Prihantoro</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>IMG_3374.png</t>
+  </si>
+  <si>
+    <t>07/01/2026 12:11 PM</t>
+  </si>
+  <si>
+    <t>Gading Perdana</t>
+  </si>
+  <si>
+    <t>GADING</t>
+  </si>
+  <si>
+    <t>IMG_3818.jpeg</t>
+  </si>
+  <si>
+    <t>07/01/2026 12:12 PM</t>
+  </si>
+  <si>
+    <t>Danniel Ang</t>
+  </si>
+  <si>
+    <t>RIAU</t>
+  </si>
+  <si>
+    <t>JPEG image-4834-90F2-79-0.jpeg</t>
+  </si>
+  <si>
+    <t>07/01/2026 04:25 PM</t>
   </si>
   <si>
     <t>Ernesta Felicia</t>
@@ -901,1543 +2440,7 @@
     <t>sta</t>
   </si>
   <si>
-    <t>06/26/2026 02:10 PM</t>
-  </si>
-  <si>
-    <t>Filbert Naldo Wijaya</t>
-  </si>
-  <si>
-    <t>FILBERT</t>
-  </si>
-  <si>
-    <t>IMG_0563.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 02:15 PM</t>
-  </si>
-  <si>
-    <t>Naufal Fahri</t>
-  </si>
-  <si>
-    <t>Naufal</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>IMG_2030.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 02:36 PM</t>
-  </si>
-  <si>
-    <t>Gabriel Budiman</t>
-  </si>
-  <si>
-    <t>Gabriel J</t>
-  </si>
-  <si>
-    <t>IMG_1974.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 02:40 PM</t>
-  </si>
-  <si>
-    <t>Gianina Christophilus</t>
-  </si>
-  <si>
-    <t>C9S1-40</t>
-  </si>
-  <si>
-    <t>IMG_5305.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 02:55 PM</t>
-  </si>
-  <si>
-    <t>Tiffany Michelle</t>
-  </si>
-  <si>
-    <t>TMS</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>IMG_2655.JPG</t>
-  </si>
-  <si>
-    <t>06/26/2026 03:11 PM</t>
-  </si>
-  <si>
-    <t>Graceila Natasya</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>IMG_3915.png</t>
-  </si>
-  <si>
-    <t>06/26/2026 03:29 PM</t>
-  </si>
-  <si>
-    <t>IMG_3772.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 03:37 PM</t>
-  </si>
-  <si>
-    <t>Stepanus Imanuel</t>
-  </si>
-  <si>
-    <t>el</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>06/26/2026 03:57 PM</t>
-  </si>
-  <si>
-    <t>IMG_1636.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 04:12 PM</t>
-  </si>
-  <si>
-    <t>Patricia Gautama</t>
-  </si>
-  <si>
-    <t>CYAK</t>
-  </si>
-  <si>
-    <t>2141cce6-a74b-4481-836b-a1532c64a654.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 04:13 PM</t>
-  </si>
-  <si>
-    <t>06/26/2026 04:20 PM</t>
-  </si>
-  <si>
-    <t>Rio Ferdinand</t>
-  </si>
-  <si>
-    <t>FERDINAND</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>IMG_2045.png</t>
-  </si>
-  <si>
-    <t>06/26/2026 04:22 PM</t>
-  </si>
-  <si>
-    <t>Joey Martin</t>
-  </si>
-  <si>
-    <t>Joey</t>
-  </si>
-  <si>
-    <t>IMG_2168.png</t>
-  </si>
-  <si>
-    <t>06/26/2026 04:26 PM</t>
-  </si>
-  <si>
-    <t>Jacqueline Iman</t>
-  </si>
-  <si>
-    <t>Jacqueline</t>
-  </si>
-  <si>
-    <t>WhatsApp Image 2026-06-26 at 23.06.00.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 04:41 PM</t>
-  </si>
-  <si>
-    <t>Dimas Ismaunnizam</t>
-  </si>
-  <si>
-    <t>MYZWAN</t>
-  </si>
-  <si>
-    <t>IMG_1811.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 04:42 PM</t>
-  </si>
-  <si>
-    <t>Devi Sujata</t>
-  </si>
-  <si>
-    <t>IMG_6353.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 05:08 PM</t>
-  </si>
-  <si>
-    <t>Michelle Roring</t>
-  </si>
-  <si>
-    <t>Misyel</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>7b4227fc-3562-4ad5-8812-b7edfabe1728.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 05:38 PM</t>
-  </si>
-  <si>
-    <t>Rosamond Lie</t>
-  </si>
-  <si>
-    <t>MOND</t>
-  </si>
-  <si>
-    <t>WhatsApp Image 2026-06-29 at 11.17.34.jpeg</t>
-  </si>
-  <si>
-    <t>06/26/2026 06:14 PM</t>
-  </si>
-  <si>
-    <t>Denzel Ibrahim</t>
-  </si>
-  <si>
-    <t>DENZEL</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>IMG_1405.png</t>
-  </si>
-  <si>
-    <t>06/26/2026 08:01 PM</t>
-  </si>
-  <si>
-    <t>Clarissa Aditjakra</t>
-  </si>
-  <si>
-    <t>CACA</t>
-  </si>
-  <si>
-    <t>IMG_0376.png</t>
-  </si>
-  <si>
-    <t>06/27/2026 12:58 AM</t>
-  </si>
-  <si>
-    <t>Marcello Wijaya</t>
-  </si>
-  <si>
-    <t>Epos</t>
-  </si>
-  <si>
-    <t>IMG_2987.jpeg</t>
-  </si>
-  <si>
-    <t>06/27/2026 02:34 AM</t>
-  </si>
-  <si>
-    <t>Allethrine</t>
-  </si>
-  <si>
-    <t>IMG_5307.jpeg</t>
-  </si>
-  <si>
-    <t>06/27/2026 06:13 AM</t>
-  </si>
-  <si>
-    <t>Rachel Sinaga</t>
-  </si>
-  <si>
-    <t>achel</t>
-  </si>
-  <si>
-    <t>IMG_3978.jpeg</t>
-  </si>
-  <si>
-    <t>06/27/2026 06:28 AM</t>
-  </si>
-  <si>
-    <t>Gwen Yeanlynn</t>
-  </si>
-  <si>
-    <t>gwen</t>
-  </si>
-  <si>
-    <t>IMG_0844.jpeg</t>
-  </si>
-  <si>
-    <t>06/27/2026 02:12 PM</t>
-  </si>
-  <si>
-    <t>Muhammad Ilyas</t>
-  </si>
-  <si>
-    <t>ilyas</t>
-  </si>
-  <si>
-    <t>IMG_0402.png</t>
-  </si>
-  <si>
-    <t>06/27/2026 03:19 PM</t>
-  </si>
-  <si>
-    <t>Raihan Daniswara</t>
-  </si>
-  <si>
-    <t>DANISWARA</t>
-  </si>
-  <si>
-    <t>IMG_3348.jpeg</t>
-  </si>
-  <si>
-    <t>06/27/2026 03:22 PM</t>
-  </si>
-  <si>
-    <t>IMG_3349.jpeg</t>
-  </si>
-  <si>
-    <t>06/27/2026 04:11 PM</t>
-  </si>
-  <si>
-    <t>Bernardus William</t>
-  </si>
-  <si>
-    <t>BEWES</t>
-  </si>
-  <si>
-    <t>IMG_2174.jpeg</t>
-  </si>
-  <si>
-    <t>06/27/2026 06:07 PM</t>
-  </si>
-  <si>
-    <t>Laurentius Nicholas</t>
-  </si>
-  <si>
-    <t>Nick</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>IMG_5710.png</t>
-  </si>
-  <si>
-    <t>06/27/2026 07:00 PM</t>
-  </si>
-  <si>
-    <t>Brandon Haliman</t>
-  </si>
-  <si>
-    <t>BRNDN</t>
-  </si>
-  <si>
-    <t>IMG_2086.png</t>
-  </si>
-  <si>
-    <t>06/27/2026 11:21 PM</t>
-  </si>
-  <si>
-    <t>Sintani Gina Lestari</t>
-  </si>
-  <si>
-    <t>Ginaa</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>f01ed7ec-a296-41e5-98fc-7367ae8721d0.jpeg</t>
-  </si>
-  <si>
-    <t>06/28/2026 01:35 AM</t>
-  </si>
-  <si>
-    <t>Maria Angliwarman</t>
-  </si>
-  <si>
-    <t>c3aeb7f5-4b9b-42be-8021-d211211e5652.jpeg</t>
-  </si>
-  <si>
-    <t>06/28/2026 06:03 AM</t>
-  </si>
-  <si>
-    <t>Filipus Darren</t>
-  </si>
-  <si>
-    <t>Fildar</t>
-  </si>
-  <si>
-    <t>IMG_6532.png</t>
-  </si>
-  <si>
-    <t>06/28/2026 06:35 AM</t>
-  </si>
-  <si>
-    <t>06/28/2026 09:42 AM</t>
-  </si>
-  <si>
-    <t>Vigo Sie</t>
-  </si>
-  <si>
-    <t>VAX</t>
-  </si>
-  <si>
-    <t>IMG_0450.jpeg</t>
-  </si>
-  <si>
-    <t>06/28/2026 10:05 AM</t>
-  </si>
-  <si>
-    <t>Akbar</t>
-  </si>
-  <si>
-    <t>AKBARE</t>
-  </si>
-  <si>
-    <t>WhatsApp Image 2026-06-28 at 17.04.43.jpeg</t>
-  </si>
-  <si>
-    <t>06/28/2026 10:37 AM</t>
-  </si>
-  <si>
-    <t>Reynard Setiawan</t>
-  </si>
-  <si>
-    <t>Rey</t>
-  </si>
-  <si>
-    <t>f9d9b56c-b61d-4e1e-9dd8-0ebe6875f12d.jpeg</t>
-  </si>
-  <si>
-    <t>06/28/2026 10:42 AM</t>
-  </si>
-  <si>
-    <t>Mangga</t>
-  </si>
-  <si>
-    <t>3XL (+ Rp 20.000)</t>
-  </si>
-  <si>
-    <t>1520c837-8280-47d3-b8c8-e0c4d30fdedd.jpeg</t>
-  </si>
-  <si>
-    <t>06/28/2026 11:02 AM</t>
-  </si>
-  <si>
-    <t>Kaisa Mardi</t>
-  </si>
-  <si>
-    <t>KAI</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>06/28/2026 11:34 AM</t>
-  </si>
-  <si>
-    <t>Muthiara Aliyu</t>
-  </si>
-  <si>
-    <t>muthi</t>
-  </si>
-  <si>
-    <t>IMG_4330.png</t>
-  </si>
-  <si>
-    <t>06/28/2026 11:43 AM</t>
-  </si>
-  <si>
-    <t>Sabila Ph</t>
-  </si>
-  <si>
-    <t>WhatsApp Image 2026-06-28 at 18.42.07.jpeg</t>
-  </si>
-  <si>
-    <t>06/28/2026 12:09 PM</t>
-  </si>
-  <si>
-    <t>Samuel Winoto</t>
-  </si>
-  <si>
-    <t>MUMU</t>
-  </si>
-  <si>
-    <t>IMG_3689.png</t>
-  </si>
-  <si>
-    <t>06/28/2026 02:33 PM</t>
-  </si>
-  <si>
-    <t>Jayvin Silo</t>
-  </si>
-  <si>
-    <t>Jayvin</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>bdbdbc9f-ab10-4508-840b-2d97443938e7.jpeg</t>
-  </si>
-  <si>
-    <t>06/28/2026 02:45 PM</t>
-  </si>
-  <si>
-    <t>Catherine Danielle</t>
-  </si>
-  <si>
-    <t>cdanielle</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Screenshot 2026-06-28 at 21.45.08.png</t>
-  </si>
-  <si>
-    <t>06/28/2026 02:48 PM</t>
-  </si>
-  <si>
-    <t>Xaviero Loganta</t>
-  </si>
-  <si>
-    <t>Ahing</t>
-  </si>
-  <si>
-    <t>PHOTO-2026-06-28-21-48-10.jpg</t>
-  </si>
-  <si>
-    <t>06/28/2026 03:54 PM</t>
-  </si>
-  <si>
-    <t>Janice Wijono</t>
-  </si>
-  <si>
-    <t>JENS</t>
-  </si>
-  <si>
-    <t>IMG_4284.jpeg</t>
-  </si>
-  <si>
-    <t>06/28/2026 04:02 PM</t>
-  </si>
-  <si>
-    <t>Gabriella Wijaya</t>
-  </si>
-  <si>
-    <t>GABEE</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>IMG_0538.png</t>
-  </si>
-  <si>
-    <t>06/28/2026 04:31 PM</t>
-  </si>
-  <si>
-    <t>Putri Checilia</t>
-  </si>
-  <si>
-    <t>chelle</t>
-  </si>
-  <si>
-    <t>06/28/2026 04:54 PM</t>
-  </si>
-  <si>
-    <t>Brian Darmadi</t>
-  </si>
-  <si>
-    <t>Darmadi</t>
-  </si>
-  <si>
-    <t>image.pngimage.png</t>
-  </si>
-  <si>
-    <t>06/28/2026 05:00 PM</t>
-  </si>
-  <si>
-    <t>Farrell Haris</t>
-  </si>
-  <si>
-    <t>Farrell</t>
-  </si>
-  <si>
-    <t>2fbe904a-04b7-4031-b04f-17b1a703d31f.jpeg</t>
-  </si>
-  <si>
-    <t>Angela Immaculata</t>
-  </si>
-  <si>
-    <t>immaculata</t>
-  </si>
-  <si>
-    <t>IMG_3943.jpeg</t>
-  </si>
-  <si>
-    <t>06/28/2026 05:06 PM</t>
-  </si>
-  <si>
-    <t>Juniarta</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>transaction_details.png</t>
-  </si>
-  <si>
-    <t>06/28/2026 05:12 PM</t>
-  </si>
-  <si>
-    <t>Rasya Devansyah</t>
-  </si>
-  <si>
-    <t>IMG_2882.png</t>
-  </si>
-  <si>
-    <t>06/28/2026 05:34 PM</t>
-  </si>
-  <si>
-    <t>Alessandro Lawadinata</t>
-  </si>
-  <si>
-    <t>LAWADINATA</t>
-  </si>
-  <si>
-    <t>06/28/2026 05:43 PM</t>
-  </si>
-  <si>
-    <t>Jesslyn Edvilie</t>
-  </si>
-  <si>
-    <t>Trixie</t>
-  </si>
-  <si>
-    <t>06/28/2026 05:52 PM</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:21 AM</t>
-  </si>
-  <si>
-    <t>Khalisha Khansa</t>
-  </si>
-  <si>
-    <t>khali</t>
-  </si>
-  <si>
-    <t>IMG_0669E25C8222-1.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:33 AM</t>
-  </si>
-  <si>
-    <t>Michelle Nathania</t>
-  </si>
-  <si>
-    <t>MICI</t>
-  </si>
-  <si>
-    <t>Michelle Nathania_Proof of Payment.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:52 AM</t>
-  </si>
-  <si>
-    <t>Valentino Triadi</t>
-  </si>
-  <si>
-    <t>VCT</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>IMG_1304.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 02:07 AM</t>
-  </si>
-  <si>
-    <t>Belmiro</t>
-  </si>
-  <si>
-    <t>IMG_2996.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 02:31 AM</t>
-  </si>
-  <si>
-    <t>Kenrich Sandria</t>
-  </si>
-  <si>
-    <t>Ken</t>
-  </si>
-  <si>
-    <t>IMG_2042.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 02:33 AM</t>
-  </si>
-  <si>
-    <t>Naufal Rauf</t>
-  </si>
-  <si>
-    <t>JATENG</t>
-  </si>
-  <si>
-    <t>IMG_8766.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 02:35 AM</t>
-  </si>
-  <si>
-    <t>Grace Frendy</t>
-  </si>
-  <si>
-    <t>GTES</t>
-  </si>
-  <si>
-    <t>IMG_0695.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 02:36 AM</t>
-  </si>
-  <si>
-    <t>FTED</t>
-  </si>
-  <si>
-    <t>06/29/2026 02:57 AM</t>
-  </si>
-  <si>
-    <t>Agnetta Indira Revata</t>
-  </si>
-  <si>
-    <t>AIR</t>
-  </si>
-  <si>
-    <t>WhatsApp Image 2026-06-29 at 09.56.18.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 03:46 AM</t>
-  </si>
-  <si>
-    <t>Albert Harison</t>
-  </si>
-  <si>
-    <t>Albert</t>
-  </si>
-  <si>
-    <t>WhatsApp Image 2026-06-29 at 10.43.13.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 04:17 AM</t>
-  </si>
-  <si>
-    <t>Harley Ganisson</t>
-  </si>
-  <si>
-    <t>Ley</t>
-  </si>
-  <si>
-    <t>IMG_1327.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 04:20 AM</t>
-  </si>
-  <si>
-    <t>Priska Aimee Likarsa</t>
-  </si>
-  <si>
-    <t>pika</t>
-  </si>
-  <si>
-    <t>896ce62d-07a7-4891-a8a9-dc416459174b.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 05:22 AM</t>
-  </si>
-  <si>
-    <t>Ananda Purwanto</t>
-  </si>
-  <si>
-    <t>Nanduy</t>
-  </si>
-  <si>
-    <t>IMG_2674.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 05:44 AM</t>
-  </si>
-  <si>
-    <t>Miranda Khairunnisa</t>
-  </si>
-  <si>
-    <t>MIRA</t>
-  </si>
-  <si>
-    <t>IMG_331CC1675D75-1.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 06:11 AM</t>
-  </si>
-  <si>
-    <t>Ananta Tharifah</t>
-  </si>
-  <si>
-    <t>Ananta G</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>IMG_6385.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 07:01 AM</t>
-  </si>
-  <si>
-    <t>Daffa Zayyan</t>
-  </si>
-  <si>
-    <t>Jersey Daffa Z.JPG</t>
-  </si>
-  <si>
-    <t>06/29/2026 07:07 AM</t>
-  </si>
-  <si>
-    <t>William Lourensius</t>
-  </si>
-  <si>
-    <t>IMG_0566.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 07:22 AM</t>
-  </si>
-  <si>
-    <t>Ignatius Ivan Wijaya</t>
-  </si>
-  <si>
-    <t>I I WIJAYA</t>
-  </si>
-  <si>
-    <t>IMG_5529.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 08:40 AM</t>
-  </si>
-  <si>
-    <t>Tegar Priambodo</t>
-  </si>
-  <si>
-    <t>Girr</t>
-  </si>
-  <si>
-    <t>IMG_4837.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 08:44 AM</t>
-  </si>
-  <si>
-    <t>IMG_4839.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 09:00 AM</t>
-  </si>
-  <si>
-    <t>Riyan Amerta</t>
-  </si>
-  <si>
-    <t>Amerta</t>
-  </si>
-  <si>
-    <t>IMG_1702.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 09:19 AM</t>
-  </si>
-  <si>
-    <t>Willy Tanuwijaya</t>
-  </si>
-  <si>
-    <t>Willy</t>
-  </si>
-  <si>
-    <t>IMG_0660.PNG</t>
-  </si>
-  <si>
-    <t>06/29/2026 09:34 AM</t>
-  </si>
-  <si>
-    <t>Sapta Pradana</t>
-  </si>
-  <si>
-    <t>Sapta</t>
-  </si>
-  <si>
-    <t>Jersey Sapta.jpg</t>
-  </si>
-  <si>
-    <t>06/29/2026 11:16 AM</t>
-  </si>
-  <si>
-    <t>Muhammad Deyis</t>
-  </si>
-  <si>
-    <t>oliver</t>
-  </si>
-  <si>
-    <t>image.jpgimage.jpg</t>
-  </si>
-  <si>
-    <t>06/29/2026 11:54 AM</t>
-  </si>
-  <si>
-    <t>Liecardo Antonio</t>
-  </si>
-  <si>
-    <t>Liecrd</t>
-  </si>
-  <si>
-    <t>IMG_1589.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 11:55 AM</t>
-  </si>
-  <si>
-    <t>Nayyara Safrilia</t>
-  </si>
-  <si>
-    <t>nayra</t>
-  </si>
-  <si>
-    <t>IMG_8094.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 11:59 AM</t>
-  </si>
-  <si>
-    <t>Kevin Handoyo</t>
-  </si>
-  <si>
-    <t>Joseph</t>
-  </si>
-  <si>
-    <t>IMG_3494.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 12:07 PM</t>
-  </si>
-  <si>
-    <t>Teresa Tania Tamsil</t>
-  </si>
-  <si>
-    <t>Tania</t>
-  </si>
-  <si>
-    <t>IMG_8817.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 12:22 PM</t>
-  </si>
-  <si>
-    <t>Rayhan Nanda</t>
-  </si>
-  <si>
-    <t>Lim Yoona</t>
-  </si>
-  <si>
-    <t>dc42a9b5-c61e-49b0-8e48-e1016263da20.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 12:50 PM</t>
-  </si>
-  <si>
-    <t>Tasya Pandya</t>
-  </si>
-  <si>
-    <t>tasya</t>
-  </si>
-  <si>
-    <t>IMG_1427.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 12:53 PM</t>
-  </si>
-  <si>
-    <t>Arkansyah Setiawan</t>
-  </si>
-  <si>
-    <t>ARK</t>
-  </si>
-  <si>
-    <t>WhatsApp Image 2026-06-29 at 19.50.56.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:08 PM</t>
-  </si>
-  <si>
-    <t>Vannya Gunawan</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>WhatsApp Image 2026-06-29 at 19.24.46.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:10 PM</t>
-  </si>
-  <si>
-    <t>Muhammad Abidin</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>IMG_1294.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:15 PM</t>
-  </si>
-  <si>
-    <t>Benedicta Sutandyo</t>
-  </si>
-  <si>
-    <t>Joy</t>
-  </si>
-  <si>
-    <t>Jersey Joyce.PNG</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:18 PM</t>
-  </si>
-  <si>
-    <t>Benaya Given Janto</t>
-  </si>
-  <si>
-    <t>BEN</t>
-  </si>
-  <si>
-    <t>IMG_2137.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:21 PM</t>
-  </si>
-  <si>
-    <t>Stanley Pratama Teguh</t>
-  </si>
-  <si>
-    <t>Stanley</t>
-  </si>
-  <si>
-    <t>7edcee91-2c67-4acf-bef7-c8c2f00bad4d.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:27 PM</t>
-  </si>
-  <si>
-    <t>Deviana Natalia</t>
-  </si>
-  <si>
-    <t>Deviana</t>
-  </si>
-  <si>
-    <t>0063ff78-8c17-4363-9d2f-f70f5d444106.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:39 PM</t>
-  </si>
-  <si>
-    <t>Sayyidah Azzahra</t>
-  </si>
-  <si>
-    <t>Zahra</t>
-  </si>
-  <si>
-    <t>Jago_receipt_39-29-2026 08-39@260629JAGBIDJA00241325.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:48 PM</t>
-  </si>
-  <si>
-    <t>Rendi Septrian</t>
-  </si>
-  <si>
-    <t>Rendi</t>
-  </si>
-  <si>
-    <t>IMG_3785.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:51 PM</t>
-  </si>
-  <si>
-    <t>Ririn Riani</t>
-  </si>
-  <si>
-    <t>RIRIN</t>
-  </si>
-  <si>
-    <t>Jersey Ririn.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:55 PM</t>
-  </si>
-  <si>
-    <t>Fairuz Ismayana</t>
-  </si>
-  <si>
-    <t>Sloth</t>
-  </si>
-  <si>
-    <t>Jersey Faiz.JPG</t>
-  </si>
-  <si>
-    <t>06/29/2026 01:57 PM</t>
-  </si>
-  <si>
-    <t>Jeson Dharma</t>
-  </si>
-  <si>
-    <t>Jeson</t>
-  </si>
-  <si>
-    <t>IMG_62F0DCE6B558-1.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 02:24 PM</t>
-  </si>
-  <si>
-    <t>Vya</t>
-  </si>
-  <si>
-    <t>083eb7b3-614b-43d0-9185-593ef7a31d85.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 02:38 PM</t>
-  </si>
-  <si>
-    <t>Teo Apriyandi</t>
-  </si>
-  <si>
-    <t>Teo</t>
-  </si>
-  <si>
-    <t>06/29/2026 02:50 PM</t>
-  </si>
-  <si>
-    <t>Samantha Niandra</t>
-  </si>
-  <si>
-    <t>SAM</t>
-  </si>
-  <si>
-    <t>0f9fc15c-f156-4b18-9620-53ba207b9407.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 03:00 PM</t>
-  </si>
-  <si>
-    <t>Kezia Tandapai</t>
-  </si>
-  <si>
-    <t>Kezia</t>
-  </si>
-  <si>
-    <t>IMG_2226.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 03:05 PM</t>
-  </si>
-  <si>
-    <t>Beata Daneswari</t>
-  </si>
-  <si>
-    <t>Beata</t>
-  </si>
-  <si>
-    <t>Screenshot 2026-06-29 at 22.04.36.heic</t>
-  </si>
-  <si>
-    <t>06/29/2026 03:18 PM</t>
-  </si>
-  <si>
-    <t>Naila Lauza</t>
-  </si>
-  <si>
-    <t>NAI</t>
-  </si>
-  <si>
-    <t>IMG_5290.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 03:32 PM</t>
-  </si>
-  <si>
-    <t>Daud Dimas P</t>
-  </si>
-  <si>
-    <t>DAVIDE</t>
-  </si>
-  <si>
-    <t>IMG_6449.JPG</t>
-  </si>
-  <si>
-    <t>06/29/2026 03:33 PM</t>
-  </si>
-  <si>
-    <t>Jonathan Basuki</t>
-  </si>
-  <si>
-    <t>Jonathan</t>
-  </si>
-  <si>
-    <t>27e266f2-3c1e-46f9-bcea-cfbdcd70b9d7.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 04:06 PM</t>
-  </si>
-  <si>
-    <t>Haikal Izzanour</t>
-  </si>
-  <si>
-    <t>Lingard</t>
-  </si>
-  <si>
-    <t>IMG_2222.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 04:24 PM</t>
-  </si>
-  <si>
-    <t>Jessica Selistio</t>
-  </si>
-  <si>
-    <t>Jeli</t>
-  </si>
-  <si>
-    <t>IMG_1353.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 04:27 PM</t>
-  </si>
-  <si>
-    <t>Sebastian Darren</t>
-  </si>
-  <si>
-    <t>SEBA</t>
-  </si>
-  <si>
-    <t>PHOTO-2026-06-29-23-27-26.jpg</t>
-  </si>
-  <si>
-    <t>06/29/2026 04:32 PM</t>
-  </si>
-  <si>
-    <t>Syukra Ramadhan</t>
-  </si>
-  <si>
-    <t>JERSEY SYUKRA.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 04:34 PM</t>
-  </si>
-  <si>
-    <t>Rio Ferdian</t>
-  </si>
-  <si>
-    <t>LAMPUNG</t>
-  </si>
-  <si>
-    <t>Screenshot_20260629-233149.myBCA.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 04:35 PM</t>
-  </si>
-  <si>
-    <t>BANTEN</t>
-  </si>
-  <si>
-    <t>Screenshot_2026-06-29-23-34-47-892_id.co.bankbkemobile.digitalbank.jpg</t>
-  </si>
-  <si>
-    <t>06/29/2026 04:39 PM</t>
-  </si>
-  <si>
-    <t>Dimas Aryawan</t>
-  </si>
-  <si>
-    <t>IMG_1009.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 04:41 PM</t>
-  </si>
-  <si>
-    <t>Azis Hardy</t>
-  </si>
-  <si>
-    <t>Hardy</t>
-  </si>
-  <si>
-    <t>1F29400F-2ABE-4F91-8E1C-64703C2F5854.jpeg</t>
-  </si>
-  <si>
-    <t>Jatayu Wicaksono</t>
-  </si>
-  <si>
-    <t>JATIM</t>
-  </si>
-  <si>
-    <t>IMG_2477.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 04:54 PM</t>
-  </si>
-  <si>
-    <t>Feivel Qutby</t>
-  </si>
-  <si>
-    <t>FEIVEL</t>
-  </si>
-  <si>
-    <t>Screenshot 2026-06-29 at 11.53.36 PM.png</t>
-  </si>
-  <si>
-    <t>Kevin Halim</t>
-  </si>
-  <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>IMG_0741.jpg</t>
-  </si>
-  <si>
-    <t>06/29/2026 05:02 PM</t>
-  </si>
-  <si>
-    <t>Carleano Ravelza Wongso</t>
-  </si>
-  <si>
-    <t>Ravel</t>
-  </si>
-  <si>
-    <t>IMG_2235.png</t>
-  </si>
-  <si>
-    <t>06/29/2026 06:23 PM</t>
-  </si>
-  <si>
-    <t>Adri Putra</t>
-  </si>
-  <si>
-    <t>Adri</t>
-  </si>
-  <si>
-    <t>cbbaed3e-6458-4f1e-863e-95fd1a410541.jpeg</t>
-  </si>
-  <si>
-    <t>06/29/2026 06:46 PM</t>
-  </si>
-  <si>
-    <t>Nabiel Ardhityo</t>
-  </si>
-  <si>
-    <t>BIEL</t>
-  </si>
-  <si>
-    <t>IMG_6901.PNG</t>
-  </si>
-  <si>
-    <t>06/29/2026 07:04 PM</t>
-  </si>
-  <si>
-    <t>Abraar Hibatullah</t>
-  </si>
-  <si>
-    <t>ABEAR</t>
-  </si>
-  <si>
-    <t>IMG_2431.jpeg</t>
-  </si>
-  <si>
-    <t>06/30/2026 01:09 AM</t>
-  </si>
-  <si>
-    <t>Michael Mintje</t>
-  </si>
-  <si>
-    <t>Mike</t>
-  </si>
-  <si>
-    <t>Screenshot 2026-06-30 at 08.08.50.heic</t>
-  </si>
-  <si>
-    <t>06/30/2026 03:03 AM</t>
-  </si>
-  <si>
-    <t>Yuki Damanik</t>
-  </si>
-  <si>
-    <t>YUKI</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>IMG_2056.png</t>
-  </si>
-  <si>
-    <t>06/30/2026 06:40 AM</t>
-  </si>
-  <si>
-    <t>KALTENG</t>
-  </si>
-  <si>
-    <t>IMG_0568.png</t>
-  </si>
-  <si>
-    <t>06/30/2026 07:37 AM</t>
-  </si>
-  <si>
-    <t>Lidia Julean</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>WhatsApp Image 2026-06-30 at 14.34.35.jpeg</t>
-  </si>
-  <si>
-    <t>06/30/2026 07:40 AM</t>
-  </si>
-  <si>
-    <t>Reynard Lie</t>
-  </si>
-  <si>
-    <t>REY</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Transaksi_BCAmobile-20260630-143803.jpeg</t>
-  </si>
-  <si>
-    <t>06/30/2026 07:47 AM</t>
-  </si>
-  <si>
-    <t>Matthew Hutabarat</t>
-  </si>
-  <si>
-    <t>NgokNgok</t>
-  </si>
-  <si>
-    <t>WhatsApp Image 2026-06-30 at 14.46.41.jpeg</t>
-  </si>
-  <si>
-    <t>06/30/2026 09:49 AM</t>
-  </si>
-  <si>
-    <t>Rafi Favian</t>
-  </si>
-  <si>
-    <t>Papiann</t>
-  </si>
-  <si>
-    <t>Jersey Apple - Rafi.jpeg</t>
-  </si>
-  <si>
-    <t>06/30/2026 12:49 PM</t>
-  </si>
-  <si>
-    <t>Michael Ginting</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>JPEG image-42F0-A94D-A4-0.jpeg</t>
-  </si>
-  <si>
-    <t>07/01/2026 02:29 AM</t>
-  </si>
-  <si>
-    <t>L Erwin Saputra</t>
-  </si>
-  <si>
-    <t>IMG_0501.jpeg</t>
-  </si>
-  <si>
-    <t>07/01/2026 06:10 AM</t>
-  </si>
-  <si>
-    <t>IMG_3021.PNG</t>
-  </si>
-  <si>
-    <t>07/01/2026 11:35 AM</t>
-  </si>
-  <si>
-    <t>Rizqi Widianto</t>
-  </si>
-  <si>
-    <t>MARNO BENGKEL</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>IMG_2902.jpeg</t>
-  </si>
-  <si>
-    <t>07/01/2026 11:53 AM</t>
-  </si>
-  <si>
-    <t>Eko Cahyo Prihantoro</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>IMG_3374.png</t>
-  </si>
-  <si>
-    <t>07/01/2026 12:11 PM</t>
-  </si>
-  <si>
-    <t>Gading Perdana</t>
-  </si>
-  <si>
-    <t>GADING</t>
-  </si>
-  <si>
-    <t>IMG_3818.jpeg</t>
-  </si>
-  <si>
-    <t>07/01/2026 12:12 PM</t>
-  </si>
-  <si>
-    <t>Danniel Ang</t>
-  </si>
-  <si>
-    <t>RIAU</t>
-  </si>
-  <si>
-    <t>JPEG image-4834-90F2-79-0.jpeg</t>
+    <t>eac0eadb-dbf3-4707-baac-e37b1e4c19d4.jpeg</t>
   </si>
 </sst>
 </file>
@@ -5036,16 +5039,16 @@
         <v>294</v>
       </c>
       <c r="E66" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F66" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H66" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I66" t="s">
         <v>19</v>
@@ -5054,24 +5057,24 @@
         <v>20</v>
       </c>
       <c r="K66" t="s">
-        <v>85</v>
+        <v>295</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B67" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C67" t="s">
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E67" t="s">
-        <v>151</v>
+        <v>299</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
@@ -5080,33 +5083,33 @@
         <v>17</v>
       </c>
       <c r="H67" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
       </c>
       <c r="J67" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K67" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B68" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C68" t="s">
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E68" t="s">
-        <v>302</v>
+        <v>163</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
@@ -5115,7 +5118,7 @@
         <v>17</v>
       </c>
       <c r="H68" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s">
         <v>19</v>
@@ -5124,68 +5127,68 @@
         <v>25</v>
       </c>
       <c r="K68" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B69" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E69" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F69" t="s">
         <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H69" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I69" t="s">
         <v>19</v>
       </c>
       <c r="J69" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K69" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B70" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C70" t="s">
         <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E70" t="s">
-        <v>167</v>
+        <v>312</v>
       </c>
       <c r="F70" t="s">
         <v>16</v>
       </c>
       <c r="G70" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I70" t="s">
         <v>19</v>
@@ -5194,65 +5197,65 @@
         <v>20</v>
       </c>
       <c r="K70" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B71" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C71" t="s">
         <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>314</v>
+        <v>14</v>
       </c>
       <c r="E71" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G71" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H71" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I71" t="s">
         <v>19</v>
       </c>
       <c r="J71" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K71" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B72" t="s">
-        <v>318</v>
+        <v>193</v>
       </c>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D72" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="E72" t="s">
-        <v>319</v>
+        <v>195</v>
       </c>
       <c r="F72" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
@@ -5261,62 +5264,62 @@
         <v>19</v>
       </c>
       <c r="J72" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K72" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>320</v>
+      </c>
+      <c r="B73" t="s">
         <v>321</v>
       </c>
-      <c r="B73" t="s">
-        <v>193</v>
-      </c>
       <c r="C73" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>194</v>
+        <v>322</v>
       </c>
       <c r="E73" t="s">
-        <v>195</v>
+        <v>323</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G73" t="s">
         <v>17</v>
       </c>
       <c r="H73" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J73" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K73" t="s">
-        <v>322</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B74" t="s">
-        <v>324</v>
+        <v>230</v>
       </c>
       <c r="C74" t="s">
         <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>325</v>
+        <v>231</v>
       </c>
       <c r="E74" t="s">
-        <v>326</v>
+        <v>187</v>
       </c>
       <c r="F74" t="s">
         <v>34</v>
@@ -5325,65 +5328,65 @@
         <v>17</v>
       </c>
       <c r="H74" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="I74" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J74" t="s">
         <v>25</v>
       </c>
       <c r="K74" t="s">
-        <v>85</v>
+        <v>325</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>326</v>
+      </c>
+      <c r="B75" t="s">
         <v>327</v>
-      </c>
-      <c r="B75" t="s">
-        <v>230</v>
       </c>
       <c r="C75" t="s">
         <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>231</v>
+        <v>328</v>
       </c>
       <c r="E75" t="s">
-        <v>187</v>
+        <v>29</v>
       </c>
       <c r="F75" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G75" t="s">
         <v>17</v>
       </c>
       <c r="H75" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I75" t="s">
         <v>19</v>
       </c>
       <c r="J75" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K75" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B76" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C76" t="s">
         <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E76" t="s">
         <v>29</v>
@@ -5401,27 +5404,27 @@
         <v>19</v>
       </c>
       <c r="J76" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K76" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C77" t="s">
         <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E77" t="s">
-        <v>29</v>
+        <v>334</v>
       </c>
       <c r="F77" t="s">
         <v>16</v>
@@ -5439,33 +5442,33 @@
         <v>25</v>
       </c>
       <c r="K77" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B78" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E78" t="s">
-        <v>337</v>
+        <v>29</v>
       </c>
       <c r="F78" t="s">
         <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H78" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
@@ -5474,24 +5477,24 @@
         <v>25</v>
       </c>
       <c r="K78" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B79" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C79" t="s">
         <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E79" t="s">
-        <v>29</v>
+        <v>316</v>
       </c>
       <c r="F79" t="s">
         <v>16</v>
@@ -5500,7 +5503,7 @@
         <v>35</v>
       </c>
       <c r="H79" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I79" t="s">
         <v>19</v>
@@ -5509,65 +5512,65 @@
         <v>25</v>
       </c>
       <c r="K79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B80" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C80" t="s">
         <v>111</v>
       </c>
       <c r="D80" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E80" t="s">
-        <v>319</v>
+        <v>61</v>
       </c>
       <c r="F80" t="s">
         <v>16</v>
       </c>
       <c r="G80" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H80" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I80" t="s">
         <v>19</v>
       </c>
       <c r="J80" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K80" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B81" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C81" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>14</v>
       </c>
       <c r="E81" t="s">
-        <v>61</v>
+        <v>204</v>
       </c>
       <c r="F81" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G81" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H81" t="s">
         <v>36</v>
@@ -5576,7 +5579,7 @@
         <v>19</v>
       </c>
       <c r="J81" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K81" t="s">
         <v>350</v>
@@ -5590,22 +5593,22 @@
         <v>352</v>
       </c>
       <c r="C82" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D82" t="s">
-        <v>14</v>
+        <v>353</v>
       </c>
       <c r="E82" t="s">
-        <v>204</v>
+        <v>354</v>
       </c>
       <c r="F82" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G82" t="s">
         <v>35</v>
       </c>
       <c r="H82" t="s">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="I82" t="s">
         <v>19</v>
@@ -5614,24 +5617,24 @@
         <v>25</v>
       </c>
       <c r="K82" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B83" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C83" t="s">
         <v>111</v>
       </c>
       <c r="D83" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E83" t="s">
-        <v>357</v>
+        <v>33</v>
       </c>
       <c r="F83" t="s">
         <v>16</v>
@@ -5640,7 +5643,7 @@
         <v>35</v>
       </c>
       <c r="H83" t="s">
-        <v>175</v>
+        <v>36</v>
       </c>
       <c r="I83" t="s">
         <v>19</v>
@@ -5649,30 +5652,30 @@
         <v>25</v>
       </c>
       <c r="K83" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B84" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C84" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E84" t="s">
-        <v>33</v>
+        <v>363</v>
       </c>
       <c r="F84" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G84" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H84" t="s">
         <v>36</v>
@@ -5684,33 +5687,33 @@
         <v>25</v>
       </c>
       <c r="K84" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B85" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C85" t="s">
         <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E85" t="s">
-        <v>366</v>
+        <v>76</v>
       </c>
       <c r="F85" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G85" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H85" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I85" t="s">
         <v>19</v>
@@ -5719,33 +5722,33 @@
         <v>25</v>
       </c>
       <c r="K85" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B86" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D86" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E86" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="F86" t="s">
         <v>16</v>
       </c>
       <c r="G86" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H86" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I86" t="s">
         <v>19</v>
@@ -5754,33 +5757,33 @@
         <v>25</v>
       </c>
       <c r="K86" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B87" t="s">
-        <v>373</v>
+        <v>306</v>
       </c>
       <c r="C87" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D87" t="s">
         <v>374</v>
       </c>
       <c r="E87" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="F87" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G87" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H87" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
@@ -5797,25 +5800,25 @@
         <v>376</v>
       </c>
       <c r="B88" t="s">
-        <v>309</v>
+        <v>377</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D88" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E88" t="s">
-        <v>167</v>
+        <v>282</v>
       </c>
       <c r="F88" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G88" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H88" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I88" t="s">
         <v>19</v>
@@ -5824,33 +5827,33 @@
         <v>25</v>
       </c>
       <c r="K88" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B89" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C89" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E89" t="s">
-        <v>282</v>
+        <v>61</v>
       </c>
       <c r="F89" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G89" t="s">
         <v>17</v>
       </c>
       <c r="H89" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="I89" t="s">
         <v>19</v>
@@ -5859,33 +5862,33 @@
         <v>25</v>
       </c>
       <c r="K89" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B90" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C90" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D90" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E90" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="F90" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G90" t="s">
         <v>17</v>
       </c>
       <c r="H90" t="s">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="I90" t="s">
         <v>19</v>
@@ -5894,24 +5897,24 @@
         <v>25</v>
       </c>
       <c r="K90" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B91" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C91" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D91" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E91" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="F91" t="s">
         <v>16</v>
@@ -5926,97 +5929,97 @@
         <v>19</v>
       </c>
       <c r="J91" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K91" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B92" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C92" t="s">
         <v>13</v>
       </c>
       <c r="D92" t="s">
+        <v>390</v>
+      </c>
+      <c r="E92" t="s">
+        <v>55</v>
+      </c>
+      <c r="F92" t="s">
+        <v>16</v>
+      </c>
+      <c r="G92" t="s">
+        <v>35</v>
+      </c>
+      <c r="H92" t="s">
+        <v>175</v>
+      </c>
+      <c r="I92" t="s">
+        <v>19</v>
+      </c>
+      <c r="J92" t="s">
+        <v>25</v>
+      </c>
+      <c r="K92" t="s">
         <v>393</v>
-      </c>
-      <c r="E92" t="s">
-        <v>151</v>
-      </c>
-      <c r="F92" t="s">
-        <v>16</v>
-      </c>
-      <c r="G92" t="s">
-        <v>17</v>
-      </c>
-      <c r="H92" t="s">
-        <v>42</v>
-      </c>
-      <c r="I92" t="s">
-        <v>19</v>
-      </c>
-      <c r="J92" t="s">
-        <v>20</v>
-      </c>
-      <c r="K92" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>394</v>
+      </c>
+      <c r="B93" t="s">
         <v>395</v>
-      </c>
-      <c r="B93" t="s">
-        <v>392</v>
       </c>
       <c r="C93" t="s">
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E93" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="F93" t="s">
         <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H93" t="s">
-        <v>175</v>
+        <v>36</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
       </c>
       <c r="J93" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K93" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B94" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C94" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D94" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E94" t="s">
-        <v>113</v>
+        <v>401</v>
       </c>
       <c r="F94" t="s">
         <v>16</v>
@@ -6025,7 +6028,7 @@
         <v>17</v>
       </c>
       <c r="H94" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I94" t="s">
         <v>19</v>
@@ -6034,24 +6037,24 @@
         <v>20</v>
       </c>
       <c r="K94" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B95" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C95" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E95" t="s">
-        <v>404</v>
+        <v>113</v>
       </c>
       <c r="F95" t="s">
         <v>16</v>
@@ -6060,80 +6063,80 @@
         <v>17</v>
       </c>
       <c r="H95" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I95" t="s">
         <v>19</v>
       </c>
       <c r="J95" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K95" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B96" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C96" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D96" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E96" t="s">
-        <v>113</v>
+        <v>410</v>
       </c>
       <c r="F96" t="s">
         <v>16</v>
       </c>
       <c r="G96" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H96" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J96" t="s">
         <v>25</v>
       </c>
       <c r="K96" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B97" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C97" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D97" t="s">
-        <v>412</v>
+        <v>14</v>
       </c>
       <c r="E97" t="s">
-        <v>413</v>
+        <v>66</v>
       </c>
       <c r="F97" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G97" t="s">
         <v>35</v>
       </c>
       <c r="H97" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J97" t="s">
         <v>25</v>
@@ -6150,19 +6153,19 @@
         <v>416</v>
       </c>
       <c r="C98" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D98" t="s">
-        <v>14</v>
+        <v>417</v>
       </c>
       <c r="E98" t="s">
-        <v>66</v>
+        <v>187</v>
       </c>
       <c r="F98" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
@@ -6174,68 +6177,68 @@
         <v>25</v>
       </c>
       <c r="K98" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B99" t="s">
-        <v>419</v>
+        <v>138</v>
       </c>
       <c r="C99" t="s">
         <v>111</v>
       </c>
       <c r="D99" t="s">
-        <v>420</v>
+        <v>139</v>
       </c>
       <c r="E99" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="F99" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G99" t="s">
         <v>17</v>
       </c>
       <c r="H99" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="I99" t="s">
         <v>19</v>
       </c>
       <c r="J99" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K99" t="s">
-        <v>421</v>
+        <v>85</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
+        <v>420</v>
+      </c>
+      <c r="B100" t="s">
+        <v>421</v>
+      </c>
+      <c r="C100" t="s">
+        <v>111</v>
+      </c>
+      <c r="D100" t="s">
         <v>422</v>
       </c>
-      <c r="B100" t="s">
-        <v>138</v>
-      </c>
-      <c r="C100" t="s">
-        <v>111</v>
-      </c>
-      <c r="D100" t="s">
-        <v>139</v>
-      </c>
       <c r="E100" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="F100" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G100" t="s">
         <v>17</v>
       </c>
       <c r="H100" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
@@ -6244,24 +6247,24 @@
         <v>20</v>
       </c>
       <c r="K100" t="s">
-        <v>85</v>
+        <v>423</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B101" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C101" t="s">
         <v>111</v>
       </c>
       <c r="D101" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E101" t="s">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="F101" t="s">
         <v>16</v>
@@ -6270,7 +6273,7 @@
         <v>17</v>
       </c>
       <c r="H101" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="I101" t="s">
         <v>19</v>
@@ -6279,24 +6282,24 @@
         <v>20</v>
       </c>
       <c r="K101" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B102" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C102" t="s">
         <v>111</v>
       </c>
       <c r="D102" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E102" t="s">
-        <v>413</v>
+        <v>151</v>
       </c>
       <c r="F102" t="s">
         <v>16</v>
@@ -6305,24 +6308,24 @@
         <v>17</v>
       </c>
       <c r="H102" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I102" t="s">
         <v>19</v>
       </c>
       <c r="J102" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K102" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B103" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C103" t="s">
         <v>111</v>
@@ -6331,16 +6334,16 @@
         <v>433</v>
       </c>
       <c r="E103" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="F103" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G103" t="s">
         <v>17</v>
       </c>
       <c r="H103" t="s">
-        <v>56</v>
+        <v>434</v>
       </c>
       <c r="I103" t="s">
         <v>19</v>
@@ -6349,24 +6352,24 @@
         <v>25</v>
       </c>
       <c r="K103" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B104" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C104" t="s">
         <v>111</v>
       </c>
       <c r="D104" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E104" t="s">
-        <v>41</v>
+        <v>439</v>
       </c>
       <c r="F104" t="s">
         <v>34</v>
@@ -6375,77 +6378,77 @@
         <v>17</v>
       </c>
       <c r="H104" t="s">
-        <v>437</v>
+        <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J104" t="s">
         <v>25</v>
       </c>
       <c r="K104" t="s">
-        <v>438</v>
+        <v>85</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B105" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C105" t="s">
         <v>111</v>
       </c>
       <c r="D105" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E105" t="s">
-        <v>442</v>
+        <v>159</v>
       </c>
       <c r="F105" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G105" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H105" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I105" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J105" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K105" t="s">
-        <v>85</v>
+        <v>443</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B106" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C106" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D106" t="s">
         <v>445</v>
       </c>
       <c r="E106" t="s">
-        <v>159</v>
+        <v>439</v>
       </c>
       <c r="F106" t="s">
         <v>16</v>
       </c>
       <c r="G106" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H106" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I106" t="s">
         <v>19</v>
@@ -6465,13 +6468,13 @@
         <v>448</v>
       </c>
       <c r="C107" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E107" t="s">
-        <v>442</v>
+        <v>151</v>
       </c>
       <c r="F107" t="s">
         <v>16</v>
@@ -6480,7 +6483,7 @@
         <v>17</v>
       </c>
       <c r="H107" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="I107" t="s">
         <v>19</v>
@@ -6489,24 +6492,24 @@
         <v>20</v>
       </c>
       <c r="K107" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B108" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C108" t="s">
         <v>111</v>
       </c>
       <c r="D108" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E108" t="s">
-        <v>151</v>
+        <v>454</v>
       </c>
       <c r="F108" t="s">
         <v>16</v>
@@ -6515,7 +6518,7 @@
         <v>17</v>
       </c>
       <c r="H108" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I108" t="s">
         <v>19</v>
@@ -6524,24 +6527,24 @@
         <v>20</v>
       </c>
       <c r="K108" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B109" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C109" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D109" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E109" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F109" t="s">
         <v>16</v>
@@ -6550,33 +6553,33 @@
         <v>17</v>
       </c>
       <c r="H109" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I109" t="s">
         <v>19</v>
       </c>
       <c r="J109" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K109" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B110" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C110" t="s">
         <v>13</v>
       </c>
       <c r="D110" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E110" t="s">
-        <v>462</v>
+        <v>363</v>
       </c>
       <c r="F110" t="s">
         <v>16</v>
@@ -6591,27 +6594,27 @@
         <v>19</v>
       </c>
       <c r="J110" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K110" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B111" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C111" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D111" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E111" t="s">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="F111" t="s">
         <v>16</v>
@@ -6620,7 +6623,7 @@
         <v>17</v>
       </c>
       <c r="H111" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I111" t="s">
         <v>19</v>
@@ -6629,33 +6632,33 @@
         <v>20</v>
       </c>
       <c r="K111" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B112" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C112" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D112" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E112" t="s">
-        <v>413</v>
+        <v>472</v>
       </c>
       <c r="F112" t="s">
         <v>16</v>
       </c>
       <c r="G112" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H112" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I112" t="s">
         <v>19</v>
@@ -6664,42 +6667,42 @@
         <v>20</v>
       </c>
       <c r="K112" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B113" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C113" t="s">
         <v>13</v>
       </c>
       <c r="D113" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E113" t="s">
-        <v>475</v>
+        <v>167</v>
       </c>
       <c r="F113" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G113" t="s">
         <v>35</v>
       </c>
       <c r="H113" t="s">
-        <v>42</v>
+        <v>175</v>
       </c>
       <c r="I113" t="s">
         <v>19</v>
       </c>
       <c r="J113" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K113" t="s">
-        <v>476</v>
+        <v>82</v>
       </c>
     </row>
     <row r="114">
@@ -6710,48 +6713,48 @@
         <v>478</v>
       </c>
       <c r="C114" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D114" t="s">
         <v>479</v>
       </c>
       <c r="E114" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F114" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G114" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H114" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J114" t="s">
         <v>25</v>
       </c>
       <c r="K114" t="s">
-        <v>82</v>
+        <v>480</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B115" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C115" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D115" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E115" t="s">
-        <v>163</v>
+        <v>410</v>
       </c>
       <c r="F115" t="s">
         <v>16</v>
@@ -6763,18 +6766,18 @@
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J115" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K115" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B116" t="s">
         <v>485</v>
@@ -6786,22 +6789,22 @@
         <v>486</v>
       </c>
       <c r="E116" t="s">
-        <v>413</v>
+        <v>41</v>
       </c>
       <c r="F116" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G116" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H116" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="I116" t="s">
         <v>19</v>
       </c>
       <c r="J116" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K116" t="s">
         <v>487</v>
@@ -6809,69 +6812,69 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B117" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C117" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D117" t="s">
         <v>489</v>
       </c>
       <c r="E117" t="s">
-        <v>41</v>
+        <v>490</v>
       </c>
       <c r="F117" t="s">
         <v>34</v>
       </c>
       <c r="G117" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H117" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="I117" t="s">
         <v>19</v>
       </c>
       <c r="J117" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K117" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B118" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="C118" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D118" t="s">
-        <v>492</v>
+        <v>14</v>
       </c>
       <c r="E118" t="s">
-        <v>493</v>
+        <v>135</v>
       </c>
       <c r="F118" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G118" t="s">
         <v>17</v>
       </c>
       <c r="H118" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I118" t="s">
         <v>19</v>
       </c>
       <c r="J118" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K118" t="s">
         <v>494</v>
@@ -6885,13 +6888,13 @@
         <v>496</v>
       </c>
       <c r="C119" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D119" t="s">
-        <v>14</v>
+        <v>497</v>
       </c>
       <c r="E119" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="F119" t="s">
         <v>16</v>
@@ -6900,7 +6903,7 @@
         <v>17</v>
       </c>
       <c r="H119" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I119" t="s">
         <v>19</v>
@@ -6909,7 +6912,7 @@
         <v>25</v>
       </c>
       <c r="K119" t="s">
-        <v>497</v>
+        <v>82</v>
       </c>
     </row>
     <row r="120">
@@ -6920,19 +6923,19 @@
         <v>499</v>
       </c>
       <c r="C120" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D120" t="s">
         <v>500</v>
       </c>
       <c r="E120" t="s">
-        <v>107</v>
+        <v>410</v>
       </c>
       <c r="F120" t="s">
         <v>16</v>
       </c>
       <c r="G120" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
@@ -6952,16 +6955,16 @@
         <v>501</v>
       </c>
       <c r="B121" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C121" t="s">
         <v>13</v>
       </c>
       <c r="D121" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E121" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F121" t="s">
         <v>16</v>
@@ -6976,7 +6979,7 @@
         <v>19</v>
       </c>
       <c r="J121" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K121" t="s">
         <v>82</v>
@@ -6984,57 +6987,57 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>502</v>
+      </c>
+      <c r="B122" t="s">
+        <v>503</v>
+      </c>
+      <c r="C122" t="s">
+        <v>111</v>
+      </c>
+      <c r="D122" t="s">
         <v>504</v>
       </c>
-      <c r="B122" t="s">
-        <v>502</v>
-      </c>
-      <c r="C122" t="s">
-        <v>13</v>
-      </c>
-      <c r="D122" t="s">
-        <v>503</v>
-      </c>
       <c r="E122" t="s">
-        <v>413</v>
+        <v>66</v>
       </c>
       <c r="F122" t="s">
         <v>16</v>
       </c>
       <c r="G122" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J122" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K122" t="s">
-        <v>82</v>
+        <v>505</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B123" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C123" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D123" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E123" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="F123" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G123" t="s">
         <v>17</v>
@@ -7043,65 +7046,65 @@
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J123" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K123" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B124" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C124" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D124" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E124" t="s">
-        <v>151</v>
+        <v>513</v>
       </c>
       <c r="F124" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G124" t="s">
         <v>17</v>
       </c>
       <c r="H124" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I124" t="s">
         <v>19</v>
       </c>
       <c r="J124" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K124" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B125" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C125" t="s">
         <v>111</v>
       </c>
       <c r="D125" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E125" t="s">
-        <v>516</v>
+        <v>163</v>
       </c>
       <c r="F125" t="s">
         <v>16</v>
@@ -7110,13 +7113,13 @@
         <v>17</v>
       </c>
       <c r="H125" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I125" t="s">
         <v>19</v>
       </c>
       <c r="J125" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K125" t="s">
         <v>517</v>
@@ -7133,10 +7136,10 @@
         <v>111</v>
       </c>
       <c r="D126" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E126" t="s">
-        <v>163</v>
+        <v>410</v>
       </c>
       <c r="F126" t="s">
         <v>16</v>
@@ -7145,33 +7148,33 @@
         <v>17</v>
       </c>
       <c r="H126" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I126" t="s">
         <v>19</v>
       </c>
       <c r="J126" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K126" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B127" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C127" t="s">
         <v>111</v>
       </c>
       <c r="D127" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E127" t="s">
-        <v>413</v>
+        <v>490</v>
       </c>
       <c r="F127" t="s">
         <v>16</v>
@@ -7180,7 +7183,7 @@
         <v>17</v>
       </c>
       <c r="H127" t="s">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="I127" t="s">
         <v>19</v>
@@ -7189,24 +7192,24 @@
         <v>25</v>
       </c>
       <c r="K127" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B128" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C128" t="s">
         <v>111</v>
       </c>
       <c r="D128" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E128" t="s">
-        <v>493</v>
+        <v>41</v>
       </c>
       <c r="F128" t="s">
         <v>16</v>
@@ -7215,24 +7218,24 @@
         <v>17</v>
       </c>
       <c r="H128" t="s">
-        <v>175</v>
+        <v>36</v>
       </c>
       <c r="I128" t="s">
         <v>19</v>
       </c>
       <c r="J128" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K128" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B129" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C129" t="s">
         <v>111</v>
@@ -7250,24 +7253,24 @@
         <v>17</v>
       </c>
       <c r="H129" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I129" t="s">
         <v>19</v>
       </c>
       <c r="J129" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K129" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>532</v>
+      </c>
+      <c r="B130" t="s">
         <v>533</v>
-      </c>
-      <c r="B130" t="s">
-        <v>530</v>
       </c>
       <c r="C130" t="s">
         <v>111</v>
@@ -7276,7 +7279,7 @@
         <v>534</v>
       </c>
       <c r="E130" t="s">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="F130" t="s">
         <v>16</v>
@@ -7285,7 +7288,7 @@
         <v>17</v>
       </c>
       <c r="H130" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="I130" t="s">
         <v>19</v>
@@ -7294,24 +7297,24 @@
         <v>25</v>
       </c>
       <c r="K130" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B131" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C131" t="s">
         <v>111</v>
       </c>
       <c r="D131" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E131" t="s">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="F131" t="s">
         <v>16</v>
@@ -7320,7 +7323,7 @@
         <v>17</v>
       </c>
       <c r="H131" t="s">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="I131" t="s">
         <v>19</v>
@@ -7329,24 +7332,24 @@
         <v>25</v>
       </c>
       <c r="K131" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B132" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C132" t="s">
         <v>111</v>
       </c>
       <c r="D132" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E132" t="s">
-        <v>47</v>
+        <v>334</v>
       </c>
       <c r="F132" t="s">
         <v>16</v>
@@ -7355,7 +7358,7 @@
         <v>17</v>
       </c>
       <c r="H132" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I132" t="s">
         <v>19</v>
@@ -7364,33 +7367,33 @@
         <v>25</v>
       </c>
       <c r="K132" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B133" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C133" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D133" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E133" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="F133" t="s">
         <v>16</v>
       </c>
       <c r="G133" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H133" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I133" t="s">
         <v>19</v>
@@ -7399,24 +7402,24 @@
         <v>25</v>
       </c>
       <c r="K133" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B134" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C134" t="s">
         <v>13</v>
       </c>
       <c r="D134" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E134" t="s">
-        <v>326</v>
+        <v>159</v>
       </c>
       <c r="F134" t="s">
         <v>16</v>
@@ -7431,27 +7434,27 @@
         <v>19</v>
       </c>
       <c r="J134" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K134" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B135" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C135" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D135" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E135" t="s">
-        <v>159</v>
+        <v>459</v>
       </c>
       <c r="F135" t="s">
         <v>16</v>
@@ -7460,36 +7463,36 @@
         <v>35</v>
       </c>
       <c r="H135" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I135" t="s">
         <v>19</v>
       </c>
       <c r="J135" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K135" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B136" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C136" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D136" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E136" t="s">
-        <v>462</v>
+        <v>559</v>
       </c>
       <c r="F136" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G136" t="s">
         <v>35</v>
@@ -7501,42 +7504,42 @@
         <v>19</v>
       </c>
       <c r="J136" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K136" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B137" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C137" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D137" t="s">
-        <v>561</v>
+        <v>14</v>
       </c>
       <c r="E137" t="s">
-        <v>562</v>
+        <v>113</v>
       </c>
       <c r="F137" t="s">
         <v>34</v>
       </c>
       <c r="G137" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H137" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J137" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K137" t="s">
         <v>563</v>
@@ -7556,19 +7559,19 @@
         <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>113</v>
+        <v>323</v>
       </c>
       <c r="F138" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G138" t="s">
         <v>17</v>
       </c>
       <c r="H138" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I138" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J138" t="s">
         <v>25</v>
@@ -7585,14 +7588,14 @@
         <v>568</v>
       </c>
       <c r="C139" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D139" t="s">
+        <v>569</v>
+      </c>
+      <c r="E139" t="s">
         <v>14</v>
       </c>
-      <c r="E139" t="s">
-        <v>326</v>
-      </c>
       <c r="F139" t="s">
         <v>16</v>
       </c>
@@ -7600,7 +7603,7 @@
         <v>17</v>
       </c>
       <c r="H139" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I139" t="s">
         <v>19</v>
@@ -7609,24 +7612,24 @@
         <v>25</v>
       </c>
       <c r="K139" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B140" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C140" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D140" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E140" t="s">
-        <v>14</v>
+        <v>334</v>
       </c>
       <c r="F140" t="s">
         <v>16</v>
@@ -7644,24 +7647,24 @@
         <v>25</v>
       </c>
       <c r="K140" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B141" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C141" t="s">
         <v>111</v>
       </c>
       <c r="D141" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E141" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F141" t="s">
         <v>16</v>
@@ -7676,27 +7679,27 @@
         <v>19</v>
       </c>
       <c r="J141" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K141" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
+        <v>577</v>
+      </c>
+      <c r="B142" t="s">
         <v>578</v>
       </c>
-      <c r="B142" t="s">
-        <v>575</v>
-      </c>
       <c r="C142" t="s">
         <v>111</v>
       </c>
       <c r="D142" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E142" t="s">
-        <v>337</v>
+        <v>76</v>
       </c>
       <c r="F142" t="s">
         <v>16</v>
@@ -7714,24 +7717,24 @@
         <v>20</v>
       </c>
       <c r="K142" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B143" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C143" t="s">
         <v>111</v>
       </c>
       <c r="D143" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E143" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F143" t="s">
         <v>16</v>
@@ -7740,7 +7743,7 @@
         <v>17</v>
       </c>
       <c r="H143" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I143" t="s">
         <v>19</v>
@@ -7749,33 +7752,33 @@
         <v>20</v>
       </c>
       <c r="K143" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B144" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C144" t="s">
         <v>111</v>
       </c>
       <c r="D144" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E144" t="s">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="F144" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G144" t="s">
         <v>17</v>
       </c>
       <c r="H144" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I144" t="s">
         <v>19</v>
@@ -7784,24 +7787,24 @@
         <v>20</v>
       </c>
       <c r="K144" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B145" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C145" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D145" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E145" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="F145" t="s">
         <v>34</v>
@@ -7810,42 +7813,42 @@
         <v>17</v>
       </c>
       <c r="H145" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I145" t="s">
         <v>19</v>
       </c>
       <c r="J145" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K145" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B146" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C146" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D146" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E146" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F146" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G146" t="s">
         <v>17</v>
       </c>
       <c r="H146" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="I146" t="s">
         <v>19</v>
@@ -7854,94 +7857,94 @@
         <v>25</v>
       </c>
       <c r="K146" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B147" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C147" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D147" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E147" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="F147" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G147" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H147" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="I147" t="s">
         <v>19</v>
       </c>
       <c r="J147" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K147" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B148" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C148" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D148" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E148" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="F148" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G148" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H148" t="s">
-        <v>175</v>
+        <v>56</v>
       </c>
       <c r="I148" t="s">
         <v>19</v>
       </c>
       <c r="J148" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K148" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B149" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C149" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D149" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E149" t="s">
-        <v>102</v>
+        <v>334</v>
       </c>
       <c r="F149" t="s">
         <v>16</v>
@@ -7950,33 +7953,33 @@
         <v>17</v>
       </c>
       <c r="H149" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="I149" t="s">
         <v>19</v>
       </c>
       <c r="J149" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K149" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B150" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C150" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D150" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E150" t="s">
-        <v>337</v>
+        <v>260</v>
       </c>
       <c r="F150" t="s">
         <v>16</v>
@@ -7994,33 +7997,33 @@
         <v>20</v>
       </c>
       <c r="K150" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B151" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C151" t="s">
         <v>111</v>
       </c>
       <c r="D151" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E151" t="s">
-        <v>260</v>
+        <v>151</v>
       </c>
       <c r="F151" t="s">
         <v>16</v>
       </c>
       <c r="G151" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H151" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I151" t="s">
         <v>19</v>
@@ -8029,33 +8032,33 @@
         <v>20</v>
       </c>
       <c r="K151" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B152" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C152" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D152" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E152" t="s">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="F152" t="s">
         <v>16</v>
       </c>
       <c r="G152" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H152" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I152" t="s">
         <v>19</v>
@@ -8064,103 +8067,103 @@
         <v>20</v>
       </c>
       <c r="K152" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B153" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C153" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D153" t="s">
-        <v>622</v>
+        <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>47</v>
+        <v>623</v>
       </c>
       <c r="F153" t="s">
         <v>16</v>
       </c>
       <c r="G153" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H153" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="I153" t="s">
         <v>19</v>
       </c>
       <c r="J153" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K153" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B154" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C154" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D154" t="s">
-        <v>14</v>
+        <v>627</v>
       </c>
       <c r="E154" t="s">
-        <v>626</v>
+        <v>163</v>
       </c>
       <c r="F154" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G154" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H154" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="I154" t="s">
         <v>19</v>
       </c>
       <c r="J154" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K154" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B155" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C155" t="s">
         <v>13</v>
       </c>
       <c r="D155" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E155" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F155" t="s">
         <v>34</v>
       </c>
       <c r="G155" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H155" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I155" t="s">
         <v>19</v>
@@ -8169,30 +8172,30 @@
         <v>20</v>
       </c>
       <c r="K155" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B156" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C156" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D156" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E156" t="s">
-        <v>159</v>
+        <v>439</v>
       </c>
       <c r="F156" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G156" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H156" t="s">
         <v>36</v>
@@ -8201,27 +8204,27 @@
         <v>19</v>
       </c>
       <c r="J156" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K156" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B157" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C157" t="s">
         <v>111</v>
       </c>
       <c r="D157" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E157" t="s">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="F157" t="s">
         <v>16</v>
@@ -8230,7 +8233,7 @@
         <v>17</v>
       </c>
       <c r="H157" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="I157" t="s">
         <v>19</v>
@@ -8239,30 +8242,30 @@
         <v>25</v>
       </c>
       <c r="K157" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B158" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C158" t="s">
         <v>111</v>
       </c>
       <c r="D158" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E158" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F158" t="s">
         <v>16</v>
       </c>
       <c r="G158" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H158" t="s">
         <v>141</v>
@@ -8274,97 +8277,97 @@
         <v>25</v>
       </c>
       <c r="K158" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B159" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C159" t="s">
         <v>111</v>
       </c>
       <c r="D159" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E159" t="s">
-        <v>413</v>
+        <v>71</v>
       </c>
       <c r="F159" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G159" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H159" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="I159" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J159" t="s">
         <v>25</v>
       </c>
       <c r="K159" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B160" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C160" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D160" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E160" t="s">
-        <v>71</v>
+        <v>334</v>
       </c>
       <c r="F160" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G160" t="s">
         <v>17</v>
       </c>
       <c r="H160" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J160" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K160" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B161" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C161" t="s">
         <v>13</v>
       </c>
       <c r="D161" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E161" t="s">
-        <v>337</v>
+        <v>459</v>
       </c>
       <c r="F161" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G161" t="s">
         <v>17</v>
@@ -8379,59 +8382,59 @@
         <v>20</v>
       </c>
       <c r="K161" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B162" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C162" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D162" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E162" t="s">
-        <v>462</v>
+        <v>151</v>
       </c>
       <c r="F162" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G162" t="s">
         <v>17</v>
       </c>
       <c r="H162" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I162" t="s">
         <v>19</v>
       </c>
       <c r="J162" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K162" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B163" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C163" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D163" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E163" t="s">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="F163" t="s">
         <v>16</v>
@@ -8440,7 +8443,7 @@
         <v>17</v>
       </c>
       <c r="H163" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I163" t="s">
         <v>19</v>
@@ -8449,30 +8452,30 @@
         <v>25</v>
       </c>
       <c r="K163" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B164" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C164" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D164" t="s">
-        <v>666</v>
+        <v>14</v>
       </c>
       <c r="E164" t="s">
         <v>14</v>
       </c>
       <c r="F164" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G164" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H164" t="s">
         <v>42</v>
@@ -8498,28 +8501,28 @@
         <v>111</v>
       </c>
       <c r="D165" t="s">
-        <v>14</v>
+        <v>670</v>
       </c>
       <c r="E165" t="s">
-        <v>14</v>
+        <v>323</v>
       </c>
       <c r="F165" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G165" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H165" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I165" t="s">
         <v>19</v>
       </c>
       <c r="J165" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K165" t="s">
-        <v>670</v>
+        <v>85</v>
       </c>
     </row>
     <row r="166">
@@ -8536,16 +8539,16 @@
         <v>673</v>
       </c>
       <c r="E166" t="s">
-        <v>326</v>
+        <v>410</v>
       </c>
       <c r="F166" t="s">
         <v>16</v>
       </c>
       <c r="G166" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H166" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="I166" t="s">
         <v>19</v>
@@ -8554,24 +8557,24 @@
         <v>20</v>
       </c>
       <c r="K166" t="s">
-        <v>85</v>
+        <v>674</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B167" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C167" t="s">
         <v>111</v>
       </c>
       <c r="D167" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E167" t="s">
-        <v>413</v>
+        <v>316</v>
       </c>
       <c r="F167" t="s">
         <v>16</v>
@@ -8580,33 +8583,33 @@
         <v>35</v>
       </c>
       <c r="H167" t="s">
-        <v>175</v>
+        <v>36</v>
       </c>
       <c r="I167" t="s">
         <v>19</v>
       </c>
       <c r="J167" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K167" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B168" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C168" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D168" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E168" t="s">
-        <v>319</v>
+        <v>81</v>
       </c>
       <c r="F168" t="s">
         <v>16</v>
@@ -8624,33 +8627,33 @@
         <v>25</v>
       </c>
       <c r="K168" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B169" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C169" t="s">
         <v>13</v>
       </c>
       <c r="D169" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E169" t="s">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="F169" t="s">
         <v>16</v>
       </c>
       <c r="G169" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H169" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I169" t="s">
         <v>19</v>
@@ -8659,24 +8662,24 @@
         <v>25</v>
       </c>
       <c r="K169" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B170" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C170" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D170" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E170" t="s">
-        <v>366</v>
+        <v>15</v>
       </c>
       <c r="F170" t="s">
         <v>16</v>
@@ -8685,33 +8688,33 @@
         <v>17</v>
       </c>
       <c r="H170" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I170" t="s">
         <v>19</v>
       </c>
       <c r="J170" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K170" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B171" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C171" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D171" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E171" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="F171" t="s">
         <v>16</v>
@@ -8726,27 +8729,27 @@
         <v>19</v>
       </c>
       <c r="J171" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K171" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B172" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C172" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D172" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E172" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="F172" t="s">
         <v>16</v>
@@ -8755,7 +8758,7 @@
         <v>17</v>
       </c>
       <c r="H172" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I172" t="s">
         <v>19</v>
@@ -8764,30 +8767,30 @@
         <v>25</v>
       </c>
       <c r="K172" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B173" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C173" t="s">
         <v>111</v>
       </c>
       <c r="D173" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E173" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F173" t="s">
         <v>16</v>
       </c>
       <c r="G173" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H173" t="s">
         <v>36</v>
@@ -8796,36 +8799,36 @@
         <v>19</v>
       </c>
       <c r="J173" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K173" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B174" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C174" t="s">
         <v>111</v>
       </c>
       <c r="D174" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E174" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="F174" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G174" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H174" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I174" t="s">
         <v>19</v>
@@ -8834,27 +8837,27 @@
         <v>20</v>
       </c>
       <c r="K174" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B175" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C175" t="s">
         <v>111</v>
       </c>
       <c r="D175" t="s">
-        <v>708</v>
+        <v>14</v>
       </c>
       <c r="E175" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="F175" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G175" t="s">
         <v>17</v>
@@ -8863,7 +8866,7 @@
         <v>18</v>
       </c>
       <c r="I175" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J175" t="s">
         <v>20</v>
@@ -8883,36 +8886,36 @@
         <v>111</v>
       </c>
       <c r="D176" t="s">
-        <v>14</v>
+        <v>712</v>
       </c>
       <c r="E176" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F176" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G176" t="s">
         <v>17</v>
       </c>
       <c r="H176" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I176" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J176" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K176" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B177" t="s">
-        <v>714</v>
+        <v>586</v>
       </c>
       <c r="C177" t="s">
         <v>111</v>
@@ -8921,7 +8924,7 @@
         <v>715</v>
       </c>
       <c r="E177" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="F177" t="s">
         <v>34</v>
@@ -8930,7 +8933,7 @@
         <v>17</v>
       </c>
       <c r="H177" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I177" t="s">
         <v>19</v>
@@ -8947,16 +8950,16 @@
         <v>717</v>
       </c>
       <c r="B178" t="s">
-        <v>589</v>
+        <v>718</v>
       </c>
       <c r="C178" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D178" t="s">
-        <v>718</v>
+        <v>14</v>
       </c>
       <c r="E178" t="s">
-        <v>163</v>
+        <v>66</v>
       </c>
       <c r="F178" t="s">
         <v>34</v>
@@ -8985,13 +8988,13 @@
         <v>721</v>
       </c>
       <c r="C179" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D179" t="s">
-        <v>14</v>
+        <v>722</v>
       </c>
       <c r="E179" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="F179" t="s">
         <v>34</v>
@@ -9000,21 +9003,21 @@
         <v>17</v>
       </c>
       <c r="H179" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I179" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J179" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K179" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B180" t="s">
         <v>724</v>
@@ -9026,7 +9029,7 @@
         <v>725</v>
       </c>
       <c r="E180" t="s">
-        <v>93</v>
+        <v>323</v>
       </c>
       <c r="F180" t="s">
         <v>34</v>
@@ -9035,13 +9038,13 @@
         <v>17</v>
       </c>
       <c r="H180" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I180" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J180" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K180" t="s">
         <v>726</v>
@@ -9049,19 +9052,19 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B181" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C181" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D181" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E181" t="s">
-        <v>326</v>
+        <v>151</v>
       </c>
       <c r="F181" t="s">
         <v>34</v>
@@ -9079,39 +9082,39 @@
         <v>25</v>
       </c>
       <c r="K181" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B182" t="s">
         <v>731</v>
       </c>
       <c r="C182" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D182" t="s">
         <v>732</v>
       </c>
       <c r="E182" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="F182" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G182" t="s">
         <v>17</v>
       </c>
       <c r="H182" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I182" t="s">
         <v>19</v>
       </c>
       <c r="J182" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K182" t="s">
         <v>733</v>
@@ -9119,19 +9122,19 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="B183" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C183" t="s">
         <v>111</v>
       </c>
       <c r="D183" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E183" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="F183" t="s">
         <v>16</v>
@@ -9140,7 +9143,7 @@
         <v>17</v>
       </c>
       <c r="H183" t="s">
-        <v>42</v>
+        <v>175</v>
       </c>
       <c r="I183" t="s">
         <v>19</v>
@@ -9149,24 +9152,24 @@
         <v>20</v>
       </c>
       <c r="K183" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B184" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C184" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D184" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E184" t="s">
-        <v>29</v>
+        <v>282</v>
       </c>
       <c r="F184" t="s">
         <v>16</v>
@@ -9175,33 +9178,33 @@
         <v>17</v>
       </c>
       <c r="H184" t="s">
-        <v>175</v>
+        <v>36</v>
       </c>
       <c r="I184" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J184" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K184" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B185" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C185" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D185" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E185" t="s">
-        <v>282</v>
+        <v>61</v>
       </c>
       <c r="F185" t="s">
         <v>16</v>
@@ -9210,33 +9213,33 @@
         <v>17</v>
       </c>
       <c r="H185" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I185" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J185" t="s">
         <v>25</v>
       </c>
       <c r="K185" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B186" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C186" t="s">
         <v>111</v>
       </c>
       <c r="D186" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E186" t="s">
-        <v>61</v>
+        <v>334</v>
       </c>
       <c r="F186" t="s">
         <v>16</v>
@@ -9245,7 +9248,7 @@
         <v>17</v>
       </c>
       <c r="H186" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I186" t="s">
         <v>19</v>
@@ -9254,68 +9257,68 @@
         <v>25</v>
       </c>
       <c r="K186" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B187" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C187" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D187" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E187" t="s">
-        <v>337</v>
+        <v>66</v>
       </c>
       <c r="F187" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G187" t="s">
         <v>17</v>
       </c>
       <c r="H187" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I187" t="s">
         <v>19</v>
       </c>
       <c r="J187" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K187" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B188" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C188" t="s">
         <v>13</v>
       </c>
       <c r="D188" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E188" t="s">
-        <v>66</v>
+        <v>757</v>
       </c>
       <c r="F188" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G188" t="s">
         <v>17</v>
       </c>
       <c r="H188" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="I188" t="s">
         <v>19</v>
@@ -9324,33 +9327,33 @@
         <v>20</v>
       </c>
       <c r="K188" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B189" t="s">
-        <v>758</v>
+        <v>565</v>
       </c>
       <c r="C189" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D189" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E189" t="s">
-        <v>760</v>
+        <v>66</v>
       </c>
       <c r="F189" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G189" t="s">
         <v>17</v>
       </c>
       <c r="H189" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I189" t="s">
         <v>19</v>
@@ -9367,60 +9370,60 @@
         <v>762</v>
       </c>
       <c r="B190" t="s">
-        <v>568</v>
+        <v>763</v>
       </c>
       <c r="C190" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D190" t="s">
-        <v>763</v>
+        <v>14</v>
       </c>
       <c r="E190" t="s">
-        <v>66</v>
+        <v>764</v>
       </c>
       <c r="F190" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G190" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H190" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I190" t="s">
         <v>19</v>
       </c>
       <c r="J190" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K190" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B191" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C191" t="s">
         <v>13</v>
       </c>
       <c r="D191" t="s">
-        <v>14</v>
+        <v>768</v>
       </c>
       <c r="E191" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F191" t="s">
         <v>16</v>
       </c>
       <c r="G191" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H191" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I191" t="s">
         <v>19</v>
@@ -9429,24 +9432,24 @@
         <v>25</v>
       </c>
       <c r="K191" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B192" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C192" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D192" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E192" t="s">
-        <v>772</v>
+        <v>33</v>
       </c>
       <c r="F192" t="s">
         <v>16</v>
@@ -9455,7 +9458,7 @@
         <v>17</v>
       </c>
       <c r="H192" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="I192" t="s">
         <v>19</v>
@@ -9464,24 +9467,24 @@
         <v>25</v>
       </c>
       <c r="K192" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B193" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C193" t="s">
         <v>111</v>
       </c>
       <c r="D193" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E193" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="F193" t="s">
         <v>16</v>
@@ -9490,33 +9493,33 @@
         <v>17</v>
       </c>
       <c r="H193" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I193" t="s">
         <v>19</v>
       </c>
       <c r="J193" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K193" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B194" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C194" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D194" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E194" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F194" t="s">
         <v>16</v>
@@ -9534,39 +9537,39 @@
         <v>20</v>
       </c>
       <c r="K194" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B195" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C195" t="s">
         <v>13</v>
       </c>
       <c r="D195" t="s">
-        <v>784</v>
+        <v>18</v>
       </c>
       <c r="E195" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="F195" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G195" t="s">
         <v>17</v>
       </c>
       <c r="H195" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I195" t="s">
         <v>19</v>
       </c>
       <c r="J195" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K195" t="s">
         <v>785</v>
@@ -9577,16 +9580,16 @@
         <v>786</v>
       </c>
       <c r="B196" t="s">
-        <v>787</v>
+        <v>516</v>
       </c>
       <c r="C196" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D196" t="s">
-        <v>18</v>
+        <v>516</v>
       </c>
       <c r="E196" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -9595,33 +9598,33 @@
         <v>17</v>
       </c>
       <c r="H196" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I196" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J196" t="s">
         <v>25</v>
       </c>
       <c r="K196" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
+        <v>788</v>
+      </c>
+      <c r="B197" t="s">
         <v>789</v>
       </c>
-      <c r="B197" t="s">
-        <v>519</v>
-      </c>
       <c r="C197" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D197" t="s">
-        <v>519</v>
+        <v>790</v>
       </c>
       <c r="E197" t="s">
-        <v>47</v>
+        <v>791</v>
       </c>
       <c r="F197" t="s">
         <v>34</v>
@@ -9630,68 +9633,68 @@
         <v>17</v>
       </c>
       <c r="H197" t="s">
-        <v>18</v>
+        <v>434</v>
       </c>
       <c r="I197" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J197" t="s">
         <v>25</v>
       </c>
       <c r="K197" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B198" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C198" t="s">
         <v>117</v>
       </c>
       <c r="D198" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E198" t="s">
-        <v>794</v>
+        <v>140</v>
       </c>
       <c r="F198" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G198" t="s">
         <v>17</v>
       </c>
       <c r="H198" t="s">
-        <v>437</v>
+        <v>42</v>
       </c>
       <c r="I198" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="J198" t="s">
         <v>25</v>
       </c>
       <c r="K198" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B199" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C199" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D199" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E199" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="F199" t="s">
         <v>16</v>
@@ -9703,30 +9706,30 @@
         <v>42</v>
       </c>
       <c r="I199" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J199" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K199" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B200" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C200" t="s">
         <v>111</v>
       </c>
       <c r="D200" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E200" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="F200" t="s">
         <v>16</v>
@@ -9735,51 +9738,51 @@
         <v>17</v>
       </c>
       <c r="H200" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I200" t="s">
         <v>19</v>
       </c>
       <c r="J200" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K200" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B201" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C201" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D201" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E201" t="s">
-        <v>126</v>
+        <v>14</v>
       </c>
       <c r="F201" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G201" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H201" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I201" t="s">
         <v>19</v>
       </c>
       <c r="J201" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K201" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/orders.xlsx
+++ b/public/data/orders.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="816">
   <si>
     <t>Submitted time</t>
   </si>
@@ -541,7 +541,7 @@
     <t>Irene Kresentia</t>
   </si>
   <si>
-    <t>I.K.</t>
+    <t>IRENE</t>
   </si>
   <si>
     <t>35</t>
@@ -2456,6 +2456,12 @@
   </si>
   <si>
     <t>IMG_0969FB1F9BC6-1.jpeg</t>
+  </si>
+  <si>
+    <t>07/02/2026 04:03 AM</t>
+  </si>
+  <si>
+    <t>IMG_0077.png</t>
   </si>
 </sst>
 </file>
@@ -8414,7 +8420,7 @@
         <v>660</v>
       </c>
       <c r="E162" t="s">
-        <v>14</v>
+        <v>279</v>
       </c>
       <c r="F162" t="s">
         <v>16</v>
@@ -9835,6 +9841,41 @@
         <v>813</v>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>814</v>
+      </c>
+      <c r="B203" t="s">
+        <v>550</v>
+      </c>
+      <c r="C203" t="s">
+        <v>111</v>
+      </c>
+      <c r="D203" t="s">
+        <v>551</v>
+      </c>
+      <c r="E203" t="s">
+        <v>61</v>
+      </c>
+      <c r="F203" t="s">
+        <v>34</v>
+      </c>
+      <c r="G203" t="s">
+        <v>17</v>
+      </c>
+      <c r="H203" t="s">
+        <v>42</v>
+      </c>
+      <c r="I203" t="s">
+        <v>122</v>
+      </c>
+      <c r="J203" t="s">
+        <v>20</v>
+      </c>
+      <c r="K203" t="s">
+        <v>815</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/public/data/orders.xlsx
+++ b/public/data/orders.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="825">
   <si>
     <t>Submitted time</t>
   </si>
@@ -2318,9 +2318,6 @@
   </si>
   <si>
     <t>NgokNgok</t>
-  </si>
-  <si>
-    <t>-1</t>
   </si>
   <si>
     <t>WhatsApp Image 2026-06-30 at 14.46.41.jpeg</t>
@@ -9430,7 +9427,7 @@
         <v>767</v>
       </c>
       <c r="E190" t="s">
-        <v>768</v>
+        <v>33</v>
       </c>
       <c r="F190" t="s">
         <v>16</v>
@@ -9448,21 +9445,21 @@
         <v>25</v>
       </c>
       <c r="K190" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
+        <v>769</v>
+      </c>
+      <c r="B191" t="s">
         <v>770</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
+        <v>111</v>
+      </c>
+      <c r="D191" t="s">
         <v>771</v>
-      </c>
-      <c r="C191" t="s">
-        <v>111</v>
-      </c>
-      <c r="D191" t="s">
-        <v>772</v>
       </c>
       <c r="E191" t="s">
         <v>102</v>
@@ -9483,21 +9480,21 @@
         <v>20</v>
       </c>
       <c r="K191" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
+        <v>773</v>
+      </c>
+      <c r="B192" t="s">
         <v>774</v>
-      </c>
-      <c r="B192" t="s">
-        <v>775</v>
       </c>
       <c r="C192" t="s">
         <v>13</v>
       </c>
       <c r="D192" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E192" t="s">
         <v>390</v>
@@ -9518,15 +9515,15 @@
         <v>20</v>
       </c>
       <c r="K192" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
+        <v>777</v>
+      </c>
+      <c r="B193" t="s">
         <v>778</v>
-      </c>
-      <c r="B193" t="s">
-        <v>779</v>
       </c>
       <c r="C193" t="s">
         <v>13</v>
@@ -9553,12 +9550,12 @@
         <v>25</v>
       </c>
       <c r="K193" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B194" t="s">
         <v>510</v>
@@ -9588,24 +9585,24 @@
         <v>25</v>
       </c>
       <c r="K194" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
+        <v>782</v>
+      </c>
+      <c r="B195" t="s">
         <v>783</v>
-      </c>
-      <c r="B195" t="s">
-        <v>784</v>
       </c>
       <c r="C195" t="s">
         <v>116</v>
       </c>
       <c r="D195" t="s">
+        <v>784</v>
+      </c>
+      <c r="E195" t="s">
         <v>785</v>
-      </c>
-      <c r="E195" t="s">
-        <v>786</v>
       </c>
       <c r="F195" t="s">
         <v>34</v>
@@ -9623,21 +9620,21 @@
         <v>25</v>
       </c>
       <c r="K195" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
+        <v>787</v>
+      </c>
+      <c r="B196" t="s">
         <v>788</v>
-      </c>
-      <c r="B196" t="s">
-        <v>789</v>
       </c>
       <c r="C196" t="s">
         <v>116</v>
       </c>
       <c r="D196" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E196" t="s">
         <v>139</v>
@@ -9658,21 +9655,21 @@
         <v>25</v>
       </c>
       <c r="K196" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
+        <v>791</v>
+      </c>
+      <c r="B197" t="s">
         <v>792</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C197" t="s">
+        <v>111</v>
+      </c>
+      <c r="D197" t="s">
         <v>793</v>
-      </c>
-      <c r="C197" t="s">
-        <v>111</v>
-      </c>
-      <c r="D197" t="s">
-        <v>794</v>
       </c>
       <c r="E197" t="s">
         <v>162</v>
@@ -9693,21 +9690,21 @@
         <v>20</v>
       </c>
       <c r="K197" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
+        <v>795</v>
+      </c>
+      <c r="B198" t="s">
         <v>796</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C198" t="s">
+        <v>111</v>
+      </c>
+      <c r="D198" t="s">
         <v>797</v>
-      </c>
-      <c r="C198" t="s">
-        <v>111</v>
-      </c>
-      <c r="D198" t="s">
-        <v>798</v>
       </c>
       <c r="E198" t="s">
         <v>125</v>
@@ -9728,21 +9725,21 @@
         <v>25</v>
       </c>
       <c r="K198" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
+        <v>799</v>
+      </c>
+      <c r="B199" t="s">
         <v>800</v>
-      </c>
-      <c r="B199" t="s">
-        <v>801</v>
       </c>
       <c r="C199" t="s">
         <v>13</v>
       </c>
       <c r="D199" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E199" t="s">
         <v>14</v>
@@ -9763,21 +9760,21 @@
         <v>20</v>
       </c>
       <c r="K199" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
+        <v>803</v>
+      </c>
+      <c r="B200" t="s">
         <v>804</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" t="s">
+        <v>111</v>
+      </c>
+      <c r="D200" t="s">
         <v>805</v>
-      </c>
-      <c r="C200" t="s">
-        <v>111</v>
-      </c>
-      <c r="D200" t="s">
-        <v>806</v>
       </c>
       <c r="E200" t="s">
         <v>15</v>
@@ -9798,15 +9795,15 @@
         <v>20</v>
       </c>
       <c r="K200" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
+        <v>807</v>
+      </c>
+      <c r="B201" t="s">
         <v>808</v>
-      </c>
-      <c r="B201" t="s">
-        <v>809</v>
       </c>
       <c r="C201" t="s">
         <v>13</v>
@@ -9833,12 +9830,12 @@
         <v>20</v>
       </c>
       <c r="K201" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B202" t="s">
         <v>547</v>
@@ -9868,21 +9865,21 @@
         <v>20</v>
       </c>
       <c r="K202" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
+        <v>812</v>
+      </c>
+      <c r="B203" t="s">
         <v>813</v>
       </c>
-      <c r="B203" t="s">
+      <c r="C203" t="s">
+        <v>111</v>
+      </c>
+      <c r="D203" t="s">
         <v>814</v>
-      </c>
-      <c r="C203" t="s">
-        <v>111</v>
-      </c>
-      <c r="D203" t="s">
-        <v>815</v>
       </c>
       <c r="E203" t="s">
         <v>162</v>
@@ -9903,12 +9900,12 @@
         <v>25</v>
       </c>
       <c r="K203" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B204" t="s">
         <v>446</v>
@@ -9943,19 +9940,19 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
+        <v>817</v>
+      </c>
+      <c r="B205" t="s">
         <v>818</v>
-      </c>
-      <c r="B205" t="s">
-        <v>819</v>
       </c>
       <c r="C205" t="s">
         <v>13</v>
       </c>
       <c r="D205" t="s">
+        <v>819</v>
+      </c>
+      <c r="E205" t="s">
         <v>820</v>
-      </c>
-      <c r="E205" t="s">
-        <v>821</v>
       </c>
       <c r="F205" t="s">
         <v>16</v>
@@ -9978,16 +9975,16 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
+        <v>821</v>
+      </c>
+      <c r="B206" t="s">
         <v>822</v>
       </c>
-      <c r="B206" t="s">
+      <c r="C206" t="s">
+        <v>111</v>
+      </c>
+      <c r="D206" t="s">
         <v>823</v>
-      </c>
-      <c r="C206" t="s">
-        <v>111</v>
-      </c>
-      <c r="D206" t="s">
-        <v>824</v>
       </c>
       <c r="E206" t="s">
         <v>55</v>
@@ -10008,7 +10005,7 @@
         <v>20</v>
       </c>
       <c r="K206" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
   </sheetData>
